--- a/school_nagatinsky/ceilling/ceilling-n.xlsx
+++ b/school_nagatinsky/ceilling/ceilling-n.xlsx
@@ -9,13 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12216" windowHeight="5784"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12216" windowHeight="5784" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="КП" sheetId="2" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="4" r:id="rId2"/>
-    <sheet name="1.1-Пт" sheetId="3" r:id="rId3"/>
-    <sheet name="2.1-Пт" sheetId="6" r:id="rId4"/>
+    <sheet name="Лист1" sheetId="7" r:id="rId2"/>
+    <sheet name="Лист2" sheetId="4" r:id="rId3"/>
+    <sheet name="0.1-Шт" sheetId="8" r:id="rId4"/>
+    <sheet name="1.1-Пт" sheetId="3" r:id="rId5"/>
+    <sheet name="2.1-Пт" sheetId="6" r:id="rId6"/>
+    <sheet name="0.2-Шт" sheetId="11" r:id="rId7"/>
+    <sheet name="1.2-Пт" sheetId="9" r:id="rId8"/>
+    <sheet name="2.2-Пт" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -33,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="257">
   <si>
     <t>Номер п/п</t>
   </si>
@@ -784,12 +789,6 @@
     <t>фиолетовое</t>
   </si>
   <si>
-    <t>1-4 этажи. Шпаклевка гипсовая базовая т.2 мм. Тип: ЧНП-5</t>
-  </si>
-  <si>
-    <t>1-4 этажи. Шпаклевка гипсовая финишная т.2 мм. Тип: ЧНП-5</t>
-  </si>
-  <si>
     <t>Наименование работ</t>
   </si>
   <si>
@@ -822,6 +821,25 @@
   <si>
     <t xml:space="preserve">ЧНП-3, ЧНП-6, ЧНП-7 
 </t>
+  </si>
+  <si>
+    <t>1-3 этажи.
+Тип: ЧНП-5</t>
+  </si>
+  <si>
+    <t>1-3 этажи. Шпаклевка гипсовая базовая т.2 мм. Тип: ЧНП-5</t>
+  </si>
+  <si>
+    <t>1.094, 1.94а</t>
+  </si>
+  <si>
+    <t>2.047, 2.047а, 2.047б</t>
+  </si>
+  <si>
+    <t>3.047, 3.047а, 3.047б</t>
+  </si>
+  <si>
+    <t>1-3 этажи. Шпаклевка гипсовая финишная т.2 мм. Тип: ЧНП-5</t>
   </si>
 </sst>
 </file>
@@ -831,7 +849,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -1219,12 +1237,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -1246,12 +1258,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" indent="6" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" indent="6" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1272,11 +1278,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1289,39 +1295,23 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="6" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="6" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1541,6 +1531,34 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
   <extLst>
@@ -1555,16 +1573,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A1:I111" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A1:I111" totalsRowShown="0" headerRowDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:I111"/>
   <tableColumns count="9">
-    <tableColumn id="1" name="Номер п/п" dataDxfId="6"/>
-    <tableColumn id="2" name="Код узла ИСР" dataDxfId="5"/>
+    <tableColumn id="1" name="Номер п/п" dataDxfId="5"/>
+    <tableColumn id="2" name="Код узла ИСР" dataDxfId="4"/>
     <tableColumn id="3" name="Наименование затрат"/>
-    <tableColumn id="4" name="Комментарий по ИСР" dataDxfId="4"/>
-    <tableColumn id="5" name="Описание" dataDxfId="3"/>
-    <tableColumn id="6" name="Ед. изм." dataDxfId="2"/>
-    <tableColumn id="7" name="Коэф.расхода" dataDxfId="1"/>
+    <tableColumn id="4" name="Комментарий по ИСР" dataDxfId="3"/>
+    <tableColumn id="5" name="Описание" dataDxfId="2"/>
+    <tableColumn id="6" name="Ед. изм." dataDxfId="1"/>
+    <tableColumn id="7" name="Коэф.расхода" dataDxfId="0"/>
     <tableColumn id="8" name="Кол-во БО"/>
     <tableColumn id="9" name="Общее кол-во"/>
   </tableColumns>
@@ -4367,6 +4385,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:T46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4375,7 +4402,7 @@
   <sheetData>
     <row r="1" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B1" s="30" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="2:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
@@ -4401,10 +4428,10 @@
       <c r="I2" s="27">
         <v>4</v>
       </c>
-      <c r="Q2" s="32" t="s">
+      <c r="Q2" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="R2" s="33"/>
+      <c r="R2" s="55"/>
     </row>
     <row r="3" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B3" s="29" t="s">
@@ -4431,10 +4458,10 @@
       <c r="I3" s="27">
         <v>3</v>
       </c>
-      <c r="Q3" s="34" t="s">
+      <c r="Q3" s="32" t="s">
         <v>233</v>
       </c>
-      <c r="R3" s="35" t="s">
+      <c r="R3" s="33" t="s">
         <v>234</v>
       </c>
     </row>
@@ -4473,10 +4500,10 @@
       <c r="M4">
         <v>1171.2</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="34">
         <v>4001</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="35">
         <v>68.8</v>
       </c>
       <c r="S4" s="31" t="s">
@@ -4512,10 +4539,10 @@
         <f t="shared" ref="J5:J9" si="0">SUM(C5:I5)</f>
         <v>3078.1</v>
       </c>
-      <c r="Q5" s="36">
+      <c r="Q5" s="34">
         <v>4002</v>
       </c>
-      <c r="R5" s="37">
+      <c r="R5" s="35">
         <v>26.9</v>
       </c>
       <c r="S5" s="31" t="s">
@@ -4557,10 +4584,10 @@
       <c r="M6">
         <v>7010.2</v>
       </c>
-      <c r="Q6" s="36">
+      <c r="Q6" s="34">
         <v>4003</v>
       </c>
-      <c r="R6" s="37">
+      <c r="R6" s="35">
         <v>43.9</v>
       </c>
       <c r="S6" s="31" t="s">
@@ -4596,10 +4623,10 @@
         <f t="shared" si="0"/>
         <v>37.6</v>
       </c>
-      <c r="Q7" s="38">
+      <c r="Q7" s="36">
         <v>4004</v>
       </c>
-      <c r="R7" s="39">
+      <c r="R7" s="37">
         <v>54.8</v>
       </c>
       <c r="S7" s="31" t="s">
@@ -4635,10 +4662,10 @@
         <f t="shared" si="0"/>
         <v>165.5</v>
       </c>
-      <c r="Q8" s="36">
+      <c r="Q8" s="34">
         <v>4005</v>
       </c>
-      <c r="R8" s="37">
+      <c r="R8" s="35">
         <v>52</v>
       </c>
       <c r="S8" s="31" t="s">
@@ -4675,15 +4702,15 @@
         <v>638.1</v>
       </c>
       <c r="L9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="M9">
         <v>827.7</v>
       </c>
-      <c r="Q9" s="36">
+      <c r="Q9" s="34">
         <v>4006</v>
       </c>
-      <c r="R9" s="37">
+      <c r="R9" s="35">
         <v>56.6</v>
       </c>
       <c r="S9" s="31" t="s">
@@ -4691,10 +4718,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q10" s="36">
+      <c r="Q10" s="34">
         <v>4007</v>
       </c>
-      <c r="R10" s="37">
+      <c r="R10" s="35">
         <v>19.2</v>
       </c>
       <c r="S10" s="31" t="s">
@@ -4702,10 +4729,10 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q11" s="36">
+      <c r="Q11" s="34">
         <v>4008</v>
       </c>
-      <c r="R11" s="37">
+      <c r="R11" s="35">
         <v>95.5</v>
       </c>
       <c r="S11" s="31" t="s">
@@ -4713,10 +4740,10 @@
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q12" s="36">
+      <c r="Q12" s="34">
         <v>4009</v>
       </c>
-      <c r="R12" s="37">
+      <c r="R12" s="35">
         <v>30.6</v>
       </c>
       <c r="S12" s="31" t="s">
@@ -4724,10 +4751,10 @@
       </c>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q13" s="36">
+      <c r="Q13" s="34">
         <v>4010</v>
       </c>
-      <c r="R13" s="37">
+      <c r="R13" s="35">
         <v>241.6</v>
       </c>
       <c r="S13" s="31" t="s">
@@ -4735,10 +4762,10 @@
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q14" s="40" t="s">
+      <c r="Q14" s="38" t="s">
         <v>235</v>
       </c>
-      <c r="R14" s="37">
+      <c r="R14" s="35">
         <v>72.400000000000006</v>
       </c>
       <c r="S14" s="31" t="s">
@@ -4746,10 +4773,10 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q15" s="36">
+      <c r="Q15" s="34">
         <v>4011</v>
       </c>
-      <c r="R15" s="37">
+      <c r="R15" s="35">
         <v>14</v>
       </c>
       <c r="S15" s="30" t="s">
@@ -4757,10 +4784,10 @@
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q16" s="36">
+      <c r="Q16" s="34">
         <v>4012</v>
       </c>
-      <c r="R16" s="37">
+      <c r="R16" s="35">
         <v>4.2</v>
       </c>
       <c r="S16" s="30" t="s">
@@ -4781,10 +4808,10 @@
       <c r="J17" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="Q17" s="36">
+      <c r="Q17" s="34">
         <v>4013</v>
       </c>
-      <c r="R17" s="37">
+      <c r="R17" s="35">
         <v>6.7</v>
       </c>
       <c r="S17" s="30" t="s">
@@ -4808,13 +4835,13 @@
       <c r="I18" s="27">
         <v>14</v>
       </c>
-      <c r="Q18" s="36">
+      <c r="Q18" s="34">
         <v>4014</v>
       </c>
-      <c r="R18" s="37">
+      <c r="R18" s="35">
         <v>9.8000000000000007</v>
       </c>
-      <c r="S18" s="57" t="s">
+      <c r="S18" s="53" t="s">
         <v>231</v>
       </c>
     </row>
@@ -4835,10 +4862,10 @@
       <c r="I19" s="27">
         <v>4.2</v>
       </c>
-      <c r="Q19" s="36">
+      <c r="Q19" s="34">
         <v>4015</v>
       </c>
-      <c r="R19" s="37">
+      <c r="R19" s="35">
         <v>16.2</v>
       </c>
       <c r="S19" s="30" t="s">
@@ -4862,10 +4889,10 @@
       <c r="I20" s="27">
         <v>6.7</v>
       </c>
-      <c r="Q20" s="36">
+      <c r="Q20" s="34">
         <v>4016</v>
       </c>
-      <c r="R20" s="37">
+      <c r="R20" s="35">
         <v>4.9000000000000004</v>
       </c>
       <c r="S20" s="31" t="s">
@@ -4885,10 +4912,10 @@
       <c r="I21" s="27">
         <v>16.2</v>
       </c>
-      <c r="Q21" s="36">
+      <c r="Q21" s="34">
         <v>4017</v>
       </c>
-      <c r="R21" s="37">
+      <c r="R21" s="35">
         <v>4.8</v>
       </c>
       <c r="S21" s="30" t="s">
@@ -4908,10 +4935,10 @@
       <c r="I22" s="27">
         <v>4.8</v>
       </c>
-      <c r="Q22" s="36">
+      <c r="Q22" s="34">
         <v>4018</v>
       </c>
-      <c r="R22" s="37">
+      <c r="R22" s="35">
         <v>32</v>
       </c>
       <c r="S22" s="31" t="s">
@@ -4919,10 +4946,10 @@
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="Q23" s="41">
+      <c r="Q23" s="56">
         <v>855</v>
       </c>
-      <c r="R23" s="42"/>
+      <c r="R23" s="57"/>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B24" s="31" t="s">
@@ -4941,13 +4968,13 @@
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B25" s="31" t="s">
-        <v>249</v>
-      </c>
-      <c r="C25" s="44">
+        <v>247</v>
+      </c>
+      <c r="C25" s="40">
         <v>98.5</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E25" s="27">
         <v>130.4</v>
@@ -4965,9 +4992,9 @@
         <v>72.400000000000006</v>
       </c>
       <c r="K25" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q25" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q25" s="39" t="s">
         <v>238</v>
       </c>
       <c r="R25">
@@ -4984,13 +5011,13 @@
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B26" s="31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C26" s="27">
         <v>117.6</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E26" s="27">
         <v>200.9</v>
@@ -5024,7 +5051,7 @@
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B27" s="31" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C27" s="27">
         <v>203.1</v>
@@ -5100,7 +5127,7 @@
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="30" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.3">
@@ -5154,7 +5181,7 @@
       </c>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B38" s="54" t="s">
+      <c r="B38" s="50" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="27">
@@ -5168,7 +5195,7 @@
       <c r="I38" s="27"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="50" t="s">
         <v>238</v>
       </c>
       <c r="C39" s="27">
@@ -5190,7 +5217,7 @@
       </c>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B40" s="54">
+      <c r="B40" s="50">
         <v>2</v>
       </c>
       <c r="C40" s="27"/>
@@ -5210,7 +5237,7 @@
       </c>
     </row>
     <row r="41" spans="2:16" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B41" s="55">
+      <c r="B41" s="51">
         <v>3</v>
       </c>
       <c r="C41" s="27">
@@ -5238,15 +5265,15 @@
         <f>SUM(C41:I41)</f>
         <v>547.9</v>
       </c>
-      <c r="O41" s="56" t="s">
-        <v>252</v>
+      <c r="O41" s="52" t="s">
+        <v>250</v>
       </c>
       <c r="P41">
         <v>827.7</v>
       </c>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B42" s="55">
+      <c r="B42" s="51">
         <v>4</v>
       </c>
       <c r="C42" s="27">
@@ -5277,7 +5304,7 @@
       <c r="O42" s="30"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B43" s="55">
+      <c r="B43" s="51">
         <v>5</v>
       </c>
       <c r="C43" s="27">
@@ -5308,7 +5335,7 @@
       <c r="O43" s="30"/>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B44" s="55">
+      <c r="B44" s="51">
         <v>6</v>
       </c>
       <c r="C44" s="27">
@@ -5339,7 +5366,7 @@
       <c r="O44" s="30"/>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B45" s="55">
+      <c r="B45" s="51">
         <v>7</v>
       </c>
       <c r="C45" s="27">
@@ -5410,180 +5437,162 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="52" customWidth="1"/>
-    <col min="2" max="2" width="28.77734375" style="52" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" style="52" customWidth="1"/>
-    <col min="4" max="4" width="19" style="52" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" style="52" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="52"/>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="32.109375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="48"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="102" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49">
+        <f>D11</f>
+        <v>979.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A4" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="46">
+        <v>1</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="47">
+        <v>116.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
+        <v>2</v>
+      </c>
+      <c r="B6" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="C1" s="45" t="s">
-        <v>215</v>
-      </c>
-      <c r="D1" s="45" t="s">
+      <c r="C6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="47">
+        <v>202.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
+        <v>3</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="47">
+        <v>129.80000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="46">
         <v>4</v>
       </c>
-      <c r="E1" s="45" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.35">
-      <c r="A2" s="50">
-        <v>1</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="53">
-        <f>D12</f>
-        <v>979.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.35">
-      <c r="A3" s="50">
-        <v>2</v>
-      </c>
-      <c r="B3" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="49" t="s">
-        <v>241</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="53">
-        <f>E2</f>
-        <v>979.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A5" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="45" t="s">
-        <v>215</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="50">
-        <v>1</v>
-      </c>
-      <c r="B6" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="51">
-        <v>116.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="50">
-        <v>2</v>
-      </c>
-      <c r="B7" s="45" t="s">
+      <c r="B8" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="51">
-        <v>202.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="50">
-        <v>3</v>
-      </c>
-      <c r="B8" s="45" t="s">
+      <c r="C8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="47">
+        <v>200.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="46">
+        <v>5</v>
+      </c>
+      <c r="B9" s="41" t="s">
         <v>245</v>
       </c>
-      <c r="C8" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="51">
-        <v>129.80000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="50">
-        <v>4</v>
-      </c>
-      <c r="B9" s="45" t="s">
-        <v>246</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="51">
-        <v>200.1</v>
+      <c r="C9" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="47">
+        <v>130.30000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="50">
-        <v>5</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="51">
-        <v>130.30000000000001</v>
+      <c r="A10" s="46">
+        <v>6</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="47">
+        <v>200.7</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="50">
-        <v>6</v>
-      </c>
-      <c r="B11" s="45" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="51">
-        <v>200.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="50"/>
-      <c r="B12" s="45" t="s">
+      <c r="A11" s="46"/>
+      <c r="B11" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="C12" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="51">
-        <f>SUM(D6:D11)</f>
+      <c r="C11" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="47">
+        <f>SUM(D5:D10)</f>
         <v>979.8</v>
       </c>
     </row>
@@ -5592,163 +5601,741 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="19" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49">
+        <f>D12</f>
+        <v>979.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.35">
+      <c r="A3" s="46">
+        <v>2</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="49">
+        <f>E2</f>
+        <v>979.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A5" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
+        <v>1</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="47">
+        <v>116.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
+        <v>2</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="47">
+        <v>202.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="46">
+        <v>3</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="47">
+        <v>129.80000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="46">
+        <v>4</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="47">
+        <v>200.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="46">
+        <v>5</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="47">
+        <v>130.30000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="46">
+        <v>6</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="47">
+        <v>200.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="46"/>
+      <c r="B12" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="47">
+        <f>SUM(D6:D11)</f>
+        <v>979.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="52" customWidth="1"/>
-    <col min="2" max="2" width="28.77734375" style="52" customWidth="1"/>
-    <col min="3" max="3" width="38.6640625" style="52" customWidth="1"/>
-    <col min="4" max="4" width="19" style="52" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" style="52" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="52"/>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" style="48" customWidth="1"/>
+    <col min="4" max="4" width="19" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="48"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45" t="s">
-        <v>242</v>
-      </c>
-      <c r="C1" s="45" t="s">
+      <c r="B1" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="41" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="108" x14ac:dyDescent="0.35">
-      <c r="A2" s="50">
-        <v>1</v>
-      </c>
-      <c r="B2" s="46" t="s">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="53">
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49">
         <f>D11</f>
         <v>979.8</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="41" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="50">
-        <v>1</v>
-      </c>
-      <c r="B5" s="45" t="s">
+      <c r="A5" s="46">
+        <v>1</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="47">
+        <v>116.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
+        <v>2</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>242</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="47">
+        <v>202.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
+        <v>3</v>
+      </c>
+      <c r="B7" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="C5" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="51">
-        <v>116.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="50">
-        <v>2</v>
-      </c>
-      <c r="B6" s="45" t="s">
+      <c r="C7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="47">
+        <v>129.80000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="46">
+        <v>4</v>
+      </c>
+      <c r="B8" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="C6" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="51">
-        <v>202.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="50">
-        <v>3</v>
-      </c>
-      <c r="B7" s="45" t="s">
+      <c r="C8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="47">
+        <v>200.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="46">
+        <v>5</v>
+      </c>
+      <c r="B9" s="41" t="s">
         <v>245</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="51">
-        <v>129.80000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="50">
-        <v>4</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>246</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="51">
-        <v>200.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="50">
-        <v>5</v>
-      </c>
-      <c r="B9" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="51">
+      <c r="C9" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="47">
         <v>130.30000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="50">
+      <c r="A10" s="46">
         <v>6</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="41" t="s">
         <v>222</v>
       </c>
-      <c r="C10" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="51">
+      <c r="C10" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="47">
         <v>200.7</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="50"/>
-      <c r="B11" s="45" t="s">
+      <c r="A11" s="46"/>
+      <c r="B11" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="C11" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="51">
+      <c r="C11" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="47">
         <f>SUM(D5:D10)</f>
         <v>979.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="32.109375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="102" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49">
+        <f>D8</f>
+        <v>891.64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A4" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="46">
+        <v>1</v>
+      </c>
+      <c r="B5" s="41" t="str">
+        <f>'1.2-Пт'!B6</f>
+        <v>1.094, 1.94а</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="47">
+        <f>'1.2-Пт'!D6</f>
+        <v>294.16000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
+        <v>2</v>
+      </c>
+      <c r="B6" s="41" t="str">
+        <f>'1.2-Пт'!B7</f>
+        <v>2.047, 2.047а, 2.047б</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="47">
+        <f>'1.2-Пт'!D7</f>
+        <v>285.60000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
+        <v>3</v>
+      </c>
+      <c r="B7" s="41" t="str">
+        <f>'1.2-Пт'!B8</f>
+        <v>3.047, 3.047а, 3.047б</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="47">
+        <f>'1.2-Пт'!D8</f>
+        <v>311.88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="46"/>
+      <c r="B8" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="47">
+        <f>SUM(D5:D7)</f>
+        <v>891.64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="19" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49">
+        <f>D9</f>
+        <v>891.64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.35">
+      <c r="A3" s="46">
+        <v>2</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="49">
+        <f>E2</f>
+        <v>891.64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A5" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
+        <v>1</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="47">
+        <v>294.16000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
+        <v>2</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="47">
+        <v>285.60000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="46">
+        <v>3</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>255</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="47">
+        <v>311.88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="46"/>
+      <c r="B9" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="47">
+        <f>SUM(D6:D8)</f>
+        <v>891.64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" style="48" customWidth="1"/>
+    <col min="4" max="4" width="19" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="108" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49">
+        <f>D8</f>
+        <v>891.64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A4" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="46">
+        <v>1</v>
+      </c>
+      <c r="B5" s="41" t="str">
+        <f>'1.2-Пт'!B6</f>
+        <v>1.094, 1.94а</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="47">
+        <f>'1.2-Пт'!D6</f>
+        <v>294.16000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
+        <v>2</v>
+      </c>
+      <c r="B6" s="41" t="str">
+        <f>'1.2-Пт'!B7</f>
+        <v>2.047, 2.047а, 2.047б</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="47">
+        <f>'1.2-Пт'!D7</f>
+        <v>285.60000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
+        <v>3</v>
+      </c>
+      <c r="B7" s="41" t="str">
+        <f>'1.2-Пт'!B8</f>
+        <v>3.047, 3.047а, 3.047б</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="47">
+        <f>'1.2-Пт'!D8</f>
+        <v>311.88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="46"/>
+      <c r="B8" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="47">
+        <f>SUM(D5:D7)</f>
+        <v>891.64</v>
       </c>
     </row>
   </sheetData>

--- a/school_nagatinsky/ceilling/ceilling-n.xlsx
+++ b/school_nagatinsky/ceilling/ceilling-n.xlsx
@@ -9,18 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12216" windowHeight="5784" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12216" windowHeight="5784" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="КП" sheetId="2" r:id="rId1"/>
-    <sheet name="Лист1" sheetId="7" r:id="rId2"/>
-    <sheet name="Лист2" sheetId="4" r:id="rId3"/>
-    <sheet name="0.1-Шт" sheetId="8" r:id="rId4"/>
-    <sheet name="1.1-Пт" sheetId="3" r:id="rId5"/>
-    <sheet name="2.1-Пт" sheetId="6" r:id="rId6"/>
-    <sheet name="0.2-Шт" sheetId="11" r:id="rId7"/>
-    <sheet name="1.2-Пт" sheetId="9" r:id="rId8"/>
-    <sheet name="2.2-Пт" sheetId="10" r:id="rId9"/>
+    <sheet name="Расчет" sheetId="4" r:id="rId2"/>
+    <sheet name="2.3в3" sheetId="15" r:id="rId3"/>
+    <sheet name="1.4ШпЧНП7_3вып" sheetId="14" r:id="rId4"/>
+    <sheet name="1.3ШпЧНП5_3вып" sheetId="13" r:id="rId5"/>
+    <sheet name="0.3-Шт3вып" sheetId="12" r:id="rId6"/>
+    <sheet name="2.2-Пт" sheetId="10" r:id="rId7"/>
+    <sheet name="2.1-Пт" sheetId="6" r:id="rId8"/>
+    <sheet name="1.2-Пт" sheetId="9" r:id="rId9"/>
+    <sheet name="1.1-Пт" sheetId="3" r:id="rId10"/>
+    <sheet name="0.2-Шт" sheetId="11" r:id="rId11"/>
+    <sheet name="0.1-Шт" sheetId="8" r:id="rId12"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="277">
   <si>
     <t>Номер п/п</t>
   </si>
@@ -840,6 +843,67 @@
   </si>
   <si>
     <t>1-3 этажи. Шпаклевка гипсовая финишная т.2 мм. Тип: ЧНП-5</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>Сумма</t>
+  </si>
+  <si>
+    <t>В конце РД рев F есть ведомость по каждому помещению</t>
+  </si>
+  <si>
+    <t>1.059</t>
+  </si>
+  <si>
+    <t>1.025</t>
+  </si>
+  <si>
+    <t>1.011</t>
+  </si>
+  <si>
+    <t>2.010</t>
+  </si>
+  <si>
+    <t>3.012</t>
+  </si>
+  <si>
+    <t>ЧНП-7</t>
+  </si>
+  <si>
+    <t>Пом</t>
+  </si>
+  <si>
+    <t>Тип</t>
+  </si>
+  <si>
+    <t>1 этаж.
+Тип: ЧНП-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-3 этажи. Шпаклевка гипсовая базовая т.2 мм. Тип: ЧНП-7 </t>
+  </si>
+  <si>
+    <t>1-3 этажи. Шпаклевка гипсовая финишная т.2 мм. Тип: ЧНП-7</t>
+  </si>
+  <si>
+    <t>1 этаж. Шпаклевка гипсовая финишная т.2 мм. Тип: ЧНП-5</t>
+  </si>
+  <si>
+    <t>1 этаж. Шпаклевка гипсовая базовая т.2 мм. Тип: ЧНП-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тип: ПТ-2.1. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тип: ПТ-2.15. </t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1069,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1144,11 +1208,66 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1295,6 +1414,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1306,6 +1426,36 @@
     </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" indent="6" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1574,7 +1724,63 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A1:I111" totalsRowShown="0" headerRowDxfId="7" tableBorderDxfId="6">
-  <autoFilter ref="A1:I111"/>
+  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="A1:I111">
+    <filterColumn colId="4">
+      <filters>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <x14:filter val="Тип: ПТ-1. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: KM1, Износостойкость: 2 класс истирания"/>
+            <x14:filter val="Тип: ПТ-1.2. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: KM1, Износостойкость: 2 класс истирания"/>
+            <x14:filter val="Тип: ПТ-10. Подвесной акустический потолок из минерального стекловолокна. Производитель: Акустик Групп. В состав входит: BA1200 - Акустическая панель Baffle Acoustic Shell, Прямоугольник 1200*600*20, кромка A (упак/8шт/5,76м2) 3 225,6 м2; 165138 - Европодвес 500мм AR (P) С - 2 300 шт; 119603 - Уголок пристеночный 19х24 (3 м) RAL 9010 - 2 295 пог. м; 042387 - Т-профиль 24х33х3600 Премиум белый - 2 736 пог. м; 042389 Т-профиль 24х26х1200 белый - 5 472 пог. м."/>
+            <x14:filter val="Тип: ПТ-2. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: KM1, Износостойкость: 2 класс истирания, Цвет: RAL 7044/серый шелк"/>
+            <x14:filter val="Тип: ПТ-2.1. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет:"/>
+            <x14:filter val="Тип: ПТ-2.12. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: NCS S 5030-R90B"/>
+            <x14:filter val="Тип: ПТ-2.13. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: NCS S 2030-R80B"/>
+            <x14:filter val="Тип: ПТ-2.14. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: NCS S 2030-R80B"/>
+            <x14:filter val="Тип: ПТ-2.15. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: RAL 7016"/>
+            <x14:filter val="Тип: ПТ-2.16. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: RAL 7044/Серый шелк"/>
+            <x14:filter val="Тип: ПТ-2.9. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: NCS S 5020-R70B"/>
+            <x14:filter val="Тип: ПТ-5. Огнестойкая краска краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: RAL 9003/Белый"/>
+            <x14:filter val="Тип: ПТ-8. Кассетный металлический потолок. Albes «TEGULAR»"/>
+            <x14:filter val="Тип: ПТБ-1.1"/>
+            <x14:filter val="Тип: ПТБ-1.2"/>
+            <x14:filter val="Тип: ПТБ-1.3"/>
+            <x14:filter val="Тип: ПТБ-1.4"/>
+            <x14:filter val="Тип: ПТБ-2.1"/>
+            <x14:filter val="Тип: ПТБ-2.2"/>
+            <x14:filter val="Тип: ПТБ-2.3"/>
+            <x14:filter val="Тип: ПТБ-2.4"/>
+            <x14:filter val="Тип: ПТБ-4"/>
+            <x14:filter val="Тип: ПТБ-5"/>
+          </mc:Choice>
+          <mc:Fallback>
+            <filter val="Тип: ПТ-1. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: KM1, Износостойкость: 2 класс истирания"/>
+            <filter val="Тип: ПТ-1.2. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: KM1, Износостойкость: 2 класс истирания"/>
+            <filter val="Тип: ПТ-2. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: KM1, Износостойкость: 2 класс истирания, Цвет: RAL 7044/серый шелк"/>
+            <filter val="Тип: ПТ-2.1. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет:"/>
+            <filter val="Тип: ПТ-2.12. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: NCS S 5030-R90B"/>
+            <filter val="Тип: ПТ-2.13. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: NCS S 2030-R80B"/>
+            <filter val="Тип: ПТ-2.14. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: NCS S 2030-R80B"/>
+            <filter val="Тип: ПТ-2.15. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: RAL 7016"/>
+            <filter val="Тип: ПТ-2.16. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: RAL 7044/Серый шелк"/>
+            <filter val="Тип: ПТ-2.9. Матовая водно-дисперсионная моющаяся краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: NCS S 5020-R70B"/>
+            <filter val="Тип: ПТ-5. Огнестойкая краска краска ANTEGA СТРОИТЕЛЬ, Класс ПБ: НГ, Износостойкость: 1 класс истирания, Цвет: RAL 9003/Белый"/>
+            <filter val="Тип: ПТ-8. Кассетный металлический потолок. Albes «TEGULAR»"/>
+            <filter val="Тип: ПТБ-1.1"/>
+            <filter val="Тип: ПТБ-1.2"/>
+            <filter val="Тип: ПТБ-1.3"/>
+            <filter val="Тип: ПТБ-1.4"/>
+            <filter val="Тип: ПТБ-2.1"/>
+            <filter val="Тип: ПТБ-2.2"/>
+            <filter val="Тип: ПТБ-2.3"/>
+            <filter val="Тип: ПТБ-2.4"/>
+            <filter val="Тип: ПТБ-4"/>
+            <filter val="Тип: ПТБ-5"/>
+          </mc:Fallback>
+        </mc:AlternateContent>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="9">
     <tableColumn id="1" name="Номер п/п" dataDxfId="5"/>
     <tableColumn id="2" name="Код узла ИСР" dataDxfId="4"/>
@@ -1877,17 +2083,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:I111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="55.6640625" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="55.5546875" customWidth="1"/>
+    <col min="5" max="5" width="56.33203125" customWidth="1"/>
     <col min="6" max="6" width="16.44140625" customWidth="1"/>
     <col min="7" max="7" width="17.77734375" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" customWidth="1"/>
     <col min="9" max="9" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1920,7 +2129,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="16.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>23</v>
       </c>
@@ -1937,7 +2146,7 @@
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
     </row>
-    <row r="3" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="16.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>26</v>
       </c>
@@ -1954,7 +2163,7 @@
       <c r="H3" s="11"/>
       <c r="I3" s="11"/>
     </row>
-    <row r="4" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="54" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>29</v>
       </c>
@@ -1979,7 +2188,7 @@
         <v>1171.2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>33</v>
       </c>
@@ -2000,7 +2209,7 @@
         <v>7612.8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>34</v>
       </c>
@@ -2021,7 +2230,7 @@
         <v>175.68</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="54" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>35</v>
       </c>
@@ -2046,7 +2255,7 @@
         <v>7010.2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>37</v>
       </c>
@@ -2067,7 +2276,7 @@
         <v>1752.55</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>38</v>
       </c>
@@ -2088,7 +2297,7 @@
         <v>35051</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="54" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>39</v>
       </c>
@@ -2113,7 +2322,7 @@
         <v>827.7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>42</v>
       </c>
@@ -2134,7 +2343,7 @@
         <v>1241.55</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>43</v>
       </c>
@@ -2155,7 +2364,7 @@
         <v>124.155</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>44</v>
       </c>
@@ -2180,7 +2389,7 @@
         <v>827.7</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>46</v>
       </c>
@@ -2201,7 +2410,7 @@
         <v>124.155</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>47</v>
       </c>
@@ -2222,7 +2431,7 @@
         <v>1241.55</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>48</v>
       </c>
@@ -2247,7 +2456,7 @@
         <v>1171.2</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>51</v>
       </c>
@@ -2268,7 +2477,7 @@
         <v>2342.4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>52</v>
       </c>
@@ -2289,7 +2498,7 @@
         <v>175.68</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>53</v>
       </c>
@@ -2314,7 +2523,7 @@
         <v>1171.2</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>55</v>
       </c>
@@ -2335,7 +2544,7 @@
         <v>175.68</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>56</v>
       </c>
@@ -2356,7 +2565,7 @@
         <v>2342.4</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>57</v>
       </c>
@@ -2381,7 +2590,7 @@
         <v>7010.2</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="54" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>61</v>
       </c>
@@ -2402,7 +2611,7 @@
         <v>12618.36</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>63</v>
       </c>
@@ -2423,7 +2632,7 @@
         <v>1051.53</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>64</v>
       </c>
@@ -2448,7 +2657,7 @@
         <v>7010.2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>66</v>
       </c>
@@ -2469,7 +2678,7 @@
         <v>1051.53</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="54" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>67</v>
       </c>
@@ -2490,7 +2699,7 @@
         <v>12618.36</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="16.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>68</v>
       </c>
@@ -2507,7 +2716,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>71</v>
       </c>
@@ -2532,7 +2741,7 @@
         <v>47.78</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>75</v>
       </c>
@@ -2553,7 +2762,7 @@
         <v>14.334</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>76</v>
       </c>
@@ -2574,7 +2783,7 @@
         <v>7.1669999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>77</v>
       </c>
@@ -2599,7 +2808,7 @@
         <v>727.11</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>79</v>
       </c>
@@ -2620,7 +2829,7 @@
         <v>109.06699999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>80</v>
       </c>
@@ -2666,7 +2875,7 @@
         <v>503.14</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>83</v>
       </c>
@@ -2687,7 +2896,7 @@
         <v>150.94200000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>84</v>
       </c>
@@ -2733,7 +2942,7 @@
         <v>2411.1799999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>87</v>
       </c>
@@ -2754,7 +2963,7 @@
         <v>361.67700000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>88</v>
       </c>
@@ -2800,7 +3009,7 @@
         <v>18.829999999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>91</v>
       </c>
@@ -2821,7 +3030,7 @@
         <v>5.649</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>92</v>
       </c>
@@ -2867,7 +3076,7 @@
         <v>57.38</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>95</v>
       </c>
@@ -2888,7 +3097,7 @@
         <v>8.6069999999999993</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
         <v>96</v>
       </c>
@@ -2934,7 +3143,7 @@
         <v>57.27</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>99</v>
       </c>
@@ -2955,7 +3164,7 @@
         <v>17.181000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>100</v>
       </c>
@@ -3001,7 +3210,7 @@
         <v>28.67</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>103</v>
       </c>
@@ -3022,7 +3231,7 @@
         <v>4.3010000000000002</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>104</v>
       </c>
@@ -3068,7 +3277,7 @@
         <v>4293.76</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>107</v>
       </c>
@@ -3089,7 +3298,7 @@
         <v>1288.1279999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>108</v>
       </c>
@@ -3135,7 +3344,7 @@
         <v>355.1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
         <v>111</v>
       </c>
@@ -3156,7 +3365,7 @@
         <v>53.265000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
         <v>112</v>
       </c>
@@ -3202,7 +3411,7 @@
         <v>3797.28</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13" t="s">
         <v>115</v>
       </c>
@@ -3223,7 +3432,7 @@
         <v>1139.184</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>116</v>
       </c>
@@ -3244,7 +3453,7 @@
         <v>569.59199999999998</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" ht="16.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13" t="s">
         <v>117</v>
       </c>
@@ -3261,7 +3470,7 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="54" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>120</v>
       </c>
@@ -3284,7 +3493,7 @@
         <v>7535.57</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
         <v>123</v>
       </c>
@@ -3355,7 +3564,7 @@
         <v>147.91</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>131</v>
       </c>
@@ -3403,7 +3612,7 @@
         <v>144.66999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>135</v>
       </c>
@@ -3451,7 +3660,7 @@
         <v>144.31</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
         <v>139</v>
       </c>
@@ -3499,7 +3708,7 @@
         <v>802.27</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
         <v>142</v>
       </c>
@@ -3547,7 +3756,7 @@
         <v>143.38999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
         <v>146</v>
       </c>
@@ -3595,7 +3804,7 @@
         <v>144.66999999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
         <v>150</v>
       </c>
@@ -3643,7 +3852,7 @@
         <v>144.31</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
         <v>154</v>
       </c>
@@ -3691,7 +3900,7 @@
         <v>802.41</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
         <v>157</v>
       </c>
@@ -3739,7 +3948,7 @@
         <v>236.15</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="90" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="90" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
         <v>161</v>
       </c>
@@ -3787,7 +3996,7 @@
         <v>286.12</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="90" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" ht="90" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="13" t="s">
         <v>165</v>
       </c>
@@ -3810,7 +4019,7 @@
         <v>286.12</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" ht="54" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="13" t="s">
         <v>167</v>
       </c>
@@ -3835,7 +4044,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
         <v>171</v>
       </c>
@@ -3856,7 +4065,7 @@
         <v>13.16</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="13" t="s">
         <v>173</v>
       </c>
@@ -3877,7 +4086,7 @@
         <v>11.28</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
         <v>175</v>
       </c>
@@ -3898,7 +4107,7 @@
         <v>135.36000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
         <v>177</v>
       </c>
@@ -3919,7 +4128,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
         <v>179</v>
       </c>
@@ -3940,7 +4149,7 @@
         <v>77.08</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
         <v>181</v>
       </c>
@@ -3961,7 +4170,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="13" t="s">
         <v>183</v>
       </c>
@@ -3982,7 +4191,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
         <v>185</v>
       </c>
@@ -4003,7 +4212,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
         <v>187</v>
       </c>
@@ -4024,7 +4233,7 @@
         <v>176.72</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="13" t="s">
         <v>189</v>
       </c>
@@ -4045,7 +4254,7 @@
         <v>157.91999999999999</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
         <v>191</v>
       </c>
@@ -4070,7 +4279,7 @@
         <v>624.6</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>193</v>
       </c>
@@ -4091,7 +4300,7 @@
         <v>2623.32</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>194</v>
       </c>
@@ -4112,7 +4321,7 @@
         <v>2935.62</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>195</v>
       </c>
@@ -4133,7 +4342,7 @@
         <v>1280.43</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
         <v>197</v>
       </c>
@@ -4154,7 +4363,7 @@
         <v>468.45</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
         <v>198</v>
       </c>
@@ -4175,7 +4384,7 @@
         <v>780.75</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
         <v>199</v>
       </c>
@@ -4196,7 +4405,7 @@
         <v>9369</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="13" t="s">
         <v>200</v>
       </c>
@@ -4217,7 +4426,7 @@
         <v>18738</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="13" t="s">
         <v>201</v>
       </c>
@@ -4238,7 +4447,7 @@
         <v>2248.56</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="13" t="s">
         <v>202</v>
       </c>
@@ -4259,7 +4468,7 @@
         <v>187.38</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
         <v>203</v>
       </c>
@@ -4280,7 +4489,7 @@
         <v>218.61</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="13" t="s">
         <v>204</v>
       </c>
@@ -4303,7 +4512,7 @@
         <v>638.57000000000005</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" ht="54" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
         <v>207</v>
       </c>
@@ -4351,7 +4560,7 @@
         <v>163.30000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="126" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="126" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="19" t="s">
         <v>212</v>
       </c>
@@ -4383,1061 +4592,317 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="19" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49">
+        <f>D12</f>
+        <v>979.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.35">
+      <c r="A3" s="46">
+        <v>2</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="49">
+        <f>E2</f>
+        <v>979.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A5" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
+        <v>1</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="47">
+        <v>116.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
+        <v>2</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="47">
+        <v>202.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="46">
+        <v>3</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="47">
+        <v>129.80000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="46">
+        <v>4</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="47">
+        <v>200.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="46">
+        <v>5</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="47">
+        <v>130.30000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="46">
+        <v>6</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="47">
+        <v>200.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="46"/>
+      <c r="B12" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="47">
+        <f>SUM(D6:D11)</f>
+        <v>979.8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:T46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="19" max="19" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="32.109375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B1" s="30" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="2" spans="2:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B2" s="27"/>
-      <c r="C2" s="27">
-        <v>1</v>
-      </c>
-      <c r="D2" s="27">
-        <v>1</v>
-      </c>
-      <c r="E2" s="27">
+    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="102" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49">
+        <f>D8</f>
+        <v>891.64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A4" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="46">
+        <v>1</v>
+      </c>
+      <c r="B5" s="41" t="str">
+        <f>'1.2-Пт'!B6</f>
+        <v>1.094, 1.94а</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="47">
+        <f>'1.2-Пт'!D6</f>
+        <v>294.16000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
         <v>2</v>
       </c>
-      <c r="F2" s="27">
-        <v>2</v>
-      </c>
-      <c r="G2" s="27">
+      <c r="B6" s="41" t="str">
+        <f>'1.2-Пт'!B7</f>
+        <v>2.047, 2.047а, 2.047б</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="47">
+        <f>'1.2-Пт'!D7</f>
+        <v>285.60000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
         <v>3</v>
       </c>
-      <c r="H2" s="27">
-        <v>3</v>
-      </c>
-      <c r="I2" s="27">
-        <v>4</v>
-      </c>
-      <c r="Q2" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="R2" s="55"/>
-    </row>
-    <row r="3" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B3" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="C3" s="27">
-        <v>1</v>
-      </c>
-      <c r="D3" s="27">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E3" s="27">
-        <v>1</v>
-      </c>
-      <c r="F3" s="27">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G3" s="27">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="I3" s="27">
-        <v>3</v>
-      </c>
-      <c r="Q3" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="R3" s="33" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B4" s="28">
-        <v>2</v>
-      </c>
-      <c r="C4" s="27">
-        <v>28.6</v>
-      </c>
-      <c r="D4" s="27">
-        <v>309.5</v>
-      </c>
-      <c r="E4" s="27">
-        <v>44.4</v>
-      </c>
-      <c r="F4" s="27">
-        <v>31.5</v>
-      </c>
-      <c r="G4" s="27">
-        <v>34.4</v>
-      </c>
-      <c r="H4" s="27">
-        <v>10</v>
-      </c>
-      <c r="I4" s="27">
-        <v>62.8</v>
-      </c>
-      <c r="J4">
-        <f>SUM(C4:I4)</f>
-        <v>521.19999999999993</v>
-      </c>
-      <c r="L4" t="s">
-        <v>236</v>
-      </c>
-      <c r="M4">
-        <v>1171.2</v>
-      </c>
-      <c r="Q4" s="34">
-        <v>4001</v>
-      </c>
-      <c r="R4" s="35">
-        <v>68.8</v>
-      </c>
-      <c r="S4" s="31" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B5" s="28">
-        <v>4</v>
-      </c>
-      <c r="C5" s="27">
-        <v>404.1</v>
-      </c>
-      <c r="D5" s="27">
-        <v>501.6</v>
-      </c>
-      <c r="E5" s="27">
-        <v>377</v>
-      </c>
-      <c r="F5" s="27">
-        <v>695.5</v>
-      </c>
-      <c r="G5" s="27">
-        <v>502.3</v>
-      </c>
-      <c r="H5" s="27">
-        <v>528.1</v>
-      </c>
-      <c r="I5" s="27">
-        <v>69.5</v>
-      </c>
-      <c r="J5">
-        <f t="shared" ref="J5:J9" si="0">SUM(C5:I5)</f>
-        <v>3078.1</v>
-      </c>
-      <c r="Q5" s="34">
-        <v>4002</v>
-      </c>
-      <c r="R5" s="35">
-        <v>26.9</v>
-      </c>
-      <c r="S5" s="31" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B6" s="28">
-        <v>5</v>
-      </c>
-      <c r="C6" s="27">
-        <v>418.1</v>
-      </c>
-      <c r="D6" s="27">
-        <v>1554.8</v>
-      </c>
-      <c r="E6" s="27">
-        <v>334.2</v>
-      </c>
-      <c r="F6" s="27">
-        <v>1730.3</v>
-      </c>
-      <c r="G6" s="27">
-        <v>335.1</v>
-      </c>
-      <c r="H6" s="27">
-        <v>2263.1999999999998</v>
-      </c>
-      <c r="I6" s="27">
-        <v>327.60000000000002</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="0"/>
-        <v>6963.3</v>
-      </c>
-      <c r="L6" t="s">
-        <v>231</v>
-      </c>
-      <c r="M6">
-        <v>7010.2</v>
-      </c>
-      <c r="Q6" s="34">
-        <v>4003</v>
-      </c>
-      <c r="R6" s="35">
-        <v>43.9</v>
-      </c>
-      <c r="S6" s="31" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B7" s="28">
-        <v>6</v>
-      </c>
-      <c r="C7" s="27">
-        <v>0</v>
-      </c>
-      <c r="D7" s="27">
-        <v>37.6</v>
-      </c>
-      <c r="E7" s="27">
-        <v>0</v>
-      </c>
-      <c r="F7" s="27">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27">
-        <v>0</v>
-      </c>
-      <c r="I7" s="27">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="0"/>
-        <v>37.6</v>
-      </c>
-      <c r="Q7" s="36">
-        <v>4004</v>
-      </c>
-      <c r="R7" s="37">
-        <v>54.8</v>
-      </c>
-      <c r="S7" s="31" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B8" s="28">
-        <v>7</v>
-      </c>
-      <c r="C8" s="27">
-        <v>15.4</v>
-      </c>
-      <c r="D8" s="27">
-        <v>71.3</v>
-      </c>
-      <c r="E8" s="27">
-        <v>15.5</v>
-      </c>
-      <c r="F8" s="27">
-        <v>23.9</v>
-      </c>
-      <c r="G8" s="27">
-        <v>15.5</v>
-      </c>
-      <c r="H8" s="27">
-        <v>23.9</v>
-      </c>
-      <c r="I8" s="27">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="0"/>
-        <v>165.5</v>
-      </c>
-      <c r="Q8" s="34">
-        <v>4005</v>
-      </c>
-      <c r="R8" s="35">
-        <v>52</v>
-      </c>
-      <c r="S8" s="31" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B9" s="28">
-        <v>8</v>
-      </c>
-      <c r="C9" s="27">
-        <v>44.1</v>
-      </c>
-      <c r="D9" s="27">
-        <v>191.4</v>
-      </c>
-      <c r="E9" s="27">
-        <v>51.1</v>
-      </c>
-      <c r="F9" s="27">
-        <v>200.1</v>
-      </c>
-      <c r="G9" s="27">
-        <v>50.9</v>
-      </c>
-      <c r="H9" s="27">
-        <v>53.6</v>
-      </c>
-      <c r="I9" s="27">
-        <v>46.9</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="0"/>
-        <v>638.1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>250</v>
-      </c>
-      <c r="M9">
-        <v>827.7</v>
-      </c>
-      <c r="Q9" s="34">
-        <v>4006</v>
-      </c>
-      <c r="R9" s="35">
-        <v>56.6</v>
-      </c>
-      <c r="S9" s="31" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q10" s="34">
-        <v>4007</v>
-      </c>
-      <c r="R10" s="35">
-        <v>19.2</v>
-      </c>
-      <c r="S10" s="31" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q11" s="34">
-        <v>4008</v>
-      </c>
-      <c r="R11" s="35">
-        <v>95.5</v>
-      </c>
-      <c r="S11" s="31" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q12" s="34">
-        <v>4009</v>
-      </c>
-      <c r="R12" s="35">
-        <v>30.6</v>
-      </c>
-      <c r="S12" s="31" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q13" s="34">
-        <v>4010</v>
-      </c>
-      <c r="R13" s="35">
-        <v>241.6</v>
-      </c>
-      <c r="S13" s="31" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q14" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="R14" s="35">
-        <v>72.400000000000006</v>
-      </c>
-      <c r="S14" s="31" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q15" s="34">
-        <v>4011</v>
-      </c>
-      <c r="R15" s="35">
-        <v>14</v>
-      </c>
-      <c r="S15" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="Q16" s="34">
-        <v>4012</v>
-      </c>
-      <c r="R16" s="35">
-        <v>4.2</v>
-      </c>
-      <c r="S16" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q17" s="34">
-        <v>4013</v>
-      </c>
-      <c r="R17" s="35">
-        <v>6.7</v>
-      </c>
-      <c r="S17" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B18" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="C18" s="27">
-        <v>18.5</v>
-      </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="I18" s="27">
-        <v>14</v>
-      </c>
-      <c r="Q18" s="34">
-        <v>4014</v>
-      </c>
-      <c r="R18" s="35">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="S18" s="53" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B19" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="C19" s="27">
-        <v>19</v>
-      </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="I19" s="27">
-        <v>4.2</v>
-      </c>
-      <c r="Q19" s="34">
-        <v>4015</v>
-      </c>
-      <c r="R19" s="35">
-        <v>16.2</v>
-      </c>
-      <c r="S19" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B20" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="C20" s="27">
-        <v>7.1</v>
-      </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="I20" s="27">
-        <v>6.7</v>
-      </c>
-      <c r="Q20" s="34">
-        <v>4016</v>
-      </c>
-      <c r="R20" s="35">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="S20" s="31" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="I21" s="27">
-        <v>16.2</v>
-      </c>
-      <c r="Q21" s="34">
-        <v>4017</v>
-      </c>
-      <c r="R21" s="35">
-        <v>4.8</v>
-      </c>
-      <c r="S21" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="I22" s="27">
-        <v>4.8</v>
-      </c>
-      <c r="Q22" s="34">
-        <v>4018</v>
-      </c>
-      <c r="R22" s="35">
-        <v>32</v>
-      </c>
-      <c r="S22" s="31" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="Q23" s="56">
-        <v>855</v>
-      </c>
-      <c r="R23" s="57"/>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B24" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="30" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B25" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="C25" s="40">
-        <v>98.5</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="E25" s="27">
-        <v>130.4</v>
-      </c>
-      <c r="F25" s="27">
-        <v>16</v>
-      </c>
-      <c r="G25" s="27">
-        <v>130.69999999999999</v>
-      </c>
-      <c r="H25" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="I25" s="27">
-        <v>72.400000000000006</v>
-      </c>
-      <c r="K25" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q25" s="39" t="s">
-        <v>238</v>
-      </c>
-      <c r="R25">
-        <v>243.2</v>
-      </c>
-      <c r="S25">
-        <f t="shared" ref="S25:S29" si="1">SUMIF($S$4:$S$22,Q25,$R$4:$R$22)</f>
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <f t="shared" ref="T25:T29" si="2">R25-S25</f>
-        <v>243.2</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B26" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C26" s="27">
-        <v>117.6</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="E26" s="27">
-        <v>200.9</v>
-      </c>
-      <c r="F26" s="27">
-        <v>17</v>
-      </c>
-      <c r="G26" s="27">
-        <v>201.3</v>
-      </c>
-      <c r="H26" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="I26" s="27">
-        <v>241.6</v>
-      </c>
-      <c r="Q26">
-        <v>4</v>
-      </c>
-      <c r="R26">
-        <v>69.5</v>
-      </c>
-      <c r="S26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <f t="shared" si="2"/>
-        <v>69.5</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B27" s="31" t="s">
-        <v>242</v>
-      </c>
-      <c r="C27" s="27">
-        <v>203.1</v>
-      </c>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="27"/>
-      <c r="Q27" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="R27">
-        <v>62.8</v>
-      </c>
-      <c r="S27">
-        <f t="shared" si="1"/>
-        <v>67.5</v>
-      </c>
-      <c r="T27">
-        <f t="shared" si="2"/>
-        <v>-4.7000000000000028</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="Q28" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="R28">
-        <v>69.5</v>
-      </c>
-      <c r="S28">
-        <f t="shared" si="1"/>
-        <v>390.8</v>
-      </c>
-      <c r="T28">
-        <f t="shared" si="2"/>
-        <v>-321.3</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="Q29" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="R29">
-        <v>327.60000000000002</v>
-      </c>
-      <c r="S29">
-        <f t="shared" si="1"/>
-        <v>350.7</v>
-      </c>
-      <c r="T29">
-        <f t="shared" si="2"/>
-        <v>-23.099999999999966</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="Q30" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="R30">
-        <v>46.9</v>
-      </c>
-      <c r="S30">
-        <f>SUMIF($S$4:$S$22,Q30,$R$4:$R$22)</f>
-        <v>45.899999999999991</v>
-      </c>
-      <c r="T30">
-        <f>R30-S30</f>
-        <v>1.0000000000000071</v>
-      </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B35" s="30" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B36" s="27"/>
-      <c r="C36" s="27">
-        <v>1</v>
-      </c>
-      <c r="D36" s="27">
-        <v>1</v>
-      </c>
-      <c r="E36" s="27">
-        <v>2</v>
-      </c>
-      <c r="F36" s="27">
-        <v>2</v>
-      </c>
-      <c r="G36" s="27">
-        <v>3</v>
-      </c>
-      <c r="H36" s="27">
-        <v>3</v>
-      </c>
-      <c r="I36" s="27">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B37" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="C37" s="27">
-        <v>1</v>
-      </c>
-      <c r="D37" s="27">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E37" s="27">
-        <v>1</v>
-      </c>
-      <c r="F37" s="27">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G37" s="27">
-        <v>1</v>
-      </c>
-      <c r="H37" s="27">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="I37" s="27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B38" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="27">
-        <v>121.3</v>
-      </c>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B39" s="50" t="s">
-        <v>238</v>
-      </c>
-      <c r="C39" s="27">
-        <v>319.60000000000002</v>
-      </c>
-      <c r="D39" s="27"/>
-      <c r="E39" s="31">
-        <v>334.2</v>
-      </c>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-      <c r="O39" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="P39">
-        <v>1171.2</v>
-      </c>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B40" s="50">
-        <v>2</v>
-      </c>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27">
-        <v>61.3</v>
-      </c>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="O40" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="P40">
-        <v>7010.2</v>
-      </c>
-    </row>
-    <row r="41" spans="2:16" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B41" s="51">
-        <v>3</v>
-      </c>
-      <c r="C41" s="27">
-        <v>55.3</v>
-      </c>
-      <c r="D41" s="27">
-        <v>309.5</v>
-      </c>
-      <c r="E41" s="27">
-        <v>44.4</v>
-      </c>
-      <c r="F41" s="27">
-        <v>31.5</v>
-      </c>
-      <c r="G41" s="27">
-        <v>34.4</v>
-      </c>
-      <c r="H41" s="27">
-        <v>10</v>
-      </c>
-      <c r="I41" s="27">
-        <v>62.8</v>
-      </c>
-      <c r="J41">
-        <f>SUM(C41:I41)</f>
-        <v>547.9</v>
-      </c>
-      <c r="O41" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="P41">
-        <v>827.7</v>
-      </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B42" s="51">
-        <v>4</v>
-      </c>
-      <c r="C42" s="27">
-        <v>398.8</v>
-      </c>
-      <c r="D42" s="27">
-        <v>501.6</v>
-      </c>
-      <c r="E42" s="27">
-        <v>377</v>
-      </c>
-      <c r="F42" s="27">
-        <v>695.5</v>
-      </c>
-      <c r="G42" s="27">
-        <v>502.3</v>
-      </c>
-      <c r="H42" s="27">
-        <v>528.1</v>
-      </c>
-      <c r="I42" s="27">
-        <v>69.5</v>
-      </c>
-      <c r="J42">
-        <f t="shared" ref="J42:J46" si="3">SUM(C42:I42)</f>
-        <v>3072.8</v>
-      </c>
-      <c r="O42" s="30"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B43" s="51">
-        <v>5</v>
-      </c>
-      <c r="C43" s="27">
-        <v>0</v>
-      </c>
-      <c r="D43" s="27">
-        <v>1554.8</v>
-      </c>
-      <c r="E43" s="27">
-        <v>334.2</v>
-      </c>
-      <c r="F43" s="27">
-        <v>1730.3</v>
-      </c>
-      <c r="G43" s="27">
-        <v>335.1</v>
-      </c>
-      <c r="H43" s="27">
-        <v>2263.1999999999998</v>
-      </c>
-      <c r="I43" s="27">
-        <v>327.60000000000002</v>
-      </c>
-      <c r="J43">
-        <f t="shared" si="3"/>
-        <v>6545.2000000000007</v>
-      </c>
-      <c r="O43" s="30"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B44" s="51">
-        <v>6</v>
-      </c>
-      <c r="C44" s="27">
-        <v>15.4</v>
-      </c>
-      <c r="D44" s="27">
-        <v>37.6</v>
-      </c>
-      <c r="E44" s="27">
-        <v>0</v>
-      </c>
-      <c r="F44" s="27">
-        <v>0</v>
-      </c>
-      <c r="G44" s="27">
-        <v>0</v>
-      </c>
-      <c r="H44" s="27">
-        <v>0</v>
-      </c>
-      <c r="I44" s="27">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <f t="shared" si="3"/>
-        <v>53</v>
-      </c>
-      <c r="O44" s="30"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B45" s="51">
-        <v>7</v>
-      </c>
-      <c r="C45" s="27">
-        <v>0</v>
-      </c>
-      <c r="D45" s="27">
-        <v>71.3</v>
-      </c>
-      <c r="E45" s="27">
-        <v>15.5</v>
-      </c>
-      <c r="F45" s="27">
-        <v>23.9</v>
-      </c>
-      <c r="G45" s="27">
-        <v>15.5</v>
-      </c>
-      <c r="H45" s="27">
-        <v>23.9</v>
-      </c>
-      <c r="I45" s="27">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <f t="shared" si="3"/>
-        <v>150.1</v>
-      </c>
-      <c r="O45" s="30"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B46" s="28">
-        <v>8</v>
-      </c>
-      <c r="C46" s="27">
-        <v>7.1</v>
-      </c>
-      <c r="D46" s="27">
-        <v>191.4</v>
-      </c>
-      <c r="E46" s="27">
-        <v>51.1</v>
-      </c>
-      <c r="F46" s="27">
-        <v>200.1</v>
-      </c>
-      <c r="G46" s="27">
-        <v>50.9</v>
-      </c>
-      <c r="H46" s="27">
-        <v>53.6</v>
-      </c>
-      <c r="I46" s="27">
-        <v>46.9</v>
-      </c>
-      <c r="J46">
-        <f t="shared" si="3"/>
-        <v>601.09999999999991</v>
-      </c>
-      <c r="O46" s="30"/>
+      <c r="B7" s="41" t="str">
+        <f>'1.2-Пт'!B8</f>
+        <v>3.047, 3.047а, 3.047б</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="47">
+        <f>'1.2-Пт'!D8</f>
+        <v>311.88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="46"/>
+      <c r="B8" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="47">
+        <f>SUM(D5:D7)</f>
+        <v>891.64</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="Q23:R23"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -5601,14 +5066,1225 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="B1:T57"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="12" max="12" width="18.77734375" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" customWidth="1"/>
+    <col min="19" max="19" width="12.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="59" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+    </row>
+    <row r="3" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B3" s="30" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B4" s="27"/>
+      <c r="C4" s="27">
+        <v>1</v>
+      </c>
+      <c r="D4" s="27">
+        <v>1</v>
+      </c>
+      <c r="E4" s="27">
+        <v>2</v>
+      </c>
+      <c r="F4" s="27">
+        <v>2</v>
+      </c>
+      <c r="G4" s="27">
+        <v>3</v>
+      </c>
+      <c r="H4" s="27">
+        <v>3</v>
+      </c>
+      <c r="I4" s="27">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="R4" s="56"/>
+    </row>
+    <row r="5" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" s="27">
+        <v>1</v>
+      </c>
+      <c r="D5" s="27">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E5" s="27">
+        <v>1</v>
+      </c>
+      <c r="F5" s="27">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G5" s="27">
+        <v>1</v>
+      </c>
+      <c r="H5" s="27">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I5" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="R5" s="33" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B6" s="28">
+        <v>2</v>
+      </c>
+      <c r="C6" s="27">
+        <v>28.6</v>
+      </c>
+      <c r="D6" s="27">
+        <v>309.5</v>
+      </c>
+      <c r="E6" s="27">
+        <v>44.4</v>
+      </c>
+      <c r="F6" s="27">
+        <v>31.5</v>
+      </c>
+      <c r="G6" s="27">
+        <v>34.4</v>
+      </c>
+      <c r="H6" s="27">
+        <v>10</v>
+      </c>
+      <c r="I6" s="27">
+        <v>62.8</v>
+      </c>
+      <c r="J6">
+        <f>SUM(C6:I6)</f>
+        <v>521.19999999999993</v>
+      </c>
+      <c r="L6" t="s">
+        <v>236</v>
+      </c>
+      <c r="M6">
+        <v>1171.2</v>
+      </c>
+      <c r="Q6" s="34">
+        <v>4001</v>
+      </c>
+      <c r="R6" s="35">
+        <v>68.8</v>
+      </c>
+      <c r="S6" s="31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B7" s="28">
+        <v>4</v>
+      </c>
+      <c r="C7" s="27">
+        <v>404.1</v>
+      </c>
+      <c r="D7" s="27">
+        <v>501.6</v>
+      </c>
+      <c r="E7" s="27">
+        <v>377</v>
+      </c>
+      <c r="F7" s="27">
+        <v>695.5</v>
+      </c>
+      <c r="G7" s="27">
+        <v>502.3</v>
+      </c>
+      <c r="H7" s="27">
+        <v>528.1</v>
+      </c>
+      <c r="I7" s="27">
+        <v>69.5</v>
+      </c>
+      <c r="J7">
+        <f t="shared" ref="J7:J11" si="0">SUM(C7:I7)</f>
+        <v>3078.1</v>
+      </c>
+      <c r="Q7" s="34">
+        <v>4002</v>
+      </c>
+      <c r="R7" s="35">
+        <v>26.9</v>
+      </c>
+      <c r="S7" s="31" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B8" s="28">
+        <v>5</v>
+      </c>
+      <c r="C8" s="27">
+        <v>418.1</v>
+      </c>
+      <c r="D8" s="27">
+        <v>1554.8</v>
+      </c>
+      <c r="E8" s="27">
+        <v>334.2</v>
+      </c>
+      <c r="F8" s="27">
+        <v>1730.3</v>
+      </c>
+      <c r="G8" s="27">
+        <v>335.1</v>
+      </c>
+      <c r="H8" s="27">
+        <v>2263.1999999999998</v>
+      </c>
+      <c r="I8" s="27">
+        <v>327.60000000000002</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>6963.3</v>
+      </c>
+      <c r="L8" t="s">
+        <v>231</v>
+      </c>
+      <c r="M8">
+        <v>7010.2</v>
+      </c>
+      <c r="Q8" s="34">
+        <v>4003</v>
+      </c>
+      <c r="R8" s="35">
+        <v>43.9</v>
+      </c>
+      <c r="S8" s="31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B9" s="28">
+        <v>6</v>
+      </c>
+      <c r="C9" s="27">
+        <v>0</v>
+      </c>
+      <c r="D9" s="27">
+        <v>37.6</v>
+      </c>
+      <c r="E9" s="27">
+        <v>0</v>
+      </c>
+      <c r="F9" s="27">
+        <v>0</v>
+      </c>
+      <c r="G9" s="27">
+        <v>0</v>
+      </c>
+      <c r="H9" s="27">
+        <v>0</v>
+      </c>
+      <c r="I9" s="27">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>37.6</v>
+      </c>
+      <c r="Q9" s="36">
+        <v>4004</v>
+      </c>
+      <c r="R9" s="37">
+        <v>54.8</v>
+      </c>
+      <c r="S9" s="31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B10" s="28">
+        <v>7</v>
+      </c>
+      <c r="C10" s="27">
+        <v>15.4</v>
+      </c>
+      <c r="D10" s="27">
+        <v>71.3</v>
+      </c>
+      <c r="E10" s="27">
+        <v>15.5</v>
+      </c>
+      <c r="F10" s="27">
+        <v>23.9</v>
+      </c>
+      <c r="G10" s="27">
+        <v>15.5</v>
+      </c>
+      <c r="H10" s="27">
+        <v>23.9</v>
+      </c>
+      <c r="I10" s="27">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>165.5</v>
+      </c>
+      <c r="Q10" s="34">
+        <v>4005</v>
+      </c>
+      <c r="R10" s="35">
+        <v>52</v>
+      </c>
+      <c r="S10" s="31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B11" s="28">
+        <v>8</v>
+      </c>
+      <c r="C11" s="27">
+        <v>44.1</v>
+      </c>
+      <c r="D11" s="27">
+        <v>191.4</v>
+      </c>
+      <c r="E11" s="27">
+        <v>51.1</v>
+      </c>
+      <c r="F11" s="27">
+        <v>200.1</v>
+      </c>
+      <c r="G11" s="27">
+        <v>50.9</v>
+      </c>
+      <c r="H11" s="27">
+        <v>53.6</v>
+      </c>
+      <c r="I11" s="27">
+        <v>46.9</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>638.1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>250</v>
+      </c>
+      <c r="M11">
+        <v>827.7</v>
+      </c>
+      <c r="Q11" s="34">
+        <v>4006</v>
+      </c>
+      <c r="R11" s="35">
+        <v>56.6</v>
+      </c>
+      <c r="S11" s="31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="Q12" s="34">
+        <v>4007</v>
+      </c>
+      <c r="R12" s="35">
+        <v>19.2</v>
+      </c>
+      <c r="S12" s="31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q13" s="34">
+        <v>4008</v>
+      </c>
+      <c r="R13" s="35">
+        <v>95.5</v>
+      </c>
+      <c r="S13" s="31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q14" s="34">
+        <v>4009</v>
+      </c>
+      <c r="R14" s="35">
+        <v>30.6</v>
+      </c>
+      <c r="S14" s="31" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q15" s="34">
+        <v>4010</v>
+      </c>
+      <c r="R15" s="35">
+        <v>241.6</v>
+      </c>
+      <c r="S15" s="31" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q16" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="R16" s="35">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="S16" s="31" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q17" s="34">
+        <v>4011</v>
+      </c>
+      <c r="R17" s="35">
+        <v>14</v>
+      </c>
+      <c r="S17" s="30" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q18" s="34">
+        <v>4012</v>
+      </c>
+      <c r="R18" s="35">
+        <v>4.2</v>
+      </c>
+      <c r="S18" s="30" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q19" s="34">
+        <v>4013</v>
+      </c>
+      <c r="R19" s="35">
+        <v>6.7</v>
+      </c>
+      <c r="S19" s="30" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="C20" s="27">
+        <v>18.5</v>
+      </c>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="I20" s="27">
+        <v>14</v>
+      </c>
+      <c r="Q20" s="34">
+        <v>4014</v>
+      </c>
+      <c r="R20" s="35">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="S20" s="53" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="31" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" s="27">
+        <v>19</v>
+      </c>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="I21" s="27">
+        <v>4.2</v>
+      </c>
+      <c r="Q21" s="34">
+        <v>4015</v>
+      </c>
+      <c r="R21" s="35">
+        <v>16.2</v>
+      </c>
+      <c r="S21" s="30" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="C22" s="27">
+        <v>7.1</v>
+      </c>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="I22" s="27">
+        <v>6.7</v>
+      </c>
+      <c r="Q22" s="34">
+        <v>4016</v>
+      </c>
+      <c r="R22" s="35">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="S22" s="31" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="I23" s="27">
+        <v>16.2</v>
+      </c>
+      <c r="Q23" s="34">
+        <v>4017</v>
+      </c>
+      <c r="R23" s="35">
+        <v>4.8</v>
+      </c>
+      <c r="S23" s="30" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="I24" s="27">
+        <v>4.8</v>
+      </c>
+      <c r="Q24" s="34">
+        <v>4018</v>
+      </c>
+      <c r="R24" s="35">
+        <v>32</v>
+      </c>
+      <c r="S24" s="31" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q25" s="57">
+        <v>855</v>
+      </c>
+      <c r="R25" s="58"/>
+    </row>
+    <row r="26" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="30" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="C27" s="40">
+        <v>98.5</v>
+      </c>
+      <c r="D27" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="E27" s="27">
+        <v>130.4</v>
+      </c>
+      <c r="F27" s="27">
+        <v>16</v>
+      </c>
+      <c r="G27" s="27">
+        <v>130.69999999999999</v>
+      </c>
+      <c r="H27" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="I27" s="27">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="K27" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q27" s="39" t="s">
+        <v>238</v>
+      </c>
+      <c r="R27">
+        <v>243.2</v>
+      </c>
+      <c r="S27">
+        <f t="shared" ref="S27:S31" si="1">SUMIF($S$6:$S$24,Q27,$R$6:$R$24)</f>
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <f t="shared" ref="T27:T31" si="2">R27-S27</f>
+        <v>243.2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="C28" s="27">
+        <v>117.6</v>
+      </c>
+      <c r="D28" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="E28" s="27">
+        <v>200.9</v>
+      </c>
+      <c r="F28" s="27">
+        <v>17</v>
+      </c>
+      <c r="G28" s="27">
+        <v>201.3</v>
+      </c>
+      <c r="H28" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="I28" s="27">
+        <v>241.6</v>
+      </c>
+      <c r="Q28">
+        <v>4</v>
+      </c>
+      <c r="R28">
+        <v>69.5</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="2"/>
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="C29" s="27">
+        <v>203.1</v>
+      </c>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="27"/>
+      <c r="Q29" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="R29">
+        <v>62.8</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="1"/>
+        <v>67.5</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="2"/>
+        <v>-4.7000000000000028</v>
+      </c>
+    </row>
+    <row r="30" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q30" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="R30">
+        <v>69.5</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="1"/>
+        <v>390.8</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="2"/>
+        <v>-321.3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q31" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="R31">
+        <v>327.60000000000002</v>
+      </c>
+      <c r="S31">
+        <f t="shared" si="1"/>
+        <v>350.7</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="2"/>
+        <v>-23.099999999999966</v>
+      </c>
+    </row>
+    <row r="32" spans="2:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q32" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="R32">
+        <v>46.9</v>
+      </c>
+      <c r="S32">
+        <f>SUMIF($S$6:$S$24,Q32,$R$6:$R$24)</f>
+        <v>45.899999999999991</v>
+      </c>
+      <c r="T32">
+        <f>R32-S32</f>
+        <v>1.0000000000000071</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="2:15" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="2:15" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B37" s="30" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B38" s="27"/>
+      <c r="C38" s="27">
+        <v>1</v>
+      </c>
+      <c r="D38" s="27">
+        <v>1</v>
+      </c>
+      <c r="E38" s="27">
+        <v>2</v>
+      </c>
+      <c r="F38" s="27">
+        <v>2</v>
+      </c>
+      <c r="G38" s="27">
+        <v>3</v>
+      </c>
+      <c r="H38" s="27">
+        <v>3</v>
+      </c>
+      <c r="I38" s="27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B39" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="C39" s="31">
+        <v>1</v>
+      </c>
+      <c r="D39" s="31">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E39" s="31">
+        <v>1</v>
+      </c>
+      <c r="F39" s="31">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G39" s="31">
+        <v>1</v>
+      </c>
+      <c r="H39" s="31">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I39" s="31">
+        <v>3</v>
+      </c>
+      <c r="J39" s="30" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B40" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="31">
+        <v>121.3</v>
+      </c>
+      <c r="D40" s="31">
+        <v>689.9</v>
+      </c>
+      <c r="E40" s="31">
+        <v>31.4</v>
+      </c>
+      <c r="F40" s="31">
+        <v>153</v>
+      </c>
+      <c r="G40" s="31">
+        <v>28.3</v>
+      </c>
+      <c r="H40" s="31">
+        <v>760.7</v>
+      </c>
+      <c r="I40" s="31">
+        <v>57.8</v>
+      </c>
+      <c r="J40" s="54">
+        <f>SUM(C40:I40)</f>
+        <v>1842.3999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B41" s="50" t="s">
+        <v>238</v>
+      </c>
+      <c r="C41" s="31">
+        <v>319.60000000000002</v>
+      </c>
+      <c r="D41" s="31">
+        <v>863.6</v>
+      </c>
+      <c r="E41" s="31">
+        <v>334.2</v>
+      </c>
+      <c r="F41" s="31">
+        <v>798.9</v>
+      </c>
+      <c r="G41" s="31">
+        <v>335.1</v>
+      </c>
+      <c r="H41" s="31">
+        <v>741</v>
+      </c>
+      <c r="I41" s="31">
+        <v>556.9</v>
+      </c>
+      <c r="J41" s="54">
+        <f t="shared" ref="J41:J51" si="3">SUM(C41:I41)</f>
+        <v>3949.3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B42" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="C42" s="31">
+        <v>0</v>
+      </c>
+      <c r="D42" s="31">
+        <v>0</v>
+      </c>
+      <c r="E42" s="31">
+        <v>0</v>
+      </c>
+      <c r="F42" s="31">
+        <v>501.8</v>
+      </c>
+      <c r="G42" s="31">
+        <v>0</v>
+      </c>
+      <c r="H42" s="31">
+        <v>0</v>
+      </c>
+      <c r="I42" s="31">
+        <v>0</v>
+      </c>
+      <c r="J42" s="54">
+        <f t="shared" si="3"/>
+        <v>501.8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B43" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="C43" s="31">
+        <v>0</v>
+      </c>
+      <c r="D43" s="31">
+        <v>98.2</v>
+      </c>
+      <c r="E43" s="31">
+        <v>0</v>
+      </c>
+      <c r="F43" s="31">
+        <v>486.3</v>
+      </c>
+      <c r="G43" s="31">
+        <v>0</v>
+      </c>
+      <c r="H43" s="31">
+        <v>1232</v>
+      </c>
+      <c r="I43" s="31">
+        <v>0</v>
+      </c>
+      <c r="J43" s="54">
+        <f t="shared" si="3"/>
+        <v>1816.5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B44" s="50" t="s">
+        <v>259</v>
+      </c>
+      <c r="C44" s="31">
+        <v>0</v>
+      </c>
+      <c r="D44" s="31">
+        <v>0</v>
+      </c>
+      <c r="E44" s="31">
+        <v>0</v>
+      </c>
+      <c r="F44" s="31">
+        <v>186.1</v>
+      </c>
+      <c r="G44" s="31">
+        <v>0</v>
+      </c>
+      <c r="H44" s="31">
+        <v>0</v>
+      </c>
+      <c r="I44" s="31">
+        <v>0</v>
+      </c>
+      <c r="J44" s="54">
+        <f t="shared" si="3"/>
+        <v>186.1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B45" s="50">
+        <v>2</v>
+      </c>
+      <c r="C45" s="31">
+        <v>0</v>
+      </c>
+      <c r="D45" s="31">
+        <v>61.3</v>
+      </c>
+      <c r="E45" s="31">
+        <v>0</v>
+      </c>
+      <c r="F45" s="31">
+        <v>0</v>
+      </c>
+      <c r="G45" s="31">
+        <v>0</v>
+      </c>
+      <c r="H45" s="31">
+        <v>0</v>
+      </c>
+      <c r="I45" s="31">
+        <v>0</v>
+      </c>
+      <c r="J45" s="54">
+        <f t="shared" si="3"/>
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B46" s="51">
+        <v>3</v>
+      </c>
+      <c r="C46" s="31">
+        <v>55.3</v>
+      </c>
+      <c r="D46" s="31">
+        <v>245.3</v>
+      </c>
+      <c r="E46" s="31">
+        <v>57.2</v>
+      </c>
+      <c r="F46" s="31">
+        <v>222.2</v>
+      </c>
+      <c r="G46" s="31">
+        <v>57</v>
+      </c>
+      <c r="H46" s="31">
+        <v>63.7</v>
+      </c>
+      <c r="I46" s="31">
+        <v>51.9</v>
+      </c>
+      <c r="J46" s="54">
+        <f t="shared" si="3"/>
+        <v>752.6</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B47" s="51">
+        <v>4</v>
+      </c>
+      <c r="C47" s="31">
+        <v>398.8</v>
+      </c>
+      <c r="D47" s="31">
+        <v>321.89999999999998</v>
+      </c>
+      <c r="E47" s="31">
+        <v>377</v>
+      </c>
+      <c r="F47" s="31">
+        <v>185.8</v>
+      </c>
+      <c r="G47" s="31">
+        <v>570.9</v>
+      </c>
+      <c r="H47" s="31">
+        <v>141.6</v>
+      </c>
+      <c r="I47" s="31">
+        <v>69.5</v>
+      </c>
+      <c r="J47" s="54">
+        <f t="shared" si="3"/>
+        <v>2065.5</v>
+      </c>
+      <c r="O47" s="30"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B48" s="51">
+        <v>5</v>
+      </c>
+      <c r="C48" s="31">
+        <v>0</v>
+      </c>
+      <c r="D48" s="31">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E48" s="31">
+        <v>0</v>
+      </c>
+      <c r="F48" s="31">
+        <v>0</v>
+      </c>
+      <c r="G48" s="31">
+        <v>0</v>
+      </c>
+      <c r="H48" s="31">
+        <v>0</v>
+      </c>
+      <c r="I48" s="31">
+        <v>0</v>
+      </c>
+      <c r="J48" s="54">
+        <f t="shared" si="3"/>
+        <v>39.299999999999997</v>
+      </c>
+      <c r="O48" s="30"/>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B49" s="51">
+        <v>6</v>
+      </c>
+      <c r="C49" s="31">
+        <v>15.4</v>
+      </c>
+      <c r="D49" s="31">
+        <v>23.6</v>
+      </c>
+      <c r="E49" s="31">
+        <v>15.5</v>
+      </c>
+      <c r="F49" s="31">
+        <v>23.9</v>
+      </c>
+      <c r="G49" s="31">
+        <v>15.5</v>
+      </c>
+      <c r="H49" s="31">
+        <v>23.9</v>
+      </c>
+      <c r="I49" s="31">
+        <v>10.8</v>
+      </c>
+      <c r="J49" s="54">
+        <f t="shared" si="3"/>
+        <v>128.60000000000002</v>
+      </c>
+      <c r="O49" s="30"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B50" s="51">
+        <v>7</v>
+      </c>
+      <c r="C50" s="31">
+        <v>0</v>
+      </c>
+      <c r="D50" s="31">
+        <v>367.8</v>
+      </c>
+      <c r="E50" s="31">
+        <v>0</v>
+      </c>
+      <c r="F50" s="31">
+        <v>0</v>
+      </c>
+      <c r="G50" s="31">
+        <v>0</v>
+      </c>
+      <c r="H50" s="31">
+        <v>12.4</v>
+      </c>
+      <c r="I50" s="31">
+        <v>0</v>
+      </c>
+      <c r="J50" s="54">
+        <f t="shared" si="3"/>
+        <v>380.2</v>
+      </c>
+      <c r="O50" s="30"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B51" s="28">
+        <v>8</v>
+      </c>
+      <c r="C51" s="31">
+        <v>7.1</v>
+      </c>
+      <c r="D51" s="31">
+        <v>6.5</v>
+      </c>
+      <c r="E51" s="31">
+        <v>0</v>
+      </c>
+      <c r="F51" s="31">
+        <v>0</v>
+      </c>
+      <c r="G51" s="31">
+        <v>0</v>
+      </c>
+      <c r="H51" s="31">
+        <v>0</v>
+      </c>
+      <c r="I51" s="31">
+        <v>0</v>
+      </c>
+      <c r="J51" s="54">
+        <f t="shared" si="3"/>
+        <v>13.6</v>
+      </c>
+      <c r="O51" s="30"/>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="L55" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="M55">
+        <v>1171.2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="L56" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="M56">
+        <v>7010.2</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L57" s="52" t="s">
+        <v>250</v>
+      </c>
+      <c r="M57">
+        <v>827.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="B1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
     <col min="2" max="2" width="28.77734375" style="48" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="18.77734375" style="48" customWidth="1"/>
     <col min="4" max="4" width="19" style="48" customWidth="1"/>
     <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="48"/>
@@ -5631,41 +6307,48 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="58.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="46">
         <v>1</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="D2" s="41" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="49">
-        <f>D12</f>
-        <v>979.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.35">
+        <f>D9</f>
+        <v>128.68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="58.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="46">
         <v>2</v>
       </c>
-      <c r="B3" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>256</v>
+      <c r="B3" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>275</v>
       </c>
       <c r="D3" s="41" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="49">
-        <f>E2</f>
-        <v>979.8</v>
-      </c>
+        <f>D13</f>
+        <v>15.43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="62"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
     </row>
     <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="41" t="s">
@@ -5680,102 +6363,733 @@
       <c r="D5" s="41" t="s">
         <v>7</v>
       </c>
+      <c r="E5" s="61"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="46">
         <v>1</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="C6" s="41" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="47">
-        <v>116.4</v>
-      </c>
+        <v>15.32</v>
+      </c>
+      <c r="E6" s="61"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="46">
         <v>2</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C7" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="47">
-        <v>202.5</v>
-      </c>
+      <c r="D7" s="49">
+        <v>97.9</v>
+      </c>
+      <c r="E7" s="61"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="46">
         <v>3</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="47">
-        <v>129.80000000000001</v>
-      </c>
+        <v>15.46</v>
+      </c>
+      <c r="E8" s="61"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="46">
+      <c r="A9" s="46"/>
+      <c r="B9" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="47">
+        <f>SUM(D6:D8)</f>
+        <v>128.68</v>
+      </c>
+      <c r="E9" s="61"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="62"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+    </row>
+    <row r="11" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A11" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="41" t="s">
-        <v>244</v>
-      </c>
+      <c r="D11" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="61"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="46">
+        <v>3</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>266</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="47">
+        <v>15.43</v>
+      </c>
+      <c r="E12" s="61"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="46"/>
+      <c r="B13" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="47">
+        <f>SUM(D12:D12)</f>
+        <v>15.43</v>
+      </c>
+      <c r="E13" s="61"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="E5:E9"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="E11:E13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="19" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49">
+        <f>E9</f>
+        <v>46.21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="46">
+        <v>2</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="49">
+        <f>E2</f>
+        <v>46.21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+    </row>
+    <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A5" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
+        <v>1</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="49">
+        <v>15.32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
+        <v>2</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="49">
+        <v>15.46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="46">
+        <v>3</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>266</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="49">
+        <v>15.43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="46"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="47">
-        <v>200.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="46">
-        <v>5</v>
-      </c>
-      <c r="B10" s="41" t="s">
-        <v>245</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="47">
-        <v>130.30000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="46">
-        <v>6</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="47">
-        <v>200.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="46"/>
-      <c r="B12" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="C12" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="47">
-        <f>SUM(D6:D11)</f>
-        <v>979.8</v>
+      <c r="D9" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="47">
+        <f>SUM(E6:E8)</f>
+        <v>46.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:E4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="19" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49">
+        <f>E9</f>
+        <v>285.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="46">
+        <v>2</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>273</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="49">
+        <f>E2</f>
+        <v>285.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+    </row>
+    <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A5" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
+        <v>1</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="49">
+        <v>97.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
+        <v>2</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="49">
+        <v>162.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="46">
+        <v>3</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="49">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="46"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="47">
+        <f>SUM(E6:E8)</f>
+        <v>285.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:E4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" style="48" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" style="48" customWidth="1"/>
+    <col min="4" max="4" width="25.77734375" style="48" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" style="48" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" style="48" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="36" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="64" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="65"/>
+      <c r="D1" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="76.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="67"/>
+      <c r="D2" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="E2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="49">
+        <f>E8</f>
+        <v>285.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="62"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+    </row>
+    <row r="4" spans="1:6" ht="36" x14ac:dyDescent="0.35">
+      <c r="A4" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="68"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="46">
+        <v>1</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="49">
+        <v>97.9</v>
+      </c>
+      <c r="F5" s="68"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
+        <v>2</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="49">
+        <v>162.9</v>
+      </c>
+      <c r="F6" s="68"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
+        <v>3</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="49">
+        <v>24.4</v>
+      </c>
+      <c r="F7" s="68"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="46"/>
+      <c r="B8" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="47">
+        <f>SUM(E5:E7)</f>
+        <v>285.2</v>
+      </c>
+      <c r="F8" s="68"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" style="48" customWidth="1"/>
+    <col min="4" max="4" width="19" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="108" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49">
+        <f>D8</f>
+        <v>891.64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A4" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="46">
+        <v>1</v>
+      </c>
+      <c r="B5" s="41" t="str">
+        <f>'1.2-Пт'!B6</f>
+        <v>1.094, 1.94а</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="47">
+        <f>'1.2-Пт'!D6</f>
+        <v>294.16000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
+        <v>2</v>
+      </c>
+      <c r="B6" s="41" t="str">
+        <f>'1.2-Пт'!B7</f>
+        <v>2.047, 2.047а, 2.047б</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="47">
+        <f>'1.2-Пт'!D7</f>
+        <v>285.60000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
+        <v>3</v>
+      </c>
+      <c r="B7" s="41" t="str">
+        <f>'1.2-Пт'!B8</f>
+        <v>3.047, 3.047а, 3.047б</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="47">
+        <f>'1.2-Пт'!D8</f>
+        <v>311.88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="46"/>
+      <c r="B8" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="47">
+        <f>SUM(D5:D7)</f>
+        <v>891.64</v>
       </c>
     </row>
   </sheetData>
@@ -5783,7 +7097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -5947,135 +7261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
-    <col min="2" max="2" width="32.109375" style="48" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" style="48" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" style="48" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="48"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="41" t="s">
-        <v>240</v>
-      </c>
-      <c r="C1" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="D1" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="102" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46">
-        <v>1</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>251</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="49">
-        <f>D8</f>
-        <v>891.64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A4" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="46">
-        <v>1</v>
-      </c>
-      <c r="B5" s="41" t="str">
-        <f>'1.2-Пт'!B6</f>
-        <v>1.094, 1.94а</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="47">
-        <f>'1.2-Пт'!D6</f>
-        <v>294.16000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="46">
-        <v>2</v>
-      </c>
-      <c r="B6" s="41" t="str">
-        <f>'1.2-Пт'!B7</f>
-        <v>2.047, 2.047а, 2.047б</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="47">
-        <f>'1.2-Пт'!D7</f>
-        <v>285.60000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="46">
-        <v>3</v>
-      </c>
-      <c r="B7" s="41" t="str">
-        <f>'1.2-Пт'!B8</f>
-        <v>3.047, 3.047а, 3.047б</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="47">
-        <f>'1.2-Пт'!D8</f>
-        <v>311.88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="46"/>
-      <c r="B8" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="47">
-        <f>SUM(D5:D7)</f>
-        <v>891.64</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -6213,132 +7399,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
-    <col min="2" max="2" width="28.77734375" style="48" customWidth="1"/>
-    <col min="3" max="3" width="38.6640625" style="48" customWidth="1"/>
-    <col min="4" max="4" width="19" style="48" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="48"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="41" t="s">
-        <v>240</v>
-      </c>
-      <c r="C1" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="D1" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="108" x14ac:dyDescent="0.35">
-      <c r="A2" s="46">
-        <v>1</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="49">
-        <f>D8</f>
-        <v>891.64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A4" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="46">
-        <v>1</v>
-      </c>
-      <c r="B5" s="41" t="str">
-        <f>'1.2-Пт'!B6</f>
-        <v>1.094, 1.94а</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="47">
-        <f>'1.2-Пт'!D6</f>
-        <v>294.16000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="46">
-        <v>2</v>
-      </c>
-      <c r="B6" s="41" t="str">
-        <f>'1.2-Пт'!B7</f>
-        <v>2.047, 2.047а, 2.047б</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="47">
-        <f>'1.2-Пт'!D7</f>
-        <v>285.60000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="46">
-        <v>3</v>
-      </c>
-      <c r="B7" s="41" t="str">
-        <f>'1.2-Пт'!B8</f>
-        <v>3.047, 3.047а, 3.047б</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="47">
-        <f>'1.2-Пт'!D8</f>
-        <v>311.88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="46"/>
-      <c r="B8" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="47">
-        <f>SUM(D5:D7)</f>
-        <v>891.64</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/school_nagatinsky/ceilling/ceilling-n.xlsx
+++ b/school_nagatinsky/ceilling/ceilling-n.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12216" windowHeight="5784" tabRatio="786" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12216" windowHeight="5784" tabRatio="786" firstSheet="10" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="КП" sheetId="2" r:id="rId1"/>
@@ -26,20 +26,21 @@
     <sheet name="2.3в3" sheetId="15" r:id="rId12"/>
     <sheet name="2.2-Пт" sheetId="10" r:id="rId13"/>
     <sheet name="2.1-Пт" sheetId="6" r:id="rId14"/>
-    <sheet name="1.8Шп4в" sheetId="32" r:id="rId15"/>
-    <sheet name="1.7Шп4вНЗ" sheetId="28" r:id="rId16"/>
-    <sheet name="1.6Шп4в" sheetId="26" r:id="rId17"/>
-    <sheet name="1.5Шп3.1в" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet name="1.4ШпЧНП7_3вып" sheetId="14" state="hidden" r:id="rId19"/>
-    <sheet name="1.3ШпЧНП5_3вып" sheetId="13" state="hidden" r:id="rId20"/>
-    <sheet name="1.2-Пт" sheetId="9" state="hidden" r:id="rId21"/>
-    <sheet name="1.1-Пт" sheetId="3" state="hidden" r:id="rId22"/>
-    <sheet name="0.7Шт4вНЗ" sheetId="27" r:id="rId23"/>
-    <sheet name="0.6Шт4в" sheetId="25" r:id="rId24"/>
-    <sheet name="0.4Шт3.1в" sheetId="16" state="hidden" r:id="rId25"/>
-    <sheet name="0.3-Шт3вып" sheetId="12" state="hidden" r:id="rId26"/>
-    <sheet name="0.2-Шт" sheetId="11" state="hidden" r:id="rId27"/>
-    <sheet name="0.1-Шт" sheetId="8" state="hidden" r:id="rId28"/>
+    <sheet name="1.9Шп4в" sheetId="34" r:id="rId15"/>
+    <sheet name="1.8Шп4в" sheetId="32" r:id="rId16"/>
+    <sheet name="1.7Шп4вНЗ" sheetId="28" r:id="rId17"/>
+    <sheet name="1.6Шп4в" sheetId="26" r:id="rId18"/>
+    <sheet name="1.5Шп3.1в" sheetId="18" state="hidden" r:id="rId19"/>
+    <sheet name="1.4ШпЧНП7_3вып" sheetId="14" state="hidden" r:id="rId20"/>
+    <sheet name="1.3ШпЧНП5_3вып" sheetId="13" state="hidden" r:id="rId21"/>
+    <sheet name="1.2-Пт" sheetId="9" state="hidden" r:id="rId22"/>
+    <sheet name="1.1-Пт" sheetId="3" state="hidden" r:id="rId23"/>
+    <sheet name="0.7Шт4вНЗ" sheetId="27" r:id="rId24"/>
+    <sheet name="0.6Шт4в" sheetId="25" r:id="rId25"/>
+    <sheet name="0.4Шт3.1в" sheetId="16" state="hidden" r:id="rId26"/>
+    <sheet name="0.3-Шт3вып" sheetId="12" state="hidden" r:id="rId27"/>
+    <sheet name="0.2-Шт" sheetId="11" state="hidden" r:id="rId28"/>
+    <sheet name="0.1-Шт" sheetId="8" state="hidden" r:id="rId29"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="459">
   <si>
     <t>Номер п/п</t>
   </si>
@@ -4398,6 +4399,9 @@
   </si>
   <si>
     <t>1.071</t>
+  </si>
+  <si>
+    <t>0.005</t>
   </si>
 </sst>
 </file>
@@ -5007,7 +5011,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5418,6 +5422,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5516,7 +5526,292 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="106">
+  <dxfs count="116">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="#,##0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -8493,16 +8788,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A1:I111" totalsRowShown="0" headerRowDxfId="105" tableBorderDxfId="104">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A1:I111" totalsRowShown="0" headerRowDxfId="115" tableBorderDxfId="114">
   <autoFilter ref="A1:I111"/>
   <tableColumns count="9">
-    <tableColumn id="1" name="Номер п/п" dataDxfId="103"/>
-    <tableColumn id="2" name="Код узла ИСР" dataDxfId="102"/>
+    <tableColumn id="1" name="Номер п/п" dataDxfId="113"/>
+    <tableColumn id="2" name="Код узла ИСР" dataDxfId="112"/>
     <tableColumn id="3" name="Наименование затрат"/>
-    <tableColumn id="4" name="Комментарий по ИСР" dataDxfId="101"/>
-    <tableColumn id="5" name="Описание" dataDxfId="100"/>
-    <tableColumn id="6" name="Ед. изм." dataDxfId="99"/>
-    <tableColumn id="7" name="Коэф.расхода" dataDxfId="98"/>
+    <tableColumn id="4" name="Комментарий по ИСР" dataDxfId="111"/>
+    <tableColumn id="5" name="Описание" dataDxfId="110"/>
+    <tableColumn id="6" name="Ед. изм." dataDxfId="109"/>
+    <tableColumn id="7" name="Коэф.расхода" dataDxfId="108"/>
     <tableColumn id="8" name="Кол-во БО"/>
     <tableColumn id="9" name="Общее кол-во"/>
   </tableColumns>
@@ -8511,137 +8806,14 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица35" displayName="Таблица35" ref="A6:E25" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14">
-  <autoFilter ref="A6:E25"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Номер п/п" dataDxfId="13"/>
-    <tableColumn id="2" name="Пом" dataDxfId="12"/>
-    <tableColumn id="3" name="Секция" dataDxfId="11"/>
-    <tableColumn id="4" name="Тип" dataDxfId="10"/>
-    <tableColumn id="5" name="Общее кол-во,_x000a_м2." dataDxfId="9"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="A4:E39" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5">
-  <autoFilter ref="A4:E39"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Номер п/п" dataDxfId="4"/>
-    <tableColumn id="2" name="Пом" dataDxfId="3"/>
-    <tableColumn id="3" name="Секция" dataDxfId="2"/>
-    <tableColumn id="4" name="Тип" dataDxfId="1"/>
-    <tableColumn id="5" name="Общее кол-во,_x000a_м2." dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица13" displayName="Таблица13" ref="A1:E235" totalsRowCount="1" headerRowBorderDxfId="97" tableBorderDxfId="96" totalsRowBorderDxfId="95">
-  <autoFilter ref="A1:E234">
-    <filterColumn colId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Таблица6" displayName="Таблица6" ref="A9:E49" totalsRowShown="0" headerRowDxfId="37" dataDxfId="35" headerRowBorderDxfId="36" tableBorderDxfId="34" totalsRowBorderDxfId="33">
+  <autoFilter ref="A9:E49">
+    <filterColumn colId="3">
       <filters>
-        <filter val="ЧНП-4"/>
+        <filter val="ЧНП-7"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <tableColumns count="5">
-    <tableColumn id="1" name="№ помеще ния" dataDxfId="94" totalsRowDxfId="93"/>
-    <tableColumn id="2" name="Марка" dataDxfId="92" totalsRowDxfId="91"/>
-    <tableColumn id="3" name="Состав  отделки" dataDxfId="90" totalsRowDxfId="89"/>
-    <tableColumn id="4" name="Площадь, м2" totalsRowFunction="custom" dataDxfId="88" totalsRowDxfId="87">
-      <totalsRowFormula>SUM(Таблица13[Площадь, м2])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="5" name="Примечание" dataDxfId="86" totalsRowDxfId="85"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Таблица58" displayName="Таблица58" ref="A4:E18" totalsRowShown="0" headerRowDxfId="84" dataDxfId="82" headerRowBorderDxfId="83" tableBorderDxfId="81" totalsRowBorderDxfId="80">
-  <autoFilter ref="A4:E18"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Номер п/п" dataDxfId="79"/>
-    <tableColumn id="2" name="Пом" dataDxfId="78"/>
-    <tableColumn id="3" name="Секция" dataDxfId="77"/>
-    <tableColumn id="4" name="Тип" dataDxfId="76"/>
-    <tableColumn id="5" name="Общее кол-во" dataDxfId="75"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Таблица391012" displayName="Таблица391012" ref="A4:E19" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
-  <autoFilter ref="A4:E19"/>
-  <sortState ref="A5:E57">
-    <sortCondition ref="A10:A63"/>
-  </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Номер п/п" dataDxfId="70"/>
-    <tableColumn id="2" name="Пом" dataDxfId="69"/>
-    <tableColumn id="3" name="Секция" dataDxfId="68"/>
-    <tableColumn id="4" name="Тип" dataDxfId="67"/>
-    <tableColumn id="5" name="Общее кол-во,_x000a_м2." dataDxfId="66"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Таблица3910" displayName="Таблица3910" ref="A4:E18" totalsRowShown="0" headerRowDxfId="65" dataDxfId="63" headerRowBorderDxfId="64" tableBorderDxfId="62">
-  <autoFilter ref="A4:E18"/>
-  <sortState ref="A10:E62">
-    <sortCondition ref="A10:A63"/>
-  </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Номер п/п" dataDxfId="61"/>
-    <tableColumn id="2" name="Пом" dataDxfId="60"/>
-    <tableColumn id="3" name="Секция" dataDxfId="59"/>
-    <tableColumn id="4" name="Тип" dataDxfId="58"/>
-    <tableColumn id="5" name="Общее кол-во,_x000a_м2." dataDxfId="57"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Таблица39" displayName="Таблица39" ref="A8:E47" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="53">
-  <autoFilter ref="A8:E47"/>
-  <sortState ref="A11:E63">
-    <sortCondition ref="A10:A63"/>
-  </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Номер п/п" dataDxfId="52"/>
-    <tableColumn id="2" name="Пом" dataDxfId="51"/>
-    <tableColumn id="3" name="Секция" dataDxfId="50"/>
-    <tableColumn id="4" name="Тип" dataDxfId="49"/>
-    <tableColumn id="5" name="Общее кол-во,_x000a_м2." dataDxfId="48"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Таблица611" displayName="Таблица611" ref="A5:E7" totalsRowShown="0" headerRowDxfId="47" dataDxfId="45" headerRowBorderDxfId="46" tableBorderDxfId="44" totalsRowBorderDxfId="43">
-  <autoFilter ref="A5:E7"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Номер п/п" dataDxfId="42"/>
-    <tableColumn id="2" name="Пом" dataDxfId="41"/>
-    <tableColumn id="3" name="Секция" dataDxfId="40"/>
-    <tableColumn id="4" name="Тип" dataDxfId="39"/>
-    <tableColumn id="5" name="Общее кол-во" dataDxfId="38"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Таблица5" displayName="Таблица5" ref="A5:E19" totalsRowShown="0" headerRowDxfId="37" dataDxfId="35" headerRowBorderDxfId="36" tableBorderDxfId="34" totalsRowBorderDxfId="33">
-  <autoFilter ref="A5:E19"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Номер п/п" dataDxfId="32"/>
     <tableColumn id="2" name="Пом" dataDxfId="31"/>
@@ -8653,21 +8825,158 @@
 </table>
 </file>
 
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Таблица6" displayName="Таблица6" ref="A9:E49" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
-  <autoFilter ref="A9:E49">
-    <filterColumn colId="3">
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица35" displayName="Таблица35" ref="A6:E25" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24">
+  <autoFilter ref="A6:E25"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Номер п/п" dataDxfId="23"/>
+    <tableColumn id="2" name="Пом" dataDxfId="22"/>
+    <tableColumn id="3" name="Секция" dataDxfId="21"/>
+    <tableColumn id="4" name="Тип" dataDxfId="20"/>
+    <tableColumn id="5" name="Общее кол-во,_x000a_м2." dataDxfId="19"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="A4:E39" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15">
+  <autoFilter ref="A4:E39"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Номер п/п" dataDxfId="14"/>
+    <tableColumn id="2" name="Пом" dataDxfId="13"/>
+    <tableColumn id="3" name="Секция" dataDxfId="12"/>
+    <tableColumn id="4" name="Тип" dataDxfId="11"/>
+    <tableColumn id="5" name="Общее кол-во,_x000a_м2." dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица13" displayName="Таблица13" ref="A1:E235" totalsRowCount="1" headerRowBorderDxfId="107" tableBorderDxfId="106" totalsRowBorderDxfId="105">
+  <autoFilter ref="A1:E234">
+    <filterColumn colId="1">
       <filters>
-        <filter val="ЧНП-7"/>
+        <filter val="ЧНП-4"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" name="Номер п/п" dataDxfId="22"/>
-    <tableColumn id="2" name="Пом" dataDxfId="21"/>
-    <tableColumn id="3" name="Секция" dataDxfId="20"/>
-    <tableColumn id="4" name="Тип" dataDxfId="19"/>
-    <tableColumn id="5" name="Общее кол-во" dataDxfId="18"/>
+    <tableColumn id="1" name="№ помеще ния" dataDxfId="104" totalsRowDxfId="103"/>
+    <tableColumn id="2" name="Марка" dataDxfId="102" totalsRowDxfId="101"/>
+    <tableColumn id="3" name="Состав  отделки" dataDxfId="100" totalsRowDxfId="99"/>
+    <tableColumn id="4" name="Площадь, м2" totalsRowFunction="custom" dataDxfId="98" totalsRowDxfId="97">
+      <totalsRowFormula>SUM(Таблица13[Площадь, м2])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" name="Примечание" dataDxfId="96" totalsRowDxfId="95"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Таблица58" displayName="Таблица58" ref="A4:E18" totalsRowShown="0" headerRowDxfId="94" dataDxfId="92" headerRowBorderDxfId="93" tableBorderDxfId="91" totalsRowBorderDxfId="90">
+  <autoFilter ref="A4:E18"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Номер п/п" dataDxfId="89"/>
+    <tableColumn id="2" name="Пом" dataDxfId="88"/>
+    <tableColumn id="3" name="Секция" dataDxfId="87"/>
+    <tableColumn id="4" name="Тип" dataDxfId="86"/>
+    <tableColumn id="5" name="Общее кол-во" dataDxfId="85"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Таблица391012" displayName="Таблица391012" ref="A4:E19" totalsRowShown="0" headerRowDxfId="84" dataDxfId="82" headerRowBorderDxfId="83" tableBorderDxfId="81">
+  <autoFilter ref="A4:E19"/>
+  <sortState ref="A5:E57">
+    <sortCondition ref="A10:A63"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Номер п/п" dataDxfId="80"/>
+    <tableColumn id="2" name="Пом" dataDxfId="79"/>
+    <tableColumn id="3" name="Секция" dataDxfId="78"/>
+    <tableColumn id="4" name="Тип" dataDxfId="77"/>
+    <tableColumn id="5" name="Общее кол-во,_x000a_м2." dataDxfId="76"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Таблица3910" displayName="Таблица3910" ref="A4:E18" totalsRowShown="0" headerRowDxfId="75" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72">
+  <autoFilter ref="A4:E18"/>
+  <sortState ref="A10:E62">
+    <sortCondition ref="A10:A63"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Номер п/п" dataDxfId="71"/>
+    <tableColumn id="2" name="Пом" dataDxfId="70"/>
+    <tableColumn id="3" name="Секция" dataDxfId="69"/>
+    <tableColumn id="4" name="Тип" dataDxfId="68"/>
+    <tableColumn id="5" name="Общее кол-во,_x000a_м2." dataDxfId="67"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Таблица39" displayName="Таблица39" ref="A8:E47" totalsRowShown="0" headerRowDxfId="66" dataDxfId="64" headerRowBorderDxfId="65" tableBorderDxfId="63">
+  <autoFilter ref="A8:E47"/>
+  <sortState ref="A11:E63">
+    <sortCondition ref="A10:A63"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Номер п/п" dataDxfId="62"/>
+    <tableColumn id="2" name="Пом" dataDxfId="61"/>
+    <tableColumn id="3" name="Секция" dataDxfId="60"/>
+    <tableColumn id="4" name="Тип" dataDxfId="59"/>
+    <tableColumn id="5" name="Общее кол-во,_x000a_м2." dataDxfId="58"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Таблица61113" displayName="Таблица61113" ref="A5:E6" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+  <autoFilter ref="A5:E6"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Номер п/п" dataDxfId="4"/>
+    <tableColumn id="2" name="Пом" dataDxfId="3"/>
+    <tableColumn id="3" name="Секция" dataDxfId="2"/>
+    <tableColumn id="4" name="Тип" dataDxfId="1"/>
+    <tableColumn id="5" name="Общее кол-во" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Таблица611" displayName="Таблица611" ref="A5:E7" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" tableBorderDxfId="54" totalsRowBorderDxfId="53">
+  <autoFilter ref="A5:E7"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Номер п/п" dataDxfId="52"/>
+    <tableColumn id="2" name="Пом" dataDxfId="51"/>
+    <tableColumn id="3" name="Секция" dataDxfId="50"/>
+    <tableColumn id="4" name="Тип" dataDxfId="49"/>
+    <tableColumn id="5" name="Общее кол-во" dataDxfId="48"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Таблица5" displayName="Таблица5" ref="A5:E19" totalsRowShown="0" headerRowDxfId="47" dataDxfId="45" headerRowBorderDxfId="46" tableBorderDxfId="44" totalsRowBorderDxfId="43">
+  <autoFilter ref="A5:E19"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Номер п/п" dataDxfId="42"/>
+    <tableColumn id="2" name="Пом" dataDxfId="41"/>
+    <tableColumn id="3" name="Секция" dataDxfId="40"/>
+    <tableColumn id="4" name="Тип" dataDxfId="39"/>
+    <tableColumn id="5" name="Общее кол-во" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11489,11 +11798,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="89"/>
-      <c r="C1" s="166" t="s">
+      <c r="C1" s="168" t="s">
         <v>240</v>
       </c>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
       <c r="F1" s="104" t="s">
         <v>303</v>
       </c>
@@ -11508,11 +11817,11 @@
       <c r="B2" s="104">
         <v>504</v>
       </c>
-      <c r="C2" s="167" t="s">
+      <c r="C2" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="167"/>
-      <c r="E2" s="167"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
       <c r="F2" s="58" t="s">
         <v>438</v>
       </c>
@@ -11528,11 +11837,11 @@
       <c r="B3" s="104">
         <v>507</v>
       </c>
-      <c r="C3" s="167" t="s">
+      <c r="C3" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="167"/>
-      <c r="E3" s="167"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="58" t="s">
         <v>437</v>
       </c>
@@ -11548,11 +11857,11 @@
       <c r="B4" s="104">
         <v>510</v>
       </c>
-      <c r="C4" s="167" t="s">
+      <c r="C4" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
       <c r="F4" s="58" t="s">
         <v>321</v>
       </c>
@@ -11568,11 +11877,11 @@
       <c r="B5" s="104">
         <v>525</v>
       </c>
-      <c r="C5" s="167" t="s">
+      <c r="C5" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="169"/>
       <c r="F5" s="58" t="s">
         <v>319</v>
       </c>
@@ -11588,11 +11897,11 @@
       <c r="B6" s="104">
         <v>528</v>
       </c>
-      <c r="C6" s="167" t="s">
+      <c r="C6" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="167"/>
-      <c r="E6" s="167"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="169"/>
       <c r="F6" s="58" t="s">
         <v>436</v>
       </c>
@@ -11602,11 +11911,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="156"/>
-      <c r="B7" s="156"/>
-      <c r="C7" s="156"/>
-      <c r="D7" s="156"/>
-      <c r="E7" s="157"/>
+      <c r="A7" s="158"/>
+      <c r="B7" s="158"/>
+      <c r="C7" s="158"/>
+      <c r="D7" s="158"/>
+      <c r="E7" s="159"/>
       <c r="F7" s="104" t="s">
         <v>216</v>
       </c>
@@ -11631,8 +11940,8 @@
       <c r="E8" s="95" t="s">
         <v>326</v>
       </c>
-      <c r="F8" s="162"/>
-      <c r="G8" s="163"/>
+      <c r="F8" s="164"/>
+      <c r="G8" s="165"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="106">
@@ -11650,8 +11959,8 @@
       <c r="E9" s="107">
         <v>41.3</v>
       </c>
-      <c r="F9" s="164"/>
-      <c r="G9" s="165"/>
+      <c r="F9" s="166"/>
+      <c r="G9" s="167"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="106">
@@ -11669,8 +11978,8 @@
       <c r="E10" s="107">
         <v>16.3</v>
       </c>
-      <c r="F10" s="164"/>
-      <c r="G10" s="165"/>
+      <c r="F10" s="166"/>
+      <c r="G10" s="167"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="106">
@@ -11688,8 +11997,8 @@
       <c r="E11" s="107">
         <v>92.3</v>
       </c>
-      <c r="F11" s="164"/>
-      <c r="G11" s="165"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="167"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="106">
@@ -11707,8 +12016,8 @@
       <c r="E12" s="107">
         <v>44.6</v>
       </c>
-      <c r="F12" s="164"/>
-      <c r="G12" s="165"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="167"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="106">
@@ -11726,8 +12035,8 @@
       <c r="E13" s="107">
         <v>12.8</v>
       </c>
-      <c r="F13" s="164"/>
-      <c r="G13" s="165"/>
+      <c r="F13" s="166"/>
+      <c r="G13" s="167"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="106">
@@ -11745,8 +12054,8 @@
       <c r="E14" s="107">
         <v>18.399999999999999</v>
       </c>
-      <c r="F14" s="164"/>
-      <c r="G14" s="165"/>
+      <c r="F14" s="166"/>
+      <c r="G14" s="167"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="106">
@@ -11764,8 +12073,8 @@
       <c r="E15" s="107">
         <v>75.099999999999994</v>
       </c>
-      <c r="F15" s="164"/>
-      <c r="G15" s="165"/>
+      <c r="F15" s="166"/>
+      <c r="G15" s="167"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="106">
@@ -11783,8 +12092,8 @@
       <c r="E16" s="107">
         <v>163.5</v>
       </c>
-      <c r="F16" s="164"/>
-      <c r="G16" s="165"/>
+      <c r="F16" s="166"/>
+      <c r="G16" s="167"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="106">
@@ -11802,8 +12111,8 @@
       <c r="E17" s="107">
         <v>132.69999999999999</v>
       </c>
-      <c r="F17" s="164"/>
-      <c r="G17" s="165"/>
+      <c r="F17" s="166"/>
+      <c r="G17" s="167"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="106">
@@ -11821,8 +12130,8 @@
       <c r="E18" s="111">
         <v>44.2</v>
       </c>
-      <c r="F18" s="164"/>
-      <c r="G18" s="165"/>
+      <c r="F18" s="166"/>
+      <c r="G18" s="167"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="106">
@@ -11840,8 +12149,8 @@
       <c r="E19" s="128">
         <v>10.8</v>
       </c>
-      <c r="F19" s="164"/>
-      <c r="G19" s="165"/>
+      <c r="F19" s="166"/>
+      <c r="G19" s="167"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="106">
@@ -11859,8 +12168,8 @@
       <c r="E20" s="128">
         <v>281.5</v>
       </c>
-      <c r="F20" s="164"/>
-      <c r="G20" s="165"/>
+      <c r="F20" s="166"/>
+      <c r="G20" s="167"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="106">
@@ -11878,8 +12187,8 @@
       <c r="E21" s="107">
         <v>19.3</v>
       </c>
-      <c r="F21" s="164"/>
-      <c r="G21" s="165"/>
+      <c r="F21" s="166"/>
+      <c r="G21" s="167"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="106">
@@ -11897,8 +12206,8 @@
       <c r="E22" s="128">
         <v>23.5</v>
       </c>
-      <c r="F22" s="164"/>
-      <c r="G22" s="165"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="167"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="106">
@@ -11916,8 +12225,8 @@
       <c r="E23" s="128">
         <v>69.3</v>
       </c>
-      <c r="F23" s="164"/>
-      <c r="G23" s="165"/>
+      <c r="F23" s="166"/>
+      <c r="G23" s="167"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="106">
@@ -11935,8 +12244,8 @@
       <c r="E24" s="107">
         <v>85.1</v>
       </c>
-      <c r="F24" s="164"/>
-      <c r="G24" s="165"/>
+      <c r="F24" s="166"/>
+      <c r="G24" s="167"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="106">
@@ -11954,8 +12263,8 @@
       <c r="E25" s="107">
         <v>66.099999999999994</v>
       </c>
-      <c r="F25" s="164"/>
-      <c r="G25" s="165"/>
+      <c r="F25" s="166"/>
+      <c r="G25" s="167"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="106">
@@ -11973,8 +12282,8 @@
       <c r="E26" s="107">
         <v>20.8</v>
       </c>
-      <c r="F26" s="164"/>
-      <c r="G26" s="165"/>
+      <c r="F26" s="166"/>
+      <c r="G26" s="167"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="106">
@@ -11992,8 +12301,8 @@
       <c r="E27" s="107">
         <v>55.3</v>
       </c>
-      <c r="F27" s="164"/>
-      <c r="G27" s="165"/>
+      <c r="F27" s="166"/>
+      <c r="G27" s="167"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="106">
@@ -12011,8 +12320,8 @@
       <c r="E28" s="121">
         <v>12.7</v>
       </c>
-      <c r="F28" s="164"/>
-      <c r="G28" s="165"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="167"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="106">
@@ -12030,8 +12339,8 @@
       <c r="E29" s="107">
         <v>159.9</v>
       </c>
-      <c r="F29" s="164"/>
-      <c r="G29" s="165"/>
+      <c r="F29" s="166"/>
+      <c r="G29" s="167"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="106">
@@ -12049,8 +12358,8 @@
       <c r="E30" s="126">
         <v>497.3</v>
       </c>
-      <c r="F30" s="164"/>
-      <c r="G30" s="165"/>
+      <c r="F30" s="166"/>
+      <c r="G30" s="167"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="106">
@@ -12068,8 +12377,8 @@
       <c r="E31" s="126">
         <v>217.5</v>
       </c>
-      <c r="F31" s="164"/>
-      <c r="G31" s="165"/>
+      <c r="F31" s="166"/>
+      <c r="G31" s="167"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="106">
@@ -12087,8 +12396,8 @@
       <c r="E32" s="126">
         <v>53.4</v>
       </c>
-      <c r="F32" s="164"/>
-      <c r="G32" s="165"/>
+      <c r="F32" s="166"/>
+      <c r="G32" s="167"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="106">
@@ -12106,8 +12415,8 @@
       <c r="E33" s="126">
         <v>12.3</v>
       </c>
-      <c r="F33" s="164"/>
-      <c r="G33" s="165"/>
+      <c r="F33" s="166"/>
+      <c r="G33" s="167"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="106">
@@ -12125,8 +12434,8 @@
       <c r="E34" s="126">
         <v>168.7</v>
       </c>
-      <c r="F34" s="164"/>
-      <c r="G34" s="165"/>
+      <c r="F34" s="166"/>
+      <c r="G34" s="167"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="106">
@@ -12144,8 +12453,8 @@
       <c r="E35" s="123">
         <v>12.8</v>
       </c>
-      <c r="F35" s="164"/>
-      <c r="G35" s="165"/>
+      <c r="F35" s="166"/>
+      <c r="G35" s="167"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="106">
@@ -12163,8 +12472,8 @@
       <c r="E36" s="126">
         <v>69.400000000000006</v>
       </c>
-      <c r="F36" s="164"/>
-      <c r="G36" s="165"/>
+      <c r="F36" s="166"/>
+      <c r="G36" s="167"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="106">
@@ -12182,8 +12491,8 @@
       <c r="E37" s="128">
         <v>43.6</v>
       </c>
-      <c r="F37" s="164"/>
-      <c r="G37" s="165"/>
+      <c r="F37" s="166"/>
+      <c r="G37" s="167"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="106">
@@ -12201,8 +12510,8 @@
       <c r="E38" s="128">
         <v>50.1</v>
       </c>
-      <c r="F38" s="164"/>
-      <c r="G38" s="165"/>
+      <c r="F38" s="166"/>
+      <c r="G38" s="167"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="106">
@@ -12220,8 +12529,8 @@
       <c r="E39" s="128">
         <v>70.2</v>
       </c>
-      <c r="F39" s="164"/>
-      <c r="G39" s="165"/>
+      <c r="F39" s="166"/>
+      <c r="G39" s="167"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="106">
@@ -12239,8 +12548,8 @@
       <c r="E40" s="128">
         <v>6.1</v>
       </c>
-      <c r="F40" s="164"/>
-      <c r="G40" s="165"/>
+      <c r="F40" s="166"/>
+      <c r="G40" s="167"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="106">
@@ -12258,8 +12567,8 @@
       <c r="E41" s="128">
         <v>11.3</v>
       </c>
-      <c r="F41" s="164"/>
-      <c r="G41" s="165"/>
+      <c r="F41" s="166"/>
+      <c r="G41" s="167"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="106">
@@ -12277,8 +12586,8 @@
       <c r="E42" s="126">
         <v>30.1</v>
       </c>
-      <c r="F42" s="164"/>
-      <c r="G42" s="165"/>
+      <c r="F42" s="166"/>
+      <c r="G42" s="167"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="106">
@@ -12296,8 +12605,8 @@
       <c r="E43" s="126">
         <v>66.900000000000006</v>
       </c>
-      <c r="F43" s="164"/>
-      <c r="G43" s="165"/>
+      <c r="F43" s="166"/>
+      <c r="G43" s="167"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="106">
@@ -12315,8 +12624,8 @@
       <c r="E44" s="126">
         <v>487.6</v>
       </c>
-      <c r="F44" s="164"/>
-      <c r="G44" s="165"/>
+      <c r="F44" s="166"/>
+      <c r="G44" s="167"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="106">
@@ -12334,8 +12643,8 @@
       <c r="E45" s="126">
         <v>34.4</v>
       </c>
-      <c r="F45" s="164"/>
-      <c r="G45" s="165"/>
+      <c r="F45" s="166"/>
+      <c r="G45" s="167"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="106">
@@ -12353,8 +12662,8 @@
       <c r="E46" s="127">
         <v>31.3</v>
       </c>
-      <c r="F46" s="164"/>
-      <c r="G46" s="165"/>
+      <c r="F46" s="166"/>
+      <c r="G46" s="167"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="106">
@@ -12372,8 +12681,8 @@
       <c r="E47" s="113">
         <v>198</v>
       </c>
-      <c r="F47" s="164"/>
-      <c r="G47" s="165"/>
+      <c r="F47" s="166"/>
+      <c r="G47" s="167"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="46"/>
@@ -12386,8 +12695,8 @@
         <f>SUM(E9:E47)</f>
         <v>3506.5</v>
       </c>
-      <c r="F48" s="164"/>
-      <c r="G48" s="165"/>
+      <c r="F48" s="166"/>
+      <c r="G48" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -12430,10 +12739,10 @@
       <c r="B1" s="56" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="152" t="s">
         <v>315</v>
       </c>
-      <c r="D1" s="152"/>
+      <c r="D1" s="154"/>
       <c r="E1" s="41" t="s">
         <v>269</v>
       </c>
@@ -12451,10 +12760,10 @@
       <c r="B2" s="57">
         <v>510</v>
       </c>
-      <c r="C2" s="153" t="s">
+      <c r="C2" s="155" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="155"/>
+      <c r="D2" s="157"/>
       <c r="E2" s="58" t="s">
         <v>321</v>
       </c>
@@ -12473,10 +12782,10 @@
       <c r="B3" s="60">
         <v>525</v>
       </c>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="169"/>
+      <c r="D3" s="171"/>
       <c r="E3" s="61" t="s">
         <v>319</v>
       </c>
@@ -12495,10 +12804,10 @@
       <c r="B4" s="56">
         <v>531</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="155" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="155"/>
+      <c r="D4" s="157"/>
       <c r="E4" s="58" t="s">
         <v>327</v>
       </c>
@@ -12517,10 +12826,10 @@
       <c r="B5" s="63" t="s">
         <v>345</v>
       </c>
-      <c r="C5" s="168" t="s">
+      <c r="C5" s="170" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="169"/>
+      <c r="D5" s="171"/>
       <c r="E5" s="61" t="s">
         <v>320</v>
       </c>
@@ -12533,11 +12842,11 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="156"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="157"/>
+      <c r="A6" s="158"/>
+      <c r="B6" s="158"/>
+      <c r="C6" s="158"/>
+      <c r="D6" s="158"/>
+      <c r="E6" s="159"/>
       <c r="F6" s="41" t="s">
         <v>216</v>
       </c>
@@ -12559,9 +12868,9 @@
       <c r="D7" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="158"/>
-      <c r="F7" s="159"/>
-      <c r="G7" s="159"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="161"/>
+      <c r="G7" s="161"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="46">
@@ -12576,9 +12885,9 @@
       <c r="D8" s="49">
         <v>18.100000000000001</v>
       </c>
-      <c r="E8" s="160"/>
-      <c r="F8" s="161"/>
-      <c r="G8" s="161"/>
+      <c r="E8" s="162"/>
+      <c r="F8" s="163"/>
+      <c r="G8" s="163"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="46">
@@ -12593,9 +12902,9 @@
       <c r="D9" s="49">
         <v>18.600000000000001</v>
       </c>
-      <c r="E9" s="160"/>
-      <c r="F9" s="161"/>
-      <c r="G9" s="161"/>
+      <c r="E9" s="162"/>
+      <c r="F9" s="163"/>
+      <c r="G9" s="163"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="46">
@@ -12610,9 +12919,9 @@
       <c r="D10" s="49">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E10" s="160"/>
-      <c r="F10" s="161"/>
-      <c r="G10" s="161"/>
+      <c r="E10" s="162"/>
+      <c r="F10" s="163"/>
+      <c r="G10" s="163"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="59">
@@ -12627,9 +12936,9 @@
       <c r="D11" s="88">
         <v>10.5</v>
       </c>
-      <c r="E11" s="160"/>
-      <c r="F11" s="161"/>
-      <c r="G11" s="161"/>
+      <c r="E11" s="162"/>
+      <c r="F11" s="163"/>
+      <c r="G11" s="163"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="46">
@@ -12644,9 +12953,9 @@
       <c r="D12" s="49">
         <v>4.8</v>
       </c>
-      <c r="E12" s="160"/>
-      <c r="F12" s="161"/>
-      <c r="G12" s="161"/>
+      <c r="E12" s="162"/>
+      <c r="F12" s="163"/>
+      <c r="G12" s="163"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="59">
@@ -12661,9 +12970,9 @@
       <c r="D13" s="88">
         <v>13.5</v>
       </c>
-      <c r="E13" s="160"/>
-      <c r="F13" s="161"/>
-      <c r="G13" s="161"/>
+      <c r="E13" s="162"/>
+      <c r="F13" s="163"/>
+      <c r="G13" s="163"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="46">
@@ -12678,9 +12987,9 @@
       <c r="D14" s="49">
         <v>13.6</v>
       </c>
-      <c r="E14" s="160"/>
-      <c r="F14" s="161"/>
-      <c r="G14" s="161"/>
+      <c r="E14" s="162"/>
+      <c r="F14" s="163"/>
+      <c r="G14" s="163"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="59">
@@ -12695,9 +13004,9 @@
       <c r="D15" s="88">
         <v>6.5</v>
       </c>
-      <c r="E15" s="160"/>
-      <c r="F15" s="161"/>
-      <c r="G15" s="161"/>
+      <c r="E15" s="162"/>
+      <c r="F15" s="163"/>
+      <c r="G15" s="163"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="46">
@@ -12712,9 +13021,9 @@
       <c r="D16" s="49">
         <v>16.399999999999999</v>
       </c>
-      <c r="E16" s="160"/>
-      <c r="F16" s="161"/>
-      <c r="G16" s="161"/>
+      <c r="E16" s="162"/>
+      <c r="F16" s="163"/>
+      <c r="G16" s="163"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="46">
@@ -12729,9 +13038,9 @@
       <c r="D17" s="49">
         <v>19.100000000000001</v>
       </c>
-      <c r="E17" s="160"/>
-      <c r="F17" s="161"/>
-      <c r="G17" s="161"/>
+      <c r="E17" s="162"/>
+      <c r="F17" s="163"/>
+      <c r="G17" s="163"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="46">
@@ -12746,9 +13055,9 @@
       <c r="D18" s="49">
         <v>18.600000000000001</v>
       </c>
-      <c r="E18" s="160"/>
-      <c r="F18" s="161"/>
-      <c r="G18" s="161"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="163"/>
+      <c r="G18" s="163"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="46">
@@ -12763,9 +13072,9 @@
       <c r="D19" s="49">
         <v>5</v>
       </c>
-      <c r="E19" s="160"/>
-      <c r="F19" s="161"/>
-      <c r="G19" s="161"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="163"/>
+      <c r="G19" s="163"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="59">
@@ -12780,9 +13089,9 @@
       <c r="D20" s="88">
         <v>13.9</v>
       </c>
-      <c r="E20" s="160"/>
-      <c r="F20" s="161"/>
-      <c r="G20" s="161"/>
+      <c r="E20" s="162"/>
+      <c r="F20" s="163"/>
+      <c r="G20" s="163"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="46">
@@ -12797,9 +13106,9 @@
       <c r="D21" s="49">
         <v>10.4</v>
       </c>
-      <c r="E21" s="160"/>
-      <c r="F21" s="161"/>
-      <c r="G21" s="161"/>
+      <c r="E21" s="162"/>
+      <c r="F21" s="163"/>
+      <c r="G21" s="163"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="59">
@@ -12814,9 +13123,9 @@
       <c r="D22" s="88">
         <v>5</v>
       </c>
-      <c r="E22" s="160"/>
-      <c r="F22" s="161"/>
-      <c r="G22" s="161"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="163"/>
+      <c r="G22" s="163"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="46">
@@ -12831,9 +13140,9 @@
       <c r="D23" s="49">
         <v>13.7</v>
       </c>
-      <c r="E23" s="160"/>
-      <c r="F23" s="161"/>
-      <c r="G23" s="161"/>
+      <c r="E23" s="162"/>
+      <c r="F23" s="163"/>
+      <c r="G23" s="163"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="59">
@@ -12848,9 +13157,9 @@
       <c r="D24" s="88">
         <v>6.7</v>
       </c>
-      <c r="E24" s="160"/>
-      <c r="F24" s="161"/>
-      <c r="G24" s="161"/>
+      <c r="E24" s="162"/>
+      <c r="F24" s="163"/>
+      <c r="G24" s="163"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="46">
@@ -12865,9 +13174,9 @@
       <c r="D25" s="49">
         <v>16.8</v>
       </c>
-      <c r="E25" s="160"/>
-      <c r="F25" s="161"/>
-      <c r="G25" s="161"/>
+      <c r="E25" s="162"/>
+      <c r="F25" s="163"/>
+      <c r="G25" s="163"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="46">
@@ -12882,9 +13191,9 @@
       <c r="D26" s="49">
         <v>28.6</v>
       </c>
-      <c r="E26" s="160"/>
-      <c r="F26" s="161"/>
-      <c r="G26" s="161"/>
+      <c r="E26" s="162"/>
+      <c r="F26" s="163"/>
+      <c r="G26" s="163"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="46">
@@ -12899,9 +13208,9 @@
       <c r="D27" s="49">
         <v>19.100000000000001</v>
       </c>
-      <c r="E27" s="160"/>
-      <c r="F27" s="161"/>
-      <c r="G27" s="161"/>
+      <c r="E27" s="162"/>
+      <c r="F27" s="163"/>
+      <c r="G27" s="163"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="46">
@@ -12916,9 +13225,9 @@
       <c r="D28" s="49">
         <v>5</v>
       </c>
-      <c r="E28" s="160"/>
-      <c r="F28" s="161"/>
-      <c r="G28" s="161"/>
+      <c r="E28" s="162"/>
+      <c r="F28" s="163"/>
+      <c r="G28" s="163"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="59">
@@ -12933,9 +13242,9 @@
       <c r="D29" s="88">
         <v>12.1</v>
       </c>
-      <c r="E29" s="160"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="161"/>
+      <c r="E29" s="162"/>
+      <c r="F29" s="163"/>
+      <c r="G29" s="163"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="46">
@@ -12950,9 +13259,9 @@
       <c r="D30" s="49">
         <v>10.5</v>
       </c>
-      <c r="E30" s="160"/>
-      <c r="F30" s="161"/>
-      <c r="G30" s="161"/>
+      <c r="E30" s="162"/>
+      <c r="F30" s="163"/>
+      <c r="G30" s="163"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="59">
@@ -12967,9 +13276,9 @@
       <c r="D31" s="88">
         <v>5.2</v>
       </c>
-      <c r="E31" s="160"/>
-      <c r="F31" s="161"/>
-      <c r="G31" s="161"/>
+      <c r="E31" s="162"/>
+      <c r="F31" s="163"/>
+      <c r="G31" s="163"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="46">
@@ -12984,9 +13293,9 @@
       <c r="D32" s="49">
         <v>5</v>
       </c>
-      <c r="E32" s="160"/>
-      <c r="F32" s="161"/>
-      <c r="G32" s="161"/>
+      <c r="E32" s="162"/>
+      <c r="F32" s="163"/>
+      <c r="G32" s="163"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="46">
@@ -13001,9 +13310,9 @@
       <c r="D33" s="49">
         <v>13.9</v>
       </c>
-      <c r="E33" s="160"/>
-      <c r="F33" s="161"/>
-      <c r="G33" s="161"/>
+      <c r="E33" s="162"/>
+      <c r="F33" s="163"/>
+      <c r="G33" s="163"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="59">
@@ -13018,9 +13327,9 @@
       <c r="D34" s="88">
         <v>5.5</v>
       </c>
-      <c r="E34" s="160"/>
-      <c r="F34" s="161"/>
-      <c r="G34" s="161"/>
+      <c r="E34" s="162"/>
+      <c r="F34" s="163"/>
+      <c r="G34" s="163"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="46">
@@ -13035,9 +13344,9 @@
       <c r="D35" s="49">
         <v>6.7</v>
       </c>
-      <c r="E35" s="160"/>
-      <c r="F35" s="161"/>
-      <c r="G35" s="161"/>
+      <c r="E35" s="162"/>
+      <c r="F35" s="163"/>
+      <c r="G35" s="163"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="59">
@@ -13052,9 +13361,9 @@
       <c r="D36" s="88">
         <v>16.399999999999999</v>
       </c>
-      <c r="E36" s="160"/>
-      <c r="F36" s="161"/>
-      <c r="G36" s="161"/>
+      <c r="E36" s="162"/>
+      <c r="F36" s="163"/>
+      <c r="G36" s="163"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="46">
@@ -13069,9 +13378,9 @@
       <c r="D37" s="49">
         <v>241.8</v>
       </c>
-      <c r="E37" s="160"/>
-      <c r="F37" s="161"/>
-      <c r="G37" s="161"/>
+      <c r="E37" s="162"/>
+      <c r="F37" s="163"/>
+      <c r="G37" s="163"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="59">
@@ -13086,9 +13395,9 @@
       <c r="D38" s="88">
         <v>72.900000000000006</v>
       </c>
-      <c r="E38" s="160"/>
-      <c r="F38" s="161"/>
-      <c r="G38" s="161"/>
+      <c r="E38" s="162"/>
+      <c r="F38" s="163"/>
+      <c r="G38" s="163"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="46">
@@ -13103,9 +13412,9 @@
       <c r="D39" s="49">
         <v>10.3</v>
       </c>
-      <c r="E39" s="160"/>
-      <c r="F39" s="161"/>
-      <c r="G39" s="161"/>
+      <c r="E39" s="162"/>
+      <c r="F39" s="163"/>
+      <c r="G39" s="163"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="46">
@@ -13120,9 +13429,9 @@
       <c r="D40" s="49">
         <v>5</v>
       </c>
-      <c r="E40" s="160"/>
-      <c r="F40" s="161"/>
-      <c r="G40" s="161"/>
+      <c r="E40" s="162"/>
+      <c r="F40" s="163"/>
+      <c r="G40" s="163"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="59">
@@ -13137,9 +13446,9 @@
       <c r="D41" s="88">
         <v>14</v>
       </c>
-      <c r="E41" s="160"/>
-      <c r="F41" s="161"/>
-      <c r="G41" s="161"/>
+      <c r="E41" s="162"/>
+      <c r="F41" s="163"/>
+      <c r="G41" s="163"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="46">
@@ -13154,9 +13463,9 @@
       <c r="D42" s="49">
         <v>4.4000000000000004</v>
       </c>
-      <c r="E42" s="160"/>
-      <c r="F42" s="161"/>
-      <c r="G42" s="161"/>
+      <c r="E42" s="162"/>
+      <c r="F42" s="163"/>
+      <c r="G42" s="163"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="59">
@@ -13171,9 +13480,9 @@
       <c r="D43" s="88">
         <v>6.6</v>
       </c>
-      <c r="E43" s="160"/>
-      <c r="F43" s="161"/>
-      <c r="G43" s="161"/>
+      <c r="E43" s="162"/>
+      <c r="F43" s="163"/>
+      <c r="G43" s="163"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="46">
@@ -13188,9 +13497,9 @@
       <c r="D44" s="49">
         <v>16.5</v>
       </c>
-      <c r="E44" s="160"/>
-      <c r="F44" s="161"/>
-      <c r="G44" s="161"/>
+      <c r="E44" s="162"/>
+      <c r="F44" s="163"/>
+      <c r="G44" s="163"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="46"/>
@@ -13202,9 +13511,9 @@
         <f>SUM(D8:D44)</f>
         <v>715.29999999999984</v>
       </c>
-      <c r="E45" s="160"/>
-      <c r="F45" s="161"/>
-      <c r="G45" s="161"/>
+      <c r="E45" s="162"/>
+      <c r="F45" s="163"/>
+      <c r="G45" s="163"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -13287,11 +13596,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="163"/>
-      <c r="B4" s="163"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="163"/>
+      <c r="A4" s="165"/>
+      <c r="B4" s="165"/>
+      <c r="C4" s="165"/>
+      <c r="D4" s="165"/>
+      <c r="E4" s="165"/>
     </row>
     <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="41" t="s">
@@ -13306,7 +13615,7 @@
       <c r="D5" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="164"/>
+      <c r="E5" s="166"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="46">
@@ -13321,7 +13630,7 @@
       <c r="D6" s="47">
         <v>15.32</v>
       </c>
-      <c r="E6" s="164"/>
+      <c r="E6" s="166"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="46">
@@ -13336,7 +13645,7 @@
       <c r="D7" s="49">
         <v>97.9</v>
       </c>
-      <c r="E7" s="164"/>
+      <c r="E7" s="166"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="46">
@@ -13351,7 +13660,7 @@
       <c r="D8" s="47">
         <v>15.46</v>
       </c>
-      <c r="E8" s="164"/>
+      <c r="E8" s="166"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="46"/>
@@ -13365,14 +13674,14 @@
         <f>SUM(D6:D8)</f>
         <v>128.68</v>
       </c>
-      <c r="E9" s="164"/>
+      <c r="E9" s="166"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="163"/>
-      <c r="B10" s="163"/>
-      <c r="C10" s="163"/>
-      <c r="D10" s="163"/>
-      <c r="E10" s="163"/>
+      <c r="A10" s="165"/>
+      <c r="B10" s="165"/>
+      <c r="C10" s="165"/>
+      <c r="D10" s="165"/>
+      <c r="E10" s="165"/>
     </row>
     <row r="11" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A11" s="41" t="s">
@@ -13387,7 +13696,7 @@
       <c r="D11" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="164"/>
+      <c r="E11" s="166"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="46">
@@ -13402,7 +13711,7 @@
       <c r="D12" s="47">
         <v>15.43</v>
       </c>
-      <c r="E12" s="164"/>
+      <c r="E12" s="166"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="46"/>
@@ -13416,7 +13725,7 @@
         <f>SUM(D12:D12)</f>
         <v>15.43</v>
       </c>
-      <c r="E13" s="164"/>
+      <c r="E13" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13723,6 +14032,174 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" style="48" customWidth="1"/>
+    <col min="2" max="3" width="15.109375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" style="48" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" style="48" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="48" customWidth="1"/>
+    <col min="7" max="7" width="30.77734375" style="48" customWidth="1"/>
+    <col min="8" max="8" width="18.109375" style="48" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="145" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="144" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1" s="152" t="s">
+        <v>315</v>
+      </c>
+      <c r="D1" s="153"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="145" t="s">
+        <v>269</v>
+      </c>
+      <c r="G1" s="145" t="s">
+        <v>215</v>
+      </c>
+      <c r="H1" s="145" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="55.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="144">
+        <v>482</v>
+      </c>
+      <c r="C2" s="155" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="156"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="58" t="s">
+        <v>375</v>
+      </c>
+      <c r="G2" s="58" t="s">
+        <v>444</v>
+      </c>
+      <c r="H2" s="49">
+        <f>SUMIF($D$6:$D$6,F2,$E$6:$E$6)</f>
+        <v>306.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="55.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="46">
+        <v>2</v>
+      </c>
+      <c r="B3" s="63">
+        <v>485</v>
+      </c>
+      <c r="C3" s="170" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="172"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="61" t="s">
+        <v>375</v>
+      </c>
+      <c r="G3" s="61" t="s">
+        <v>445</v>
+      </c>
+      <c r="H3" s="64">
+        <f>SUMIF($D$6:$D$6,F3,$E$6:$E$6)</f>
+        <v>306.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="158"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="145" t="s">
+        <v>216</v>
+      </c>
+      <c r="H4" s="47">
+        <f>SUM(H2:H3)</f>
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="99" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="99" t="s">
+        <v>396</v>
+      </c>
+      <c r="D5" s="99" t="s">
+        <v>269</v>
+      </c>
+      <c r="E5" s="117" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="160"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="96">
+        <v>1</v>
+      </c>
+      <c r="B6" s="97" t="s">
+        <v>458</v>
+      </c>
+      <c r="C6" s="97">
+        <v>1</v>
+      </c>
+      <c r="D6" s="97" t="s">
+        <v>375</v>
+      </c>
+      <c r="E6" s="98">
+        <v>306.5</v>
+      </c>
+      <c r="F6" s="162"/>
+      <c r="G6" s="163"/>
+      <c r="H6" s="163"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="46"/>
+      <c r="B7" s="145"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="145" t="s">
+        <v>216</v>
+      </c>
+      <c r="E7" s="47">
+        <f>SUM(E6:E6)</f>
+        <v>306.5</v>
+      </c>
+      <c r="F7" s="162"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="163"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="F5:H7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -13743,11 +14220,11 @@
       <c r="B1" s="136" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="152" t="s">
         <v>315</v>
       </c>
-      <c r="D1" s="151"/>
-      <c r="E1" s="152"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="154"/>
       <c r="F1" s="137" t="s">
         <v>269</v>
       </c>
@@ -13765,11 +14242,11 @@
       <c r="B2" s="136">
         <v>482</v>
       </c>
-      <c r="C2" s="153" t="s">
+      <c r="C2" s="155" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="154"/>
-      <c r="E2" s="155"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="157"/>
       <c r="F2" s="58" t="s">
         <v>375</v>
       </c>
@@ -13788,11 +14265,11 @@
       <c r="B3" s="63">
         <v>485</v>
       </c>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="170"/>
-      <c r="E3" s="169"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="171"/>
       <c r="F3" s="61" t="s">
         <v>375</v>
       </c>
@@ -13805,12 +14282,12 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="156"/>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-      <c r="F4" s="157"/>
+      <c r="A4" s="158"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
+      <c r="F4" s="159"/>
       <c r="G4" s="137" t="s">
         <v>216</v>
       </c>
@@ -13835,9 +14312,9 @@
       <c r="E5" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="158"/>
-      <c r="G5" s="159"/>
-      <c r="H5" s="159"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="96">
@@ -13855,9 +14332,9 @@
       <c r="E6" s="98">
         <v>41.3</v>
       </c>
-      <c r="F6" s="160"/>
-      <c r="G6" s="161"/>
-      <c r="H6" s="161"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="163"/>
+      <c r="H6" s="163"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="96">
@@ -13875,9 +14352,9 @@
       <c r="E7" s="98">
         <v>92.3</v>
       </c>
-      <c r="F7" s="160"/>
-      <c r="G7" s="161"/>
-      <c r="H7" s="161"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="163"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="46"/>
@@ -13890,9 +14367,9 @@
         <f>SUM(E6:E7)</f>
         <v>133.6</v>
       </c>
-      <c r="F8" s="160"/>
-      <c r="G8" s="161"/>
-      <c r="H8" s="161"/>
+      <c r="F8" s="162"/>
+      <c r="G8" s="163"/>
+      <c r="H8" s="163"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -13909,7 +14386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -13931,11 +14408,11 @@
       <c r="B1" s="91" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="152" t="s">
         <v>315</v>
       </c>
-      <c r="D1" s="151"/>
-      <c r="E1" s="152"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="154"/>
       <c r="F1" s="92" t="s">
         <v>269</v>
       </c>
@@ -13953,11 +14430,11 @@
       <c r="B2" s="91" t="s">
         <v>305</v>
       </c>
-      <c r="C2" s="153" t="s">
+      <c r="C2" s="155" t="s">
         <v>310</v>
       </c>
-      <c r="D2" s="154"/>
-      <c r="E2" s="155"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="157"/>
       <c r="F2" s="58" t="s">
         <v>218</v>
       </c>
@@ -13976,11 +14453,11 @@
       <c r="B3" s="63" t="s">
         <v>305</v>
       </c>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="170"/>
-      <c r="E3" s="169"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="171"/>
       <c r="F3" s="61" t="s">
         <v>218</v>
       </c>
@@ -13993,12 +14470,12 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="156"/>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-      <c r="F4" s="157"/>
+      <c r="A4" s="158"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
+      <c r="F4" s="159"/>
       <c r="G4" s="92" t="s">
         <v>216</v>
       </c>
@@ -14023,9 +14500,9 @@
       <c r="E5" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="158"/>
-      <c r="G5" s="159"/>
-      <c r="H5" s="159"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="114">
@@ -14043,9 +14520,9 @@
       <c r="E6" s="115">
         <v>7.1</v>
       </c>
-      <c r="F6" s="160"/>
-      <c r="G6" s="161"/>
-      <c r="H6" s="161"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="163"/>
+      <c r="H6" s="163"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="114">
@@ -14063,9 +14540,9 @@
       <c r="E7" s="116">
         <v>16.100000000000001</v>
       </c>
-      <c r="F7" s="160"/>
-      <c r="G7" s="161"/>
-      <c r="H7" s="161"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="163"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="114">
@@ -14083,9 +14560,9 @@
       <c r="E8" s="115">
         <v>7.9</v>
       </c>
-      <c r="F8" s="160"/>
-      <c r="G8" s="161"/>
-      <c r="H8" s="161"/>
+      <c r="F8" s="162"/>
+      <c r="G8" s="163"/>
+      <c r="H8" s="163"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="114">
@@ -14103,9 +14580,9 @@
       <c r="E9" s="116">
         <v>7.7</v>
       </c>
-      <c r="F9" s="160"/>
-      <c r="G9" s="161"/>
-      <c r="H9" s="161"/>
+      <c r="F9" s="162"/>
+      <c r="G9" s="163"/>
+      <c r="H9" s="163"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="114">
@@ -14123,9 +14600,9 @@
       <c r="E10" s="115">
         <v>12.5</v>
       </c>
-      <c r="F10" s="160"/>
-      <c r="G10" s="161"/>
-      <c r="H10" s="161"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="163"/>
+      <c r="H10" s="163"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="114">
@@ -14143,9 +14620,9 @@
       <c r="E11" s="116">
         <v>12</v>
       </c>
-      <c r="F11" s="160"/>
-      <c r="G11" s="161"/>
-      <c r="H11" s="161"/>
+      <c r="F11" s="162"/>
+      <c r="G11" s="163"/>
+      <c r="H11" s="163"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="114">
@@ -14163,9 +14640,9 @@
       <c r="E12" s="116">
         <v>7.6</v>
       </c>
-      <c r="F12" s="160"/>
-      <c r="G12" s="161"/>
-      <c r="H12" s="161"/>
+      <c r="F12" s="162"/>
+      <c r="G12" s="163"/>
+      <c r="H12" s="163"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="114">
@@ -14183,9 +14660,9 @@
       <c r="E13" s="116">
         <v>5.3</v>
       </c>
-      <c r="F13" s="160"/>
-      <c r="G13" s="161"/>
-      <c r="H13" s="161"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="163"/>
+      <c r="H13" s="163"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="114">
@@ -14203,9 +14680,9 @@
       <c r="E14" s="116">
         <v>9.6999999999999993</v>
       </c>
-      <c r="F14" s="160"/>
-      <c r="G14" s="161"/>
-      <c r="H14" s="161"/>
+      <c r="F14" s="162"/>
+      <c r="G14" s="163"/>
+      <c r="H14" s="163"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="114">
@@ -14223,9 +14700,9 @@
       <c r="E15" s="115">
         <v>21.8</v>
       </c>
-      <c r="F15" s="160"/>
-      <c r="G15" s="161"/>
-      <c r="H15" s="161"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="163"/>
+      <c r="H15" s="163"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="114">
@@ -14243,9 +14720,9 @@
       <c r="E16" s="116">
         <v>8.5</v>
       </c>
-      <c r="F16" s="160"/>
-      <c r="G16" s="161"/>
-      <c r="H16" s="161"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="163"/>
+      <c r="H16" s="163"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="114">
@@ -14263,9 +14740,9 @@
       <c r="E17" s="116">
         <v>15.7</v>
       </c>
-      <c r="F17" s="160"/>
-      <c r="G17" s="161"/>
-      <c r="H17" s="161"/>
+      <c r="F17" s="162"/>
+      <c r="G17" s="163"/>
+      <c r="H17" s="163"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="114">
@@ -14283,9 +14760,9 @@
       <c r="E18" s="116">
         <v>9.4</v>
       </c>
-      <c r="F18" s="160"/>
-      <c r="G18" s="161"/>
-      <c r="H18" s="161"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="163"/>
+      <c r="H18" s="163"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="114">
@@ -14303,9 +14780,9 @@
       <c r="E19" s="116">
         <v>3.7</v>
       </c>
-      <c r="F19" s="160"/>
-      <c r="G19" s="161"/>
-      <c r="H19" s="161"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="163"/>
+      <c r="H19" s="163"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="46"/>
@@ -14318,9 +14795,9 @@
         <f>SUM(E6:E19)</f>
         <v>145</v>
       </c>
-      <c r="F20" s="160"/>
-      <c r="G20" s="161"/>
-      <c r="H20" s="161"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="163"/>
+      <c r="H20" s="163"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -14337,7 +14814,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -14359,11 +14836,11 @@
       <c r="B1" s="91" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="152" t="s">
         <v>315</v>
       </c>
-      <c r="D1" s="151"/>
-      <c r="E1" s="152"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="154"/>
       <c r="F1" s="92" t="s">
         <v>269</v>
       </c>
@@ -14381,11 +14858,11 @@
       <c r="B2" s="91">
         <v>482</v>
       </c>
-      <c r="C2" s="153" t="s">
+      <c r="C2" s="155" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="154"/>
-      <c r="E2" s="155"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="157"/>
       <c r="F2" s="58" t="s">
         <v>346</v>
       </c>
@@ -14404,11 +14881,11 @@
       <c r="B3" s="63">
         <v>485</v>
       </c>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="170"/>
-      <c r="E3" s="169"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="171"/>
       <c r="F3" s="61" t="s">
         <v>346</v>
       </c>
@@ -14427,11 +14904,11 @@
       <c r="B4" s="91">
         <v>494</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="155" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="154"/>
-      <c r="E4" s="155"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="157"/>
       <c r="F4" s="58" t="s">
         <v>231</v>
       </c>
@@ -14450,11 +14927,11 @@
       <c r="B5" s="63">
         <v>497</v>
       </c>
-      <c r="C5" s="168" t="s">
+      <c r="C5" s="170" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="170"/>
-      <c r="E5" s="169"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="171"/>
       <c r="F5" s="61" t="s">
         <v>231</v>
       </c>
@@ -14473,11 +14950,11 @@
       <c r="B6" s="91">
         <v>482</v>
       </c>
-      <c r="C6" s="153" t="s">
+      <c r="C6" s="155" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="154"/>
-      <c r="E6" s="155"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="157"/>
       <c r="F6" s="58" t="s">
         <v>267</v>
       </c>
@@ -14496,11 +14973,11 @@
       <c r="B7" s="63">
         <v>485</v>
       </c>
-      <c r="C7" s="168" t="s">
+      <c r="C7" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="170"/>
-      <c r="E7" s="169"/>
+      <c r="D7" s="172"/>
+      <c r="E7" s="171"/>
       <c r="F7" s="61" t="s">
         <v>267</v>
       </c>
@@ -14513,12 +14990,12 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="156"/>
-      <c r="B8" s="156"/>
-      <c r="C8" s="156"/>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
-      <c r="F8" s="157"/>
+      <c r="A8" s="158"/>
+      <c r="B8" s="158"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="159"/>
       <c r="G8" s="92" t="s">
         <v>216</v>
       </c>
@@ -14543,9 +15020,9 @@
       <c r="E9" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="158"/>
-      <c r="G9" s="159"/>
-      <c r="H9" s="159"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="161"/>
+      <c r="H9" s="161"/>
     </row>
     <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="96">
@@ -14563,9 +15040,9 @@
       <c r="E10" s="98">
         <v>41.3</v>
       </c>
-      <c r="F10" s="160"/>
-      <c r="G10" s="161"/>
-      <c r="H10" s="161"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="163"/>
+      <c r="H10" s="163"/>
     </row>
     <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="96">
@@ -14583,9 +15060,9 @@
       <c r="E11" s="98">
         <v>92.3</v>
       </c>
-      <c r="F11" s="160"/>
-      <c r="G11" s="161"/>
-      <c r="H11" s="161"/>
+      <c r="F11" s="162"/>
+      <c r="G11" s="163"/>
+      <c r="H11" s="163"/>
     </row>
     <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="96">
@@ -14603,9 +15080,9 @@
       <c r="E12" s="98">
         <v>44.6</v>
       </c>
-      <c r="F12" s="160"/>
-      <c r="G12" s="161"/>
-      <c r="H12" s="161"/>
+      <c r="F12" s="162"/>
+      <c r="G12" s="163"/>
+      <c r="H12" s="163"/>
     </row>
     <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="96">
@@ -14623,9 +15100,9 @@
       <c r="E13" s="98">
         <v>1.7</v>
       </c>
-      <c r="F13" s="160"/>
-      <c r="G13" s="161"/>
-      <c r="H13" s="161"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="163"/>
+      <c r="H13" s="163"/>
     </row>
     <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="96">
@@ -14643,9 +15120,9 @@
       <c r="E14" s="98">
         <v>14.6</v>
       </c>
-      <c r="F14" s="160"/>
-      <c r="G14" s="161"/>
-      <c r="H14" s="161"/>
+      <c r="F14" s="162"/>
+      <c r="G14" s="163"/>
+      <c r="H14" s="163"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="96">
@@ -14663,9 +15140,9 @@
       <c r="E15" s="98">
         <v>12.8</v>
       </c>
-      <c r="F15" s="160"/>
-      <c r="G15" s="161"/>
-      <c r="H15" s="161"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="163"/>
+      <c r="H15" s="163"/>
     </row>
     <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="96">
@@ -14683,9 +15160,9 @@
       <c r="E16" s="98">
         <v>10.8</v>
       </c>
-      <c r="F16" s="160"/>
-      <c r="G16" s="161"/>
-      <c r="H16" s="161"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="163"/>
+      <c r="H16" s="163"/>
     </row>
     <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="96">
@@ -14703,9 +15180,9 @@
       <c r="E17" s="98">
         <v>132.69999999999999</v>
       </c>
-      <c r="F17" s="160"/>
-      <c r="G17" s="161"/>
-      <c r="H17" s="161"/>
+      <c r="F17" s="162"/>
+      <c r="G17" s="163"/>
+      <c r="H17" s="163"/>
     </row>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="96">
@@ -14723,9 +15200,9 @@
       <c r="E18" s="98">
         <v>163.5</v>
       </c>
-      <c r="F18" s="160"/>
-      <c r="G18" s="161"/>
-      <c r="H18" s="161"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="163"/>
+      <c r="H18" s="163"/>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="96">
@@ -14743,9 +15220,9 @@
       <c r="E19" s="98">
         <v>75.099999999999994</v>
       </c>
-      <c r="F19" s="160"/>
-      <c r="G19" s="161"/>
-      <c r="H19" s="161"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="163"/>
+      <c r="H19" s="163"/>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="96">
@@ -14763,9 +15240,9 @@
       <c r="E20" s="98">
         <v>44.2</v>
       </c>
-      <c r="F20" s="160"/>
-      <c r="G20" s="161"/>
-      <c r="H20" s="161"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="163"/>
+      <c r="H20" s="163"/>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="96">
@@ -14783,9 +15260,9 @@
       <c r="E21" s="98">
         <v>18.399999999999999</v>
       </c>
-      <c r="F21" s="160"/>
-      <c r="G21" s="161"/>
-      <c r="H21" s="161"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="163"/>
+      <c r="H21" s="163"/>
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="96">
@@ -14803,9 +15280,9 @@
       <c r="E22" s="98">
         <v>281.5</v>
       </c>
-      <c r="F22" s="160"/>
-      <c r="G22" s="161"/>
-      <c r="H22" s="161"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="163"/>
+      <c r="H22" s="163"/>
     </row>
     <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="96">
@@ -14823,9 +15300,9 @@
       <c r="E23" s="98">
         <v>66.099999999999994</v>
       </c>
-      <c r="F23" s="160"/>
-      <c r="G23" s="161"/>
-      <c r="H23" s="161"/>
+      <c r="F23" s="162"/>
+      <c r="G23" s="163"/>
+      <c r="H23" s="163"/>
     </row>
     <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="96">
@@ -14843,9 +15320,9 @@
       <c r="E24" s="98">
         <v>20.8</v>
       </c>
-      <c r="F24" s="160"/>
-      <c r="G24" s="161"/>
-      <c r="H24" s="161"/>
+      <c r="F24" s="162"/>
+      <c r="G24" s="163"/>
+      <c r="H24" s="163"/>
     </row>
     <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="96">
@@ -14863,9 +15340,9 @@
       <c r="E25" s="98">
         <v>69.3</v>
       </c>
-      <c r="F25" s="160"/>
-      <c r="G25" s="161"/>
-      <c r="H25" s="161"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="163"/>
+      <c r="H25" s="163"/>
     </row>
     <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="96">
@@ -14883,9 +15360,9 @@
       <c r="E26" s="98">
         <v>23.5</v>
       </c>
-      <c r="F26" s="160"/>
-      <c r="G26" s="161"/>
-      <c r="H26" s="161"/>
+      <c r="F26" s="162"/>
+      <c r="G26" s="163"/>
+      <c r="H26" s="163"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="96">
@@ -14903,9 +15380,9 @@
       <c r="E27" s="98">
         <v>85.1</v>
       </c>
-      <c r="F27" s="160"/>
-      <c r="G27" s="161"/>
-      <c r="H27" s="161"/>
+      <c r="F27" s="162"/>
+      <c r="G27" s="163"/>
+      <c r="H27" s="163"/>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="96">
@@ -14923,9 +15400,9 @@
       <c r="E28" s="98">
         <v>19.3</v>
       </c>
-      <c r="F28" s="160"/>
-      <c r="G28" s="161"/>
-      <c r="H28" s="161"/>
+      <c r="F28" s="162"/>
+      <c r="G28" s="163"/>
+      <c r="H28" s="163"/>
     </row>
     <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="96">
@@ -14943,9 +15420,9 @@
       <c r="E29" s="98">
         <v>55.3</v>
       </c>
-      <c r="F29" s="160"/>
-      <c r="G29" s="161"/>
-      <c r="H29" s="161"/>
+      <c r="F29" s="162"/>
+      <c r="G29" s="163"/>
+      <c r="H29" s="163"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="96">
@@ -14963,9 +15440,9 @@
       <c r="E30" s="98">
         <v>12.7</v>
       </c>
-      <c r="F30" s="160"/>
-      <c r="G30" s="161"/>
-      <c r="H30" s="161"/>
+      <c r="F30" s="162"/>
+      <c r="G30" s="163"/>
+      <c r="H30" s="163"/>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="96">
@@ -14983,9 +15460,9 @@
       <c r="E31" s="98">
         <v>159.9</v>
       </c>
-      <c r="F31" s="160"/>
-      <c r="G31" s="161"/>
-      <c r="H31" s="161"/>
+      <c r="F31" s="162"/>
+      <c r="G31" s="163"/>
+      <c r="H31" s="163"/>
     </row>
     <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="96">
@@ -15003,9 +15480,9 @@
       <c r="E32" s="98">
         <v>217.5</v>
       </c>
-      <c r="F32" s="160"/>
-      <c r="G32" s="161"/>
-      <c r="H32" s="161"/>
+      <c r="F32" s="162"/>
+      <c r="G32" s="163"/>
+      <c r="H32" s="163"/>
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="96">
@@ -15023,9 +15500,9 @@
       <c r="E33" s="98">
         <v>497.3</v>
       </c>
-      <c r="F33" s="160"/>
-      <c r="G33" s="161"/>
-      <c r="H33" s="161"/>
+      <c r="F33" s="162"/>
+      <c r="G33" s="163"/>
+      <c r="H33" s="163"/>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="96">
@@ -15043,9 +15520,9 @@
       <c r="E34" s="98">
         <v>53.4</v>
       </c>
-      <c r="F34" s="160"/>
-      <c r="G34" s="161"/>
-      <c r="H34" s="161"/>
+      <c r="F34" s="162"/>
+      <c r="G34" s="163"/>
+      <c r="H34" s="163"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="96">
@@ -15063,9 +15540,9 @@
       <c r="E35" s="98">
         <v>12.3</v>
       </c>
-      <c r="F35" s="160"/>
-      <c r="G35" s="161"/>
-      <c r="H35" s="161"/>
+      <c r="F35" s="162"/>
+      <c r="G35" s="163"/>
+      <c r="H35" s="163"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="96">
@@ -15083,9 +15560,9 @@
       <c r="E36" s="98">
         <v>12.8</v>
       </c>
-      <c r="F36" s="160"/>
-      <c r="G36" s="161"/>
-      <c r="H36" s="161"/>
+      <c r="F36" s="162"/>
+      <c r="G36" s="163"/>
+      <c r="H36" s="163"/>
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="96">
@@ -15103,9 +15580,9 @@
       <c r="E37" s="98">
         <v>30.1</v>
       </c>
-      <c r="F37" s="160"/>
-      <c r="G37" s="161"/>
-      <c r="H37" s="161"/>
+      <c r="F37" s="162"/>
+      <c r="G37" s="163"/>
+      <c r="H37" s="163"/>
     </row>
     <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="96">
@@ -15123,9 +15600,9 @@
       <c r="E38" s="98">
         <v>11.3</v>
       </c>
-      <c r="F38" s="160"/>
-      <c r="G38" s="161"/>
-      <c r="H38" s="161"/>
+      <c r="F38" s="162"/>
+      <c r="G38" s="163"/>
+      <c r="H38" s="163"/>
     </row>
     <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="96">
@@ -15143,9 +15620,9 @@
       <c r="E39" s="98">
         <v>6.1</v>
       </c>
-      <c r="F39" s="160"/>
-      <c r="G39" s="161"/>
-      <c r="H39" s="161"/>
+      <c r="F39" s="162"/>
+      <c r="G39" s="163"/>
+      <c r="H39" s="163"/>
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="96">
@@ -15163,9 +15640,9 @@
       <c r="E40" s="98">
         <v>70.2</v>
       </c>
-      <c r="F40" s="160"/>
-      <c r="G40" s="161"/>
-      <c r="H40" s="161"/>
+      <c r="F40" s="162"/>
+      <c r="G40" s="163"/>
+      <c r="H40" s="163"/>
     </row>
     <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="96">
@@ -15183,9 +15660,9 @@
       <c r="E41" s="98">
         <v>50.1</v>
       </c>
-      <c r="F41" s="160"/>
-      <c r="G41" s="161"/>
-      <c r="H41" s="161"/>
+      <c r="F41" s="162"/>
+      <c r="G41" s="163"/>
+      <c r="H41" s="163"/>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="96">
@@ -15203,9 +15680,9 @@
       <c r="E42" s="98">
         <v>43.6</v>
       </c>
-      <c r="F42" s="160"/>
-      <c r="G42" s="161"/>
-      <c r="H42" s="161"/>
+      <c r="F42" s="162"/>
+      <c r="G42" s="163"/>
+      <c r="H42" s="163"/>
     </row>
     <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="96">
@@ -15223,9 +15700,9 @@
       <c r="E43" s="98">
         <v>69.400000000000006</v>
       </c>
-      <c r="F43" s="160"/>
-      <c r="G43" s="161"/>
-      <c r="H43" s="161"/>
+      <c r="F43" s="162"/>
+      <c r="G43" s="163"/>
+      <c r="H43" s="163"/>
     </row>
     <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="96">
@@ -15243,9 +15720,9 @@
       <c r="E44" s="98">
         <v>168.7</v>
       </c>
-      <c r="F44" s="160"/>
-      <c r="G44" s="161"/>
-      <c r="H44" s="161"/>
+      <c r="F44" s="162"/>
+      <c r="G44" s="163"/>
+      <c r="H44" s="163"/>
     </row>
     <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="96">
@@ -15263,9 +15740,9 @@
       <c r="E45" s="98">
         <v>66.900000000000006</v>
       </c>
-      <c r="F45" s="160"/>
-      <c r="G45" s="161"/>
-      <c r="H45" s="161"/>
+      <c r="F45" s="162"/>
+      <c r="G45" s="163"/>
+      <c r="H45" s="163"/>
     </row>
     <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="96">
@@ -15283,9 +15760,9 @@
       <c r="E46" s="98">
         <v>198</v>
       </c>
-      <c r="F46" s="160"/>
-      <c r="G46" s="161"/>
-      <c r="H46" s="161"/>
+      <c r="F46" s="162"/>
+      <c r="G46" s="163"/>
+      <c r="H46" s="163"/>
     </row>
     <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="96">
@@ -15303,9 +15780,9 @@
       <c r="E47" s="98">
         <v>31.3</v>
       </c>
-      <c r="F47" s="160"/>
-      <c r="G47" s="161"/>
-      <c r="H47" s="161"/>
+      <c r="F47" s="162"/>
+      <c r="G47" s="163"/>
+      <c r="H47" s="163"/>
     </row>
     <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="96">
@@ -15323,9 +15800,9 @@
       <c r="E48" s="98">
         <v>487.6</v>
       </c>
-      <c r="F48" s="160"/>
-      <c r="G48" s="161"/>
-      <c r="H48" s="161"/>
+      <c r="F48" s="162"/>
+      <c r="G48" s="163"/>
+      <c r="H48" s="163"/>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="96">
@@ -15343,9 +15820,9 @@
       <c r="E49" s="102">
         <v>34.4</v>
       </c>
-      <c r="F49" s="160"/>
-      <c r="G49" s="161"/>
-      <c r="H49" s="161"/>
+      <c r="F49" s="162"/>
+      <c r="G49" s="163"/>
+      <c r="H49" s="163"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="46"/>
@@ -15358,9 +15835,9 @@
         <f>SUM(E10:E49)</f>
         <v>3506.5000000000005</v>
       </c>
-      <c r="F50" s="160"/>
-      <c r="G50" s="161"/>
-      <c r="H50" s="161"/>
+      <c r="F50" s="162"/>
+      <c r="G50" s="163"/>
+      <c r="H50" s="163"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -15381,7 +15858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -15403,10 +15880,10 @@
       <c r="B1" s="55" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="152" t="s">
         <v>315</v>
       </c>
-      <c r="D1" s="152"/>
+      <c r="D1" s="154"/>
       <c r="E1" s="41" t="s">
         <v>269</v>
       </c>
@@ -15424,10 +15901,10 @@
       <c r="B2" s="57">
         <v>488</v>
       </c>
-      <c r="C2" s="153" t="s">
+      <c r="C2" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="155"/>
+      <c r="D2" s="157"/>
       <c r="E2" s="58" t="s">
         <v>236</v>
       </c>
@@ -15446,10 +15923,10 @@
       <c r="B3" s="60">
         <v>491</v>
       </c>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="169"/>
+      <c r="D3" s="171"/>
       <c r="E3" s="61" t="s">
         <v>236</v>
       </c>
@@ -15468,10 +15945,10 @@
       <c r="B4" s="55">
         <v>494</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="155" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="155"/>
+      <c r="D4" s="157"/>
       <c r="E4" s="58" t="s">
         <v>231</v>
       </c>
@@ -15490,10 +15967,10 @@
       <c r="B5" s="63">
         <v>497</v>
       </c>
-      <c r="C5" s="168" t="s">
+      <c r="C5" s="170" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="169"/>
+      <c r="D5" s="171"/>
       <c r="E5" s="61" t="s">
         <v>231</v>
       </c>
@@ -15512,10 +15989,10 @@
       <c r="B6" s="55">
         <v>482</v>
       </c>
-      <c r="C6" s="153" t="s">
+      <c r="C6" s="155" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="155"/>
+      <c r="D6" s="157"/>
       <c r="E6" s="58" t="s">
         <v>267</v>
       </c>
@@ -15534,10 +16011,10 @@
       <c r="B7" s="63">
         <v>485</v>
       </c>
-      <c r="C7" s="168" t="s">
+      <c r="C7" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="169"/>
+      <c r="D7" s="171"/>
       <c r="E7" s="61" t="s">
         <v>267</v>
       </c>
@@ -15556,10 +16033,10 @@
       <c r="B8" s="55" t="s">
         <v>305</v>
       </c>
-      <c r="C8" s="153" t="s">
+      <c r="C8" s="155" t="s">
         <v>310</v>
       </c>
-      <c r="D8" s="155"/>
+      <c r="D8" s="157"/>
       <c r="E8" s="58" t="s">
         <v>218</v>
       </c>
@@ -15578,10 +16055,10 @@
       <c r="B9" s="63" t="s">
         <v>305</v>
       </c>
-      <c r="C9" s="168" t="s">
+      <c r="C9" s="170" t="s">
         <v>310</v>
       </c>
-      <c r="D9" s="169"/>
+      <c r="D9" s="171"/>
       <c r="E9" s="61" t="s">
         <v>218</v>
       </c>
@@ -15594,11 +16071,11 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="156"/>
-      <c r="B10" s="156"/>
-      <c r="C10" s="156"/>
-      <c r="D10" s="156"/>
-      <c r="E10" s="157"/>
+      <c r="A10" s="158"/>
+      <c r="B10" s="158"/>
+      <c r="C10" s="158"/>
+      <c r="D10" s="158"/>
+      <c r="E10" s="159"/>
       <c r="F10" s="41" t="s">
         <v>216</v>
       </c>
@@ -15620,9 +16097,9 @@
       <c r="D11" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="158"/>
-      <c r="F11" s="159"/>
-      <c r="G11" s="159"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="161"/>
+      <c r="G11" s="161"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="59">
@@ -15637,9 +16114,9 @@
       <c r="D12" s="88">
         <v>18.100000000000001</v>
       </c>
-      <c r="E12" s="160"/>
-      <c r="F12" s="161"/>
-      <c r="G12" s="161"/>
+      <c r="E12" s="162"/>
+      <c r="F12" s="163"/>
+      <c r="G12" s="163"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="46">
@@ -15654,9 +16131,9 @@
       <c r="D13" s="49">
         <v>18.600000000000001</v>
       </c>
-      <c r="E13" s="160"/>
-      <c r="F13" s="161"/>
-      <c r="G13" s="161"/>
+      <c r="E13" s="162"/>
+      <c r="F13" s="163"/>
+      <c r="G13" s="163"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="59">
@@ -15671,9 +16148,9 @@
       <c r="D14" s="88">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E14" s="160"/>
-      <c r="F14" s="161"/>
-      <c r="G14" s="161"/>
+      <c r="E14" s="162"/>
+      <c r="F14" s="163"/>
+      <c r="G14" s="163"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="46">
@@ -15688,9 +16165,9 @@
       <c r="D15" s="49">
         <v>10.5</v>
       </c>
-      <c r="E15" s="160"/>
-      <c r="F15" s="161"/>
-      <c r="G15" s="161"/>
+      <c r="E15" s="162"/>
+      <c r="F15" s="163"/>
+      <c r="G15" s="163"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="46">
@@ -15705,9 +16182,9 @@
       <c r="D16" s="49">
         <v>4.8</v>
       </c>
-      <c r="E16" s="160"/>
-      <c r="F16" s="161"/>
-      <c r="G16" s="161"/>
+      <c r="E16" s="162"/>
+      <c r="F16" s="163"/>
+      <c r="G16" s="163"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="59">
@@ -15722,9 +16199,9 @@
       <c r="D17" s="88">
         <v>13.5</v>
       </c>
-      <c r="E17" s="160"/>
-      <c r="F17" s="161"/>
-      <c r="G17" s="161"/>
+      <c r="E17" s="162"/>
+      <c r="F17" s="163"/>
+      <c r="G17" s="163"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="46">
@@ -15739,9 +16216,9 @@
       <c r="D18" s="49">
         <v>13.6</v>
       </c>
-      <c r="E18" s="160"/>
-      <c r="F18" s="161"/>
-      <c r="G18" s="161"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="163"/>
+      <c r="G18" s="163"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="59">
@@ -15756,9 +16233,9 @@
       <c r="D19" s="88">
         <v>6.5</v>
       </c>
-      <c r="E19" s="160"/>
-      <c r="F19" s="161"/>
-      <c r="G19" s="161"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="163"/>
+      <c r="G19" s="163"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="46">
@@ -15773,9 +16250,9 @@
       <c r="D20" s="49">
         <v>16.399999999999999</v>
       </c>
-      <c r="E20" s="160"/>
-      <c r="F20" s="161"/>
-      <c r="G20" s="161"/>
+      <c r="E20" s="162"/>
+      <c r="F20" s="163"/>
+      <c r="G20" s="163"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="46">
@@ -15790,9 +16267,9 @@
       <c r="D21" s="49">
         <v>19.100000000000001</v>
       </c>
-      <c r="E21" s="160"/>
-      <c r="F21" s="161"/>
-      <c r="G21" s="161"/>
+      <c r="E21" s="162"/>
+      <c r="F21" s="163"/>
+      <c r="G21" s="163"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="46">
@@ -15807,9 +16284,9 @@
       <c r="D22" s="49">
         <v>18.600000000000001</v>
       </c>
-      <c r="E22" s="160"/>
-      <c r="F22" s="161"/>
-      <c r="G22" s="161"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="163"/>
+      <c r="G22" s="163"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="46">
@@ -15824,9 +16301,9 @@
       <c r="D23" s="49">
         <v>5</v>
       </c>
-      <c r="E23" s="160"/>
-      <c r="F23" s="161"/>
-      <c r="G23" s="161"/>
+      <c r="E23" s="162"/>
+      <c r="F23" s="163"/>
+      <c r="G23" s="163"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="59">
@@ -15841,9 +16318,9 @@
       <c r="D24" s="88">
         <v>13.9</v>
       </c>
-      <c r="E24" s="160"/>
-      <c r="F24" s="161"/>
-      <c r="G24" s="161"/>
+      <c r="E24" s="162"/>
+      <c r="F24" s="163"/>
+      <c r="G24" s="163"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="46">
@@ -15858,9 +16335,9 @@
       <c r="D25" s="49">
         <v>10.4</v>
       </c>
-      <c r="E25" s="160"/>
-      <c r="F25" s="161"/>
-      <c r="G25" s="161"/>
+      <c r="E25" s="162"/>
+      <c r="F25" s="163"/>
+      <c r="G25" s="163"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="59">
@@ -15875,9 +16352,9 @@
       <c r="D26" s="88">
         <v>5</v>
       </c>
-      <c r="E26" s="160"/>
-      <c r="F26" s="161"/>
-      <c r="G26" s="161"/>
+      <c r="E26" s="162"/>
+      <c r="F26" s="163"/>
+      <c r="G26" s="163"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="46">
@@ -15892,9 +16369,9 @@
       <c r="D27" s="49">
         <v>13.7</v>
       </c>
-      <c r="E27" s="160"/>
-      <c r="F27" s="161"/>
-      <c r="G27" s="161"/>
+      <c r="E27" s="162"/>
+      <c r="F27" s="163"/>
+      <c r="G27" s="163"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="59">
@@ -15909,9 +16386,9 @@
       <c r="D28" s="88">
         <v>6.7</v>
       </c>
-      <c r="E28" s="160"/>
-      <c r="F28" s="161"/>
-      <c r="G28" s="161"/>
+      <c r="E28" s="162"/>
+      <c r="F28" s="163"/>
+      <c r="G28" s="163"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="46">
@@ -15926,9 +16403,9 @@
       <c r="D29" s="49">
         <v>16.8</v>
       </c>
-      <c r="E29" s="160"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="161"/>
+      <c r="E29" s="162"/>
+      <c r="F29" s="163"/>
+      <c r="G29" s="163"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="46">
@@ -15943,9 +16420,9 @@
       <c r="D30" s="49">
         <v>28.6</v>
       </c>
-      <c r="E30" s="160"/>
-      <c r="F30" s="161"/>
-      <c r="G30" s="161"/>
+      <c r="E30" s="162"/>
+      <c r="F30" s="163"/>
+      <c r="G30" s="163"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="46">
@@ -15960,9 +16437,9 @@
       <c r="D31" s="49">
         <v>19.100000000000001</v>
       </c>
-      <c r="E31" s="160"/>
-      <c r="F31" s="161"/>
-      <c r="G31" s="161"/>
+      <c r="E31" s="162"/>
+      <c r="F31" s="163"/>
+      <c r="G31" s="163"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="46">
@@ -15977,9 +16454,9 @@
       <c r="D32" s="49">
         <v>5</v>
       </c>
-      <c r="E32" s="160"/>
-      <c r="F32" s="161"/>
-      <c r="G32" s="161"/>
+      <c r="E32" s="162"/>
+      <c r="F32" s="163"/>
+      <c r="G32" s="163"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="59">
@@ -15994,9 +16471,9 @@
       <c r="D33" s="88">
         <v>12.1</v>
       </c>
-      <c r="E33" s="160"/>
-      <c r="F33" s="161"/>
-      <c r="G33" s="161"/>
+      <c r="E33" s="162"/>
+      <c r="F33" s="163"/>
+      <c r="G33" s="163"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="46">
@@ -16011,9 +16488,9 @@
       <c r="D34" s="49">
         <v>10.5</v>
       </c>
-      <c r="E34" s="160"/>
-      <c r="F34" s="161"/>
-      <c r="G34" s="161"/>
+      <c r="E34" s="162"/>
+      <c r="F34" s="163"/>
+      <c r="G34" s="163"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="59">
@@ -16028,9 +16505,9 @@
       <c r="D35" s="88">
         <v>5.2</v>
       </c>
-      <c r="E35" s="160"/>
-      <c r="F35" s="161"/>
-      <c r="G35" s="161"/>
+      <c r="E35" s="162"/>
+      <c r="F35" s="163"/>
+      <c r="G35" s="163"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="46">
@@ -16045,9 +16522,9 @@
       <c r="D36" s="49">
         <v>5</v>
       </c>
-      <c r="E36" s="160"/>
-      <c r="F36" s="161"/>
-      <c r="G36" s="161"/>
+      <c r="E36" s="162"/>
+      <c r="F36" s="163"/>
+      <c r="G36" s="163"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="59">
@@ -16062,9 +16539,9 @@
       <c r="D37" s="88">
         <v>13.9</v>
       </c>
-      <c r="E37" s="160"/>
-      <c r="F37" s="161"/>
-      <c r="G37" s="161"/>
+      <c r="E37" s="162"/>
+      <c r="F37" s="163"/>
+      <c r="G37" s="163"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="46">
@@ -16079,9 +16556,9 @@
       <c r="D38" s="49">
         <v>5.5</v>
       </c>
-      <c r="E38" s="160"/>
-      <c r="F38" s="161"/>
-      <c r="G38" s="161"/>
+      <c r="E38" s="162"/>
+      <c r="F38" s="163"/>
+      <c r="G38" s="163"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="59">
@@ -16096,9 +16573,9 @@
       <c r="D39" s="88">
         <v>6.7</v>
       </c>
-      <c r="E39" s="160"/>
-      <c r="F39" s="161"/>
-      <c r="G39" s="161"/>
+      <c r="E39" s="162"/>
+      <c r="F39" s="163"/>
+      <c r="G39" s="163"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="46">
@@ -16113,9 +16590,9 @@
       <c r="D40" s="49">
         <v>16.399999999999999</v>
       </c>
-      <c r="E40" s="160"/>
-      <c r="F40" s="161"/>
-      <c r="G40" s="161"/>
+      <c r="E40" s="162"/>
+      <c r="F40" s="163"/>
+      <c r="G40" s="163"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="59">
@@ -16130,9 +16607,9 @@
       <c r="D41" s="88">
         <v>241.8</v>
       </c>
-      <c r="E41" s="160"/>
-      <c r="F41" s="161"/>
-      <c r="G41" s="161"/>
+      <c r="E41" s="162"/>
+      <c r="F41" s="163"/>
+      <c r="G41" s="163"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="46">
@@ -16147,9 +16624,9 @@
       <c r="D42" s="49">
         <v>72.900000000000006</v>
       </c>
-      <c r="E42" s="160"/>
-      <c r="F42" s="161"/>
-      <c r="G42" s="161"/>
+      <c r="E42" s="162"/>
+      <c r="F42" s="163"/>
+      <c r="G42" s="163"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="59">
@@ -16164,9 +16641,9 @@
       <c r="D43" s="88">
         <v>10.3</v>
       </c>
-      <c r="E43" s="160"/>
-      <c r="F43" s="161"/>
-      <c r="G43" s="161"/>
+      <c r="E43" s="162"/>
+      <c r="F43" s="163"/>
+      <c r="G43" s="163"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="46">
@@ -16181,9 +16658,9 @@
       <c r="D44" s="49">
         <v>5</v>
       </c>
-      <c r="E44" s="160"/>
-      <c r="F44" s="161"/>
-      <c r="G44" s="161"/>
+      <c r="E44" s="162"/>
+      <c r="F44" s="163"/>
+      <c r="G44" s="163"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="59">
@@ -16198,9 +16675,9 @@
       <c r="D45" s="88">
         <v>14</v>
       </c>
-      <c r="E45" s="160"/>
-      <c r="F45" s="161"/>
-      <c r="G45" s="161"/>
+      <c r="E45" s="162"/>
+      <c r="F45" s="163"/>
+      <c r="G45" s="163"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="46">
@@ -16215,9 +16692,9 @@
       <c r="D46" s="49">
         <v>4.4000000000000004</v>
       </c>
-      <c r="E46" s="160"/>
-      <c r="F46" s="161"/>
-      <c r="G46" s="161"/>
+      <c r="E46" s="162"/>
+      <c r="F46" s="163"/>
+      <c r="G46" s="163"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="59">
@@ -16232,9 +16709,9 @@
       <c r="D47" s="88">
         <v>6.6</v>
       </c>
-      <c r="E47" s="160"/>
-      <c r="F47" s="161"/>
-      <c r="G47" s="161"/>
+      <c r="E47" s="162"/>
+      <c r="F47" s="163"/>
+      <c r="G47" s="163"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="46">
@@ -16249,9 +16726,9 @@
       <c r="D48" s="49">
         <v>16.5</v>
       </c>
-      <c r="E48" s="160"/>
-      <c r="F48" s="161"/>
-      <c r="G48" s="161"/>
+      <c r="E48" s="162"/>
+      <c r="F48" s="163"/>
+      <c r="G48" s="163"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="46"/>
@@ -16263,9 +16740,9 @@
         <f>SUM(D12:D48)</f>
         <v>715.29999999999984</v>
       </c>
-      <c r="E49" s="160"/>
-      <c r="F49" s="161"/>
-      <c r="G49" s="161"/>
+      <c r="E49" s="162"/>
+      <c r="F49" s="163"/>
+      <c r="G49" s="163"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -16280,169 +16757,6 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="48" customWidth="1"/>
-    <col min="3" max="3" width="30.109375" style="48" customWidth="1"/>
-    <col min="4" max="4" width="19" style="48" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="48"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="41" t="s">
-        <v>240</v>
-      </c>
-      <c r="C1" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="D1" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46">
-        <v>1</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="49">
-        <f>E9</f>
-        <v>46.21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="46">
-        <v>2</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="49">
-        <f>E2</f>
-        <v>46.21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="156"/>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-    </row>
-    <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A5" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="46">
-        <v>1</v>
-      </c>
-      <c r="B6" s="41" t="s">
-        <v>264</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="49">
-        <v>15.32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="46">
-        <v>2</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>265</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="49">
-        <v>15.46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="46">
-        <v>3</v>
-      </c>
-      <c r="B8" s="41" t="s">
-        <v>266</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="49">
-        <v>15.43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="46"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="47">
-        <f>SUM(E6:E8)</f>
-        <v>46.21</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16541,43 +16855,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D2" s="41" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="49">
         <f>E9</f>
-        <v>285.2</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="46">
         <v>2</v>
       </c>
-      <c r="B3" s="44" t="s">
-        <v>59</v>
+      <c r="B3" s="42" t="s">
+        <v>16</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D3" s="41" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="49">
         <f>E2</f>
-        <v>285.2</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="156"/>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
+      <c r="A4" s="158"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
     </row>
     <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="41" t="s">
@@ -16601,16 +16915,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="D6" s="41" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="49">
-        <v>97.9</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -16618,16 +16932,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="D7" s="41" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="49">
-        <v>162.9</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -16635,16 +16949,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="D8" s="41" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="49">
-        <v>24.4</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -16658,7 +16972,7 @@
       </c>
       <c r="E9" s="47">
         <f>SUM(E6:E8)</f>
-        <v>285.2</v>
+        <v>46.21</v>
       </c>
     </row>
   </sheetData>
@@ -16670,6 +16984,169 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="19" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="46">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49">
+        <f>E9</f>
+        <v>285.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="46">
+        <v>2</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>273</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="49">
+        <f>E2</f>
+        <v>285.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="158"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
+    </row>
+    <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A5" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="46">
+        <v>1</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="49">
+        <v>97.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
+        <v>2</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="49">
+        <v>162.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="46">
+        <v>3</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="49">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="46"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="47">
+        <f>SUM(E6:E8)</f>
+        <v>285.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:E4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -16809,7 +17286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -16991,7 +17468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -17011,11 +17488,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="89"/>
-      <c r="C1" s="166" t="s">
+      <c r="C1" s="168" t="s">
         <v>240</v>
       </c>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
       <c r="F1" s="92" t="s">
         <v>303</v>
       </c>
@@ -17030,11 +17507,11 @@
       <c r="B2" s="62" t="s">
         <v>305</v>
       </c>
-      <c r="C2" s="171" t="s">
+      <c r="C2" s="173" t="s">
         <v>304</v>
       </c>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
       <c r="F2" s="61" t="s">
         <v>346</v>
       </c>
@@ -17050,11 +17527,11 @@
       <c r="B3" s="92" t="s">
         <v>305</v>
       </c>
-      <c r="C3" s="167" t="s">
+      <c r="C3" s="169" t="s">
         <v>304</v>
       </c>
-      <c r="D3" s="167"/>
-      <c r="E3" s="167"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="58" t="s">
         <v>267</v>
       </c>
@@ -17070,11 +17547,11 @@
       <c r="B4" s="62" t="s">
         <v>305</v>
       </c>
-      <c r="C4" s="171" t="s">
+      <c r="C4" s="173" t="s">
         <v>304</v>
       </c>
-      <c r="D4" s="171"/>
-      <c r="E4" s="171"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="173"/>
       <c r="F4" s="61" t="s">
         <v>218</v>
       </c>
@@ -17084,11 +17561,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="156"/>
-      <c r="B5" s="156"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="156"/>
-      <c r="E5" s="157"/>
+      <c r="A5" s="158"/>
+      <c r="B5" s="158"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="159"/>
       <c r="F5" s="92" t="s">
         <v>216</v>
       </c>
@@ -17113,8 +17590,8 @@
       <c r="E6" s="95" t="s">
         <v>326</v>
       </c>
-      <c r="F6" s="162"/>
-      <c r="G6" s="163"/>
+      <c r="F6" s="164"/>
+      <c r="G6" s="165"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="106">
@@ -17132,8 +17609,8 @@
       <c r="E7" s="107">
         <v>14.6</v>
       </c>
-      <c r="F7" s="164"/>
-      <c r="G7" s="165"/>
+      <c r="F7" s="166"/>
+      <c r="G7" s="167"/>
     </row>
     <row r="8" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="106">
@@ -17151,8 +17628,8 @@
       <c r="E8" s="107">
         <v>7.1</v>
       </c>
-      <c r="F8" s="164"/>
-      <c r="G8" s="165"/>
+      <c r="F8" s="166"/>
+      <c r="G8" s="167"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="106">
@@ -17170,8 +17647,8 @@
       <c r="E9" s="107">
         <v>12.8</v>
       </c>
-      <c r="F9" s="164"/>
-      <c r="G9" s="165"/>
+      <c r="F9" s="166"/>
+      <c r="G9" s="167"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="106">
@@ -17189,8 +17666,8 @@
       <c r="E10" s="107">
         <v>16.100000000000001</v>
       </c>
-      <c r="F10" s="164"/>
-      <c r="G10" s="165"/>
+      <c r="F10" s="166"/>
+      <c r="G10" s="167"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="106">
@@ -17208,8 +17685,8 @@
       <c r="E11" s="107">
         <v>7.9</v>
       </c>
-      <c r="F11" s="164"/>
-      <c r="G11" s="165"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="167"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="106">
@@ -17227,8 +17704,8 @@
       <c r="E12" s="107">
         <v>7.7</v>
       </c>
-      <c r="F12" s="164"/>
-      <c r="G12" s="165"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="167"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="106">
@@ -17246,8 +17723,8 @@
       <c r="E13" s="107">
         <v>12.5</v>
       </c>
-      <c r="F13" s="164"/>
-      <c r="G13" s="165"/>
+      <c r="F13" s="166"/>
+      <c r="G13" s="167"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="106">
@@ -17265,8 +17742,8 @@
       <c r="E14" s="107">
         <v>12</v>
       </c>
-      <c r="F14" s="164"/>
-      <c r="G14" s="165"/>
+      <c r="F14" s="166"/>
+      <c r="G14" s="167"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="106">
@@ -17284,8 +17761,8 @@
       <c r="E15" s="107">
         <v>7.6</v>
       </c>
-      <c r="F15" s="164"/>
-      <c r="G15" s="165"/>
+      <c r="F15" s="166"/>
+      <c r="G15" s="167"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="106">
@@ -17303,8 +17780,8 @@
       <c r="E16" s="107">
         <v>5.3</v>
       </c>
-      <c r="F16" s="164"/>
-      <c r="G16" s="165"/>
+      <c r="F16" s="166"/>
+      <c r="G16" s="167"/>
     </row>
     <row r="17" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="106">
@@ -17322,8 +17799,8 @@
       <c r="E17" s="109">
         <v>19.3</v>
       </c>
-      <c r="F17" s="164"/>
-      <c r="G17" s="165"/>
+      <c r="F17" s="166"/>
+      <c r="G17" s="167"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="106">
@@ -17341,8 +17818,8 @@
       <c r="E18" s="107">
         <v>12.7</v>
       </c>
-      <c r="F18" s="164"/>
-      <c r="G18" s="165"/>
+      <c r="F18" s="166"/>
+      <c r="G18" s="167"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="106">
@@ -17360,8 +17837,8 @@
       <c r="E19" s="107">
         <v>9.6999999999999993</v>
       </c>
-      <c r="F19" s="164"/>
-      <c r="G19" s="165"/>
+      <c r="F19" s="166"/>
+      <c r="G19" s="167"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="106">
@@ -17379,8 +17856,8 @@
       <c r="E20" s="107">
         <v>21.8</v>
       </c>
-      <c r="F20" s="164"/>
-      <c r="G20" s="165"/>
+      <c r="F20" s="166"/>
+      <c r="G20" s="167"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="106">
@@ -17398,8 +17875,8 @@
       <c r="E21" s="107">
         <v>8.5</v>
       </c>
-      <c r="F21" s="164"/>
-      <c r="G21" s="165"/>
+      <c r="F21" s="166"/>
+      <c r="G21" s="167"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="106">
@@ -17417,8 +17894,8 @@
       <c r="E22" s="107">
         <v>15.7</v>
       </c>
-      <c r="F22" s="164"/>
-      <c r="G22" s="165"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="167"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="106">
@@ -17436,8 +17913,8 @@
       <c r="E23" s="107">
         <v>9.4</v>
       </c>
-      <c r="F23" s="164"/>
-      <c r="G23" s="165"/>
+      <c r="F23" s="166"/>
+      <c r="G23" s="167"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="106">
@@ -17455,8 +17932,8 @@
       <c r="E24" s="107">
         <v>3.7</v>
       </c>
-      <c r="F24" s="164"/>
-      <c r="G24" s="165"/>
+      <c r="F24" s="166"/>
+      <c r="G24" s="167"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="106">
@@ -17474,8 +17951,8 @@
       <c r="E25" s="107">
         <v>12.8</v>
       </c>
-      <c r="F25" s="164"/>
-      <c r="G25" s="165"/>
+      <c r="F25" s="166"/>
+      <c r="G25" s="167"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="46"/>
@@ -17488,8 +17965,8 @@
         <f>SUM(E7:E25)</f>
         <v>217.2</v>
       </c>
-      <c r="F26" s="164"/>
-      <c r="G26" s="165"/>
+      <c r="F26" s="166"/>
+      <c r="G26" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -17508,7 +17985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -17528,11 +18005,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="89"/>
-      <c r="C1" s="166" t="s">
+      <c r="C1" s="168" t="s">
         <v>240</v>
       </c>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
       <c r="F1" s="41" t="s">
         <v>303</v>
       </c>
@@ -17547,11 +18024,11 @@
       <c r="B2" s="92">
         <v>479</v>
       </c>
-      <c r="C2" s="167" t="s">
+      <c r="C2" s="169" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="167"/>
-      <c r="E2" s="167"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
       <c r="F2" s="58" t="s">
         <v>231</v>
       </c>
@@ -17561,11 +18038,11 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="156"/>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="157"/>
+      <c r="A3" s="158"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="159"/>
       <c r="F3" s="41" t="s">
         <v>216</v>
       </c>
@@ -17590,8 +18067,8 @@
       <c r="E4" s="95" t="s">
         <v>326</v>
       </c>
-      <c r="F4" s="162"/>
-      <c r="G4" s="163"/>
+      <c r="F4" s="164"/>
+      <c r="G4" s="165"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="106">
@@ -17609,8 +18086,8 @@
       <c r="E5" s="107">
         <v>41.3</v>
       </c>
-      <c r="F5" s="164"/>
-      <c r="G5" s="165"/>
+      <c r="F5" s="166"/>
+      <c r="G5" s="167"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="106">
@@ -17628,8 +18105,8 @@
       <c r="E6" s="107">
         <v>92.3</v>
       </c>
-      <c r="F6" s="164"/>
-      <c r="G6" s="165"/>
+      <c r="F6" s="166"/>
+      <c r="G6" s="167"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="106">
@@ -17647,8 +18124,8 @@
       <c r="E7" s="107">
         <v>44.6</v>
       </c>
-      <c r="F7" s="164"/>
-      <c r="G7" s="165"/>
+      <c r="F7" s="166"/>
+      <c r="G7" s="167"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="106">
@@ -17666,8 +18143,8 @@
       <c r="E8" s="107">
         <v>1.7</v>
       </c>
-      <c r="F8" s="164"/>
-      <c r="G8" s="165"/>
+      <c r="F8" s="166"/>
+      <c r="G8" s="167"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="106">
@@ -17685,8 +18162,8 @@
       <c r="E9" s="107">
         <v>10.8</v>
       </c>
-      <c r="F9" s="164"/>
-      <c r="G9" s="165"/>
+      <c r="F9" s="166"/>
+      <c r="G9" s="167"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="106">
@@ -17704,8 +18181,8 @@
       <c r="E10" s="107">
         <v>132.69999999999999</v>
       </c>
-      <c r="F10" s="164"/>
-      <c r="G10" s="165"/>
+      <c r="F10" s="166"/>
+      <c r="G10" s="167"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="106">
@@ -17723,8 +18200,8 @@
       <c r="E11" s="107">
         <v>163.5</v>
       </c>
-      <c r="F11" s="164"/>
-      <c r="G11" s="165"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="167"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="106">
@@ -17742,8 +18219,8 @@
       <c r="E12" s="107">
         <v>75.099999999999994</v>
       </c>
-      <c r="F12" s="164"/>
-      <c r="G12" s="165"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="167"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="106">
@@ -17761,8 +18238,8 @@
       <c r="E13" s="107">
         <v>44.2</v>
       </c>
-      <c r="F13" s="164"/>
-      <c r="G13" s="165"/>
+      <c r="F13" s="166"/>
+      <c r="G13" s="167"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="106">
@@ -17780,8 +18257,8 @@
       <c r="E14" s="107">
         <v>18.399999999999999</v>
       </c>
-      <c r="F14" s="164"/>
-      <c r="G14" s="165"/>
+      <c r="F14" s="166"/>
+      <c r="G14" s="167"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="106">
@@ -17799,8 +18276,8 @@
       <c r="E15" s="107">
         <v>281.5</v>
       </c>
-      <c r="F15" s="164"/>
-      <c r="G15" s="165"/>
+      <c r="F15" s="166"/>
+      <c r="G15" s="167"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="106">
@@ -17818,8 +18295,8 @@
       <c r="E16" s="107">
         <v>66.099999999999994</v>
       </c>
-      <c r="F16" s="164"/>
-      <c r="G16" s="165"/>
+      <c r="F16" s="166"/>
+      <c r="G16" s="167"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="106">
@@ -17837,8 +18314,8 @@
       <c r="E17" s="107">
         <v>20.8</v>
       </c>
-      <c r="F17" s="164"/>
-      <c r="G17" s="165"/>
+      <c r="F17" s="166"/>
+      <c r="G17" s="167"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="106">
@@ -17856,8 +18333,8 @@
       <c r="E18" s="107">
         <v>69.3</v>
       </c>
-      <c r="F18" s="164"/>
-      <c r="G18" s="165"/>
+      <c r="F18" s="166"/>
+      <c r="G18" s="167"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="106">
@@ -17875,8 +18352,8 @@
       <c r="E19" s="107">
         <v>23.5</v>
       </c>
-      <c r="F19" s="164"/>
-      <c r="G19" s="165"/>
+      <c r="F19" s="166"/>
+      <c r="G19" s="167"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="106">
@@ -17894,8 +18371,8 @@
       <c r="E20" s="107">
         <v>85.1</v>
       </c>
-      <c r="F20" s="164"/>
-      <c r="G20" s="165"/>
+      <c r="F20" s="166"/>
+      <c r="G20" s="167"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="106">
@@ -17913,8 +18390,8 @@
       <c r="E21" s="111">
         <v>55.3</v>
       </c>
-      <c r="F21" s="164"/>
-      <c r="G21" s="165"/>
+      <c r="F21" s="166"/>
+      <c r="G21" s="167"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="106">
@@ -17932,8 +18409,8 @@
       <c r="E22" s="107">
         <v>159.9</v>
       </c>
-      <c r="F22" s="164"/>
-      <c r="G22" s="165"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="167"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="106">
@@ -17951,8 +18428,8 @@
       <c r="E23" s="107">
         <v>217.5</v>
       </c>
-      <c r="F23" s="164"/>
-      <c r="G23" s="165"/>
+      <c r="F23" s="166"/>
+      <c r="G23" s="167"/>
     </row>
     <row r="24" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="106">
@@ -17970,8 +18447,8 @@
       <c r="E24" s="109">
         <v>497.3</v>
       </c>
-      <c r="F24" s="164"/>
-      <c r="G24" s="165"/>
+      <c r="F24" s="166"/>
+      <c r="G24" s="167"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="106">
@@ -17989,8 +18466,8 @@
       <c r="E25" s="111">
         <v>53.4</v>
       </c>
-      <c r="F25" s="164"/>
-      <c r="G25" s="165"/>
+      <c r="F25" s="166"/>
+      <c r="G25" s="167"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="106">
@@ -18008,8 +18485,8 @@
       <c r="E26" s="107">
         <v>12.3</v>
       </c>
-      <c r="F26" s="164"/>
-      <c r="G26" s="165"/>
+      <c r="F26" s="166"/>
+      <c r="G26" s="167"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="106">
@@ -18027,8 +18504,8 @@
       <c r="E27" s="107">
         <v>30.1</v>
       </c>
-      <c r="F27" s="164"/>
-      <c r="G27" s="165"/>
+      <c r="F27" s="166"/>
+      <c r="G27" s="167"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="106">
@@ -18046,8 +18523,8 @@
       <c r="E28" s="107">
         <v>11.3</v>
       </c>
-      <c r="F28" s="164"/>
-      <c r="G28" s="165"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="167"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="106">
@@ -18065,8 +18542,8 @@
       <c r="E29" s="107">
         <v>6.1</v>
       </c>
-      <c r="F29" s="164"/>
-      <c r="G29" s="165"/>
+      <c r="F29" s="166"/>
+      <c r="G29" s="167"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="106">
@@ -18084,8 +18561,8 @@
       <c r="E30" s="107">
         <v>70.2</v>
       </c>
-      <c r="F30" s="164"/>
-      <c r="G30" s="165"/>
+      <c r="F30" s="166"/>
+      <c r="G30" s="167"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="106">
@@ -18103,8 +18580,8 @@
       <c r="E31" s="107">
         <v>50.1</v>
       </c>
-      <c r="F31" s="164"/>
-      <c r="G31" s="165"/>
+      <c r="F31" s="166"/>
+      <c r="G31" s="167"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="106">
@@ -18122,8 +18599,8 @@
       <c r="E32" s="107">
         <v>43.6</v>
       </c>
-      <c r="F32" s="164"/>
-      <c r="G32" s="165"/>
+      <c r="F32" s="166"/>
+      <c r="G32" s="167"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="106">
@@ -18141,8 +18618,8 @@
       <c r="E33" s="107">
         <v>69.400000000000006</v>
       </c>
-      <c r="F33" s="164"/>
-      <c r="G33" s="165"/>
+      <c r="F33" s="166"/>
+      <c r="G33" s="167"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="106">
@@ -18160,8 +18637,8 @@
       <c r="E34" s="107">
         <v>168.7</v>
       </c>
-      <c r="F34" s="164"/>
-      <c r="G34" s="165"/>
+      <c r="F34" s="166"/>
+      <c r="G34" s="167"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="106">
@@ -18179,8 +18656,8 @@
       <c r="E35" s="107">
         <v>66.900000000000006</v>
       </c>
-      <c r="F35" s="164"/>
-      <c r="G35" s="165"/>
+      <c r="F35" s="166"/>
+      <c r="G35" s="167"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="106">
@@ -18198,8 +18675,8 @@
       <c r="E36" s="107">
         <v>198</v>
       </c>
-      <c r="F36" s="164"/>
-      <c r="G36" s="165"/>
+      <c r="F36" s="166"/>
+      <c r="G36" s="167"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="106">
@@ -18217,8 +18694,8 @@
       <c r="E37" s="107">
         <v>31.3</v>
       </c>
-      <c r="F37" s="164"/>
-      <c r="G37" s="165"/>
+      <c r="F37" s="166"/>
+      <c r="G37" s="167"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="106">
@@ -18236,8 +18713,8 @@
       <c r="E38" s="107">
         <v>487.6</v>
       </c>
-      <c r="F38" s="164"/>
-      <c r="G38" s="165"/>
+      <c r="F38" s="166"/>
+      <c r="G38" s="167"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="106">
@@ -18255,8 +18732,8 @@
       <c r="E39" s="113">
         <v>34.4</v>
       </c>
-      <c r="F39" s="164"/>
-      <c r="G39" s="165"/>
+      <c r="F39" s="166"/>
+      <c r="G39" s="167"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="46"/>
@@ -18269,8 +18746,8 @@
         <f>SUM(E5:E39)</f>
         <v>3434.3</v>
       </c>
-      <c r="F40" s="164"/>
-      <c r="G40" s="165"/>
+      <c r="F40" s="166"/>
+      <c r="G40" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -18287,7 +18764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -18306,10 +18783,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="55"/>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="152" t="s">
         <v>240</v>
       </c>
-      <c r="D1" s="152"/>
+      <c r="D1" s="154"/>
       <c r="E1" s="41" t="s">
         <v>303</v>
       </c>
@@ -18324,10 +18801,10 @@
       <c r="B2" s="57">
         <v>476</v>
       </c>
-      <c r="C2" s="153" t="s">
+      <c r="C2" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="155"/>
+      <c r="D2" s="157"/>
       <c r="E2" s="58" t="s">
         <v>236</v>
       </c>
@@ -18343,10 +18820,10 @@
       <c r="B3" s="60">
         <v>479</v>
       </c>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="169"/>
+      <c r="D3" s="171"/>
       <c r="E3" s="61" t="s">
         <v>231</v>
       </c>
@@ -18362,10 +18839,10 @@
       <c r="B4" s="55" t="s">
         <v>305</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="155" t="s">
         <v>304</v>
       </c>
-      <c r="D4" s="155"/>
+      <c r="D4" s="157"/>
       <c r="E4" s="58" t="s">
         <v>267</v>
       </c>
@@ -18381,10 +18858,10 @@
       <c r="B5" s="63" t="s">
         <v>305</v>
       </c>
-      <c r="C5" s="168" t="s">
+      <c r="C5" s="170" t="s">
         <v>304</v>
       </c>
-      <c r="D5" s="169"/>
+      <c r="D5" s="171"/>
       <c r="E5" s="61" t="s">
         <v>218</v>
       </c>
@@ -18394,10 +18871,10 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="156"/>
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="157"/>
+      <c r="A6" s="158"/>
+      <c r="B6" s="158"/>
+      <c r="C6" s="158"/>
+      <c r="D6" s="159"/>
       <c r="E6" s="41" t="s">
         <v>216</v>
       </c>
@@ -18419,8 +18896,8 @@
       <c r="D7" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="E7" s="162"/>
-      <c r="F7" s="163"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="165"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="59">
@@ -18435,8 +18912,8 @@
       <c r="D8" s="88">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E8" s="164"/>
-      <c r="F8" s="165"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="167"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="46">
@@ -18451,8 +18928,8 @@
       <c r="D9" s="49">
         <v>15.2</v>
       </c>
-      <c r="E9" s="164"/>
-      <c r="F9" s="165"/>
+      <c r="E9" s="166"/>
+      <c r="F9" s="167"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="46">
@@ -18467,8 +18944,8 @@
       <c r="D10" s="49">
         <v>18.100000000000001</v>
       </c>
-      <c r="E10" s="164"/>
-      <c r="F10" s="165"/>
+      <c r="E10" s="166"/>
+      <c r="F10" s="167"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="46">
@@ -18483,8 +18960,8 @@
       <c r="D11" s="49">
         <v>18.600000000000001</v>
       </c>
-      <c r="E11" s="164"/>
-      <c r="F11" s="165"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="167"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="46">
@@ -18499,8 +18976,8 @@
       <c r="D12" s="49">
         <v>10.5</v>
       </c>
-      <c r="E12" s="164"/>
-      <c r="F12" s="165"/>
+      <c r="E12" s="166"/>
+      <c r="F12" s="167"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="59">
@@ -18515,8 +18992,8 @@
       <c r="D13" s="88">
         <v>4.8</v>
       </c>
-      <c r="E13" s="164"/>
-      <c r="F13" s="165"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="167"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="46">
@@ -18531,8 +19008,8 @@
       <c r="D14" s="49">
         <v>13.5</v>
       </c>
-      <c r="E14" s="164"/>
-      <c r="F14" s="165"/>
+      <c r="E14" s="166"/>
+      <c r="F14" s="167"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="59">
@@ -18547,8 +19024,8 @@
       <c r="D15" s="88">
         <v>13.6</v>
       </c>
-      <c r="E15" s="164"/>
-      <c r="F15" s="165"/>
+      <c r="E15" s="166"/>
+      <c r="F15" s="167"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="46">
@@ -18563,8 +19040,8 @@
       <c r="D16" s="49">
         <v>6.5</v>
       </c>
-      <c r="E16" s="164"/>
-      <c r="F16" s="165"/>
+      <c r="E16" s="166"/>
+      <c r="F16" s="167"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="59">
@@ -18579,8 +19056,8 @@
       <c r="D17" s="88">
         <v>16.399999999999999</v>
       </c>
-      <c r="E17" s="164"/>
-      <c r="F17" s="165"/>
+      <c r="E17" s="166"/>
+      <c r="F17" s="167"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="46">
@@ -18595,8 +19072,8 @@
       <c r="D18" s="49">
         <v>5</v>
       </c>
-      <c r="E18" s="164"/>
-      <c r="F18" s="165"/>
+      <c r="E18" s="166"/>
+      <c r="F18" s="167"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="59">
@@ -18611,8 +19088,8 @@
       <c r="D19" s="88">
         <v>13.9</v>
       </c>
-      <c r="E19" s="164"/>
-      <c r="F19" s="165"/>
+      <c r="E19" s="166"/>
+      <c r="F19" s="167"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="46">
@@ -18627,8 +19104,8 @@
       <c r="D20" s="49">
         <v>15.3</v>
       </c>
-      <c r="E20" s="164"/>
-      <c r="F20" s="165"/>
+      <c r="E20" s="166"/>
+      <c r="F20" s="167"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="46">
@@ -18643,8 +19120,8 @@
       <c r="D21" s="49">
         <v>10.4</v>
       </c>
-      <c r="E21" s="164"/>
-      <c r="F21" s="165"/>
+      <c r="E21" s="166"/>
+      <c r="F21" s="167"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="46">
@@ -18659,8 +19136,8 @@
       <c r="D22" s="49">
         <v>19.100000000000001</v>
       </c>
-      <c r="E22" s="164"/>
-      <c r="F22" s="165"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="167"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="46">
@@ -18675,8 +19152,8 @@
       <c r="D23" s="49">
         <v>18.600000000000001</v>
       </c>
-      <c r="E23" s="164"/>
-      <c r="F23" s="165"/>
+      <c r="E23" s="166"/>
+      <c r="F23" s="167"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="46">
@@ -18691,8 +19168,8 @@
       <c r="D24" s="49">
         <v>5</v>
       </c>
-      <c r="E24" s="164"/>
-      <c r="F24" s="165"/>
+      <c r="E24" s="166"/>
+      <c r="F24" s="167"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="59">
@@ -18707,8 +19184,8 @@
       <c r="D25" s="88">
         <v>13.7</v>
       </c>
-      <c r="E25" s="164"/>
-      <c r="F25" s="165"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="167"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="46">
@@ -18723,8 +19200,8 @@
       <c r="D26" s="49">
         <v>6.7</v>
       </c>
-      <c r="E26" s="164"/>
-      <c r="F26" s="165"/>
+      <c r="E26" s="166"/>
+      <c r="F26" s="167"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="59">
@@ -18739,8 +19216,8 @@
       <c r="D27" s="88">
         <v>16.8</v>
       </c>
-      <c r="E27" s="164"/>
-      <c r="F27" s="165"/>
+      <c r="E27" s="166"/>
+      <c r="F27" s="167"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="46">
@@ -18755,8 +19232,8 @@
       <c r="D28" s="49">
         <v>5</v>
       </c>
-      <c r="E28" s="164"/>
-      <c r="F28" s="165"/>
+      <c r="E28" s="166"/>
+      <c r="F28" s="167"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="59">
@@ -18771,8 +19248,8 @@
       <c r="D29" s="88">
         <v>12.1</v>
       </c>
-      <c r="E29" s="164"/>
-      <c r="F29" s="165"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="167"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="46">
@@ -18787,8 +19264,8 @@
       <c r="D30" s="49">
         <v>15.3</v>
       </c>
-      <c r="E30" s="164"/>
-      <c r="F30" s="165"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="167"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="46">
@@ -18803,8 +19280,8 @@
       <c r="D31" s="49">
         <v>28.6</v>
       </c>
-      <c r="E31" s="164"/>
-      <c r="F31" s="165"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="167"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="46">
@@ -18819,8 +19296,8 @@
       <c r="D32" s="49">
         <v>19.100000000000001</v>
       </c>
-      <c r="E32" s="164"/>
-      <c r="F32" s="165"/>
+      <c r="E32" s="166"/>
+      <c r="F32" s="167"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="46">
@@ -18835,8 +19312,8 @@
       <c r="D33" s="49">
         <v>10.5</v>
       </c>
-      <c r="E33" s="164"/>
-      <c r="F33" s="165"/>
+      <c r="E33" s="166"/>
+      <c r="F33" s="167"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="59">
@@ -18851,8 +19328,8 @@
       <c r="D34" s="88">
         <v>5.2</v>
       </c>
-      <c r="E34" s="164"/>
-      <c r="F34" s="165"/>
+      <c r="E34" s="166"/>
+      <c r="F34" s="167"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="46">
@@ -18867,8 +19344,8 @@
       <c r="D35" s="49">
         <v>5</v>
       </c>
-      <c r="E35" s="164"/>
-      <c r="F35" s="165"/>
+      <c r="E35" s="166"/>
+      <c r="F35" s="167"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="59">
@@ -18883,8 +19360,8 @@
       <c r="D36" s="88">
         <v>13.9</v>
       </c>
-      <c r="E36" s="164"/>
-      <c r="F36" s="165"/>
+      <c r="E36" s="166"/>
+      <c r="F36" s="167"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="46">
@@ -18899,8 +19376,8 @@
       <c r="D37" s="49">
         <v>5.5</v>
       </c>
-      <c r="E37" s="164"/>
-      <c r="F37" s="165"/>
+      <c r="E37" s="166"/>
+      <c r="F37" s="167"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="59">
@@ -18915,8 +19392,8 @@
       <c r="D38" s="88">
         <v>6.7</v>
       </c>
-      <c r="E38" s="164"/>
-      <c r="F38" s="165"/>
+      <c r="E38" s="166"/>
+      <c r="F38" s="167"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="46">
@@ -18931,8 +19408,8 @@
       <c r="D39" s="49">
         <v>16.399999999999999</v>
       </c>
-      <c r="E39" s="164"/>
-      <c r="F39" s="165"/>
+      <c r="E39" s="166"/>
+      <c r="F39" s="167"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="59">
@@ -18947,8 +19424,8 @@
       <c r="D40" s="88">
         <v>241.8</v>
       </c>
-      <c r="E40" s="164"/>
-      <c r="F40" s="165"/>
+      <c r="E40" s="166"/>
+      <c r="F40" s="167"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="46">
@@ -18963,8 +19440,8 @@
       <c r="D41" s="49">
         <v>72.900000000000006</v>
       </c>
-      <c r="E41" s="164"/>
-      <c r="F41" s="165"/>
+      <c r="E41" s="166"/>
+      <c r="F41" s="167"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="59">
@@ -18979,8 +19456,8 @@
       <c r="D42" s="88">
         <v>10.3</v>
       </c>
-      <c r="E42" s="164"/>
-      <c r="F42" s="165"/>
+      <c r="E42" s="166"/>
+      <c r="F42" s="167"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="46">
@@ -18995,8 +19472,8 @@
       <c r="D43" s="49">
         <v>5</v>
       </c>
-      <c r="E43" s="164"/>
-      <c r="F43" s="165"/>
+      <c r="E43" s="166"/>
+      <c r="F43" s="167"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="59">
@@ -19011,8 +19488,8 @@
       <c r="D44" s="88">
         <v>14</v>
       </c>
-      <c r="E44" s="164"/>
-      <c r="F44" s="165"/>
+      <c r="E44" s="166"/>
+      <c r="F44" s="167"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="46">
@@ -19027,8 +19504,8 @@
       <c r="D45" s="49">
         <v>4.4000000000000004</v>
       </c>
-      <c r="E45" s="164"/>
-      <c r="F45" s="165"/>
+      <c r="E45" s="166"/>
+      <c r="F45" s="167"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="59">
@@ -19043,8 +19520,8 @@
       <c r="D46" s="88">
         <v>6.6</v>
       </c>
-      <c r="E46" s="164"/>
-      <c r="F46" s="165"/>
+      <c r="E46" s="166"/>
+      <c r="F46" s="167"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="46">
@@ -19059,8 +19536,8 @@
       <c r="D47" s="49">
         <v>16.5</v>
       </c>
-      <c r="E47" s="164"/>
-      <c r="F47" s="165"/>
+      <c r="E47" s="166"/>
+      <c r="F47" s="167"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="46"/>
@@ -19072,8 +19549,8 @@
         <f>SUM(D9:D47)</f>
         <v>756.49999999999989</v>
       </c>
-      <c r="E48" s="164"/>
-      <c r="F48" s="165"/>
+      <c r="E48" s="166"/>
+      <c r="F48" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -19089,7 +19566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -19107,10 +19584,10 @@
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="150" t="s">
+      <c r="B1" s="152" t="s">
         <v>240</v>
       </c>
-      <c r="C1" s="152"/>
+      <c r="C1" s="154"/>
       <c r="D1" s="41" t="s">
         <v>215</v>
       </c>
@@ -19125,10 +19602,10 @@
       <c r="A2" s="46">
         <v>1</v>
       </c>
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="174" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="173"/>
+      <c r="C2" s="175"/>
       <c r="D2" s="43" t="s">
         <v>270</v>
       </c>
@@ -19141,12 +19618,12 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="163"/>
-      <c r="B3" s="163"/>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
+      <c r="A3" s="165"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
     </row>
     <row r="4" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A4" s="41" t="s">
@@ -19164,7 +19641,7 @@
       <c r="E4" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="174"/>
+      <c r="F4" s="176"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="46">
@@ -19182,7 +19659,7 @@
       <c r="E5" s="49">
         <v>97.9</v>
       </c>
-      <c r="F5" s="174"/>
+      <c r="F5" s="176"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="46">
@@ -19200,7 +19677,7 @@
       <c r="E6" s="49">
         <v>162.9</v>
       </c>
-      <c r="F6" s="174"/>
+      <c r="F6" s="176"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="46">
@@ -19218,7 +19695,7 @@
       <c r="E7" s="49">
         <v>24.4</v>
       </c>
-      <c r="F7" s="174"/>
+      <c r="F7" s="176"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="46"/>
@@ -19233,7 +19710,7 @@
         <f>SUM(E5:E7)</f>
         <v>285.2</v>
       </c>
-      <c r="F8" s="174"/>
+      <c r="F8" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -19246,7 +19723,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -19374,7 +19851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -19547,16 +20024,16 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="2:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="144" t="s">
+      <c r="B1" s="146" t="s">
         <v>328</v>
       </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="30" t="s">
@@ -23625,16 +24102,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="144" t="s">
+      <c r="B1" s="146" t="s">
         <v>261</v>
       </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B3" s="30" t="s">
@@ -23664,10 +24141,10 @@
       <c r="I4" s="27">
         <v>4</v>
       </c>
-      <c r="Q4" s="146" t="s">
+      <c r="Q4" s="148" t="s">
         <v>232</v>
       </c>
-      <c r="R4" s="147"/>
+      <c r="R4" s="149"/>
     </row>
     <row r="5" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="29" t="s">
@@ -24182,10 +24659,10 @@
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="Q25" s="148">
+      <c r="Q25" s="150">
         <v>855</v>
       </c>
-      <c r="R25" s="149"/>
+      <c r="R25" s="151"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B26" s="31" t="s">
@@ -24841,11 +25318,11 @@
       <c r="B1" s="103" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="152" t="s">
         <v>315</v>
       </c>
-      <c r="D1" s="151"/>
-      <c r="E1" s="152"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="154"/>
       <c r="F1" s="104" t="s">
         <v>269</v>
       </c>
@@ -24863,11 +25340,11 @@
       <c r="B2" s="103">
         <v>121</v>
       </c>
-      <c r="C2" s="153" t="s">
+      <c r="C2" s="155" t="s">
         <v>377</v>
       </c>
-      <c r="D2" s="154"/>
-      <c r="E2" s="155"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="157"/>
       <c r="F2" s="58" t="s">
         <v>218</v>
       </c>
@@ -24880,12 +25357,12 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="156"/>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="157"/>
+      <c r="A3" s="158"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="159"/>
       <c r="G3" s="104" t="s">
         <v>216</v>
       </c>
@@ -24910,9 +25387,9 @@
       <c r="E4" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159"/>
-      <c r="H4" s="159"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="161"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="114">
@@ -24930,9 +25407,9 @@
       <c r="E5" s="115">
         <v>7.1</v>
       </c>
-      <c r="F5" s="160"/>
-      <c r="G5" s="161"/>
-      <c r="H5" s="161"/>
+      <c r="F5" s="162"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="163"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="114">
@@ -24950,9 +25427,9 @@
       <c r="E6" s="116">
         <v>16.100000000000001</v>
       </c>
-      <c r="F6" s="160"/>
-      <c r="G6" s="161"/>
-      <c r="H6" s="161"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="163"/>
+      <c r="H6" s="163"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="114">
@@ -24970,9 +25447,9 @@
       <c r="E7" s="115">
         <v>7.9</v>
       </c>
-      <c r="F7" s="160"/>
-      <c r="G7" s="161"/>
-      <c r="H7" s="161"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="163"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="114">
@@ -24990,9 +25467,9 @@
       <c r="E8" s="116">
         <v>7.7</v>
       </c>
-      <c r="F8" s="160"/>
-      <c r="G8" s="161"/>
-      <c r="H8" s="161"/>
+      <c r="F8" s="162"/>
+      <c r="G8" s="163"/>
+      <c r="H8" s="163"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="114">
@@ -25010,9 +25487,9 @@
       <c r="E9" s="115">
         <v>12.5</v>
       </c>
-      <c r="F9" s="160"/>
-      <c r="G9" s="161"/>
-      <c r="H9" s="161"/>
+      <c r="F9" s="162"/>
+      <c r="G9" s="163"/>
+      <c r="H9" s="163"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="114">
@@ -25030,9 +25507,9 @@
       <c r="E10" s="116">
         <v>12</v>
       </c>
-      <c r="F10" s="160"/>
-      <c r="G10" s="161"/>
-      <c r="H10" s="161"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="163"/>
+      <c r="H10" s="163"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="114">
@@ -25050,9 +25527,9 @@
       <c r="E11" s="116">
         <v>7.6</v>
       </c>
-      <c r="F11" s="160"/>
-      <c r="G11" s="161"/>
-      <c r="H11" s="161"/>
+      <c r="F11" s="162"/>
+      <c r="G11" s="163"/>
+      <c r="H11" s="163"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="114">
@@ -25070,9 +25547,9 @@
       <c r="E12" s="116">
         <v>5.3</v>
       </c>
-      <c r="F12" s="160"/>
-      <c r="G12" s="161"/>
-      <c r="H12" s="161"/>
+      <c r="F12" s="162"/>
+      <c r="G12" s="163"/>
+      <c r="H12" s="163"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="114">
@@ -25090,9 +25567,9 @@
       <c r="E13" s="116">
         <v>9.6999999999999993</v>
       </c>
-      <c r="F13" s="160"/>
-      <c r="G13" s="161"/>
-      <c r="H13" s="161"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="163"/>
+      <c r="H13" s="163"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="114">
@@ -25110,9 +25587,9 @@
       <c r="E14" s="115">
         <v>21.8</v>
       </c>
-      <c r="F14" s="160"/>
-      <c r="G14" s="161"/>
-      <c r="H14" s="161"/>
+      <c r="F14" s="162"/>
+      <c r="G14" s="163"/>
+      <c r="H14" s="163"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="114">
@@ -25130,9 +25607,9 @@
       <c r="E15" s="116">
         <v>8.5</v>
       </c>
-      <c r="F15" s="160"/>
-      <c r="G15" s="161"/>
-      <c r="H15" s="161"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="163"/>
+      <c r="H15" s="163"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="114">
@@ -25150,9 +25627,9 @@
       <c r="E16" s="116">
         <v>15.7</v>
       </c>
-      <c r="F16" s="160"/>
-      <c r="G16" s="161"/>
-      <c r="H16" s="161"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="163"/>
+      <c r="H16" s="163"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="114">
@@ -25170,9 +25647,9 @@
       <c r="E17" s="116">
         <v>9.4</v>
       </c>
-      <c r="F17" s="160"/>
-      <c r="G17" s="161"/>
-      <c r="H17" s="161"/>
+      <c r="F17" s="162"/>
+      <c r="G17" s="163"/>
+      <c r="H17" s="163"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="114">
@@ -25190,9 +25667,9 @@
       <c r="E18" s="116">
         <v>3.7</v>
       </c>
-      <c r="F18" s="160"/>
-      <c r="G18" s="161"/>
-      <c r="H18" s="161"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="163"/>
+      <c r="H18" s="163"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="46"/>
@@ -25205,9 +25682,9 @@
         <f>SUM(E5:E18)</f>
         <v>145</v>
       </c>
-      <c r="F19" s="160"/>
-      <c r="G19" s="161"/>
-      <c r="H19" s="161"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="163"/>
+      <c r="H19" s="163"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -25279,10 +25756,10 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="156"/>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="157"/>
+      <c r="A3" s="158"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
       <c r="E3" s="41" t="s">
         <v>216</v>
       </c>
@@ -25304,8 +25781,8 @@
       <c r="D4" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="E4" s="162"/>
-      <c r="F4" s="163"/>
+      <c r="E4" s="164"/>
+      <c r="F4" s="165"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="46">
@@ -25320,8 +25797,8 @@
       <c r="D5" s="49">
         <v>18.100000000000001</v>
       </c>
-      <c r="E5" s="164"/>
-      <c r="F5" s="165"/>
+      <c r="E5" s="166"/>
+      <c r="F5" s="167"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="46">
@@ -25336,8 +25813,8 @@
       <c r="D6" s="49">
         <v>18.600000000000001</v>
       </c>
-      <c r="E6" s="164"/>
-      <c r="F6" s="165"/>
+      <c r="E6" s="166"/>
+      <c r="F6" s="167"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="46">
@@ -25352,8 +25829,8 @@
       <c r="D7" s="88">
         <v>4.8</v>
       </c>
-      <c r="E7" s="164"/>
-      <c r="F7" s="165"/>
+      <c r="E7" s="166"/>
+      <c r="F7" s="167"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="46">
@@ -25368,8 +25845,8 @@
       <c r="D8" s="49">
         <v>13.5</v>
       </c>
-      <c r="E8" s="164"/>
-      <c r="F8" s="165"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="167"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="46">
@@ -25384,8 +25861,8 @@
       <c r="D9" s="88">
         <v>13.6</v>
       </c>
-      <c r="E9" s="164"/>
-      <c r="F9" s="165"/>
+      <c r="E9" s="166"/>
+      <c r="F9" s="167"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="46">
@@ -25400,8 +25877,8 @@
       <c r="D10" s="49">
         <v>6.5</v>
       </c>
-      <c r="E10" s="164"/>
-      <c r="F10" s="165"/>
+      <c r="E10" s="166"/>
+      <c r="F10" s="167"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="46">
@@ -25416,16 +25893,16 @@
       <c r="D11" s="88">
         <v>16.399999999999999</v>
       </c>
-      <c r="E11" s="164"/>
-      <c r="F11" s="165"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="167"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="46"/>
       <c r="B12" s="62"/>
       <c r="C12" s="62"/>
       <c r="D12" s="88"/>
-      <c r="E12" s="164"/>
-      <c r="F12" s="165"/>
+      <c r="E12" s="166"/>
+      <c r="F12" s="167"/>
     </row>
     <row r="13" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="46">
@@ -25440,8 +25917,8 @@
       <c r="D13" s="49">
         <v>19.100000000000001</v>
       </c>
-      <c r="E13" s="164"/>
-      <c r="F13" s="165"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="167"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="46">
@@ -25456,8 +25933,8 @@
       <c r="D14" s="49">
         <v>18.600000000000001</v>
       </c>
-      <c r="E14" s="164"/>
-      <c r="F14" s="165"/>
+      <c r="E14" s="166"/>
+      <c r="F14" s="167"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="46">
@@ -25472,8 +25949,8 @@
       <c r="D15" s="49">
         <v>5</v>
       </c>
-      <c r="E15" s="164"/>
-      <c r="F15" s="165"/>
+      <c r="E15" s="166"/>
+      <c r="F15" s="167"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="46">
@@ -25488,8 +25965,8 @@
       <c r="D16" s="88">
         <v>13.7</v>
       </c>
-      <c r="E16" s="164"/>
-      <c r="F16" s="165"/>
+      <c r="E16" s="166"/>
+      <c r="F16" s="167"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="46">
@@ -25504,8 +25981,8 @@
       <c r="D17" s="49">
         <v>6.7</v>
       </c>
-      <c r="E17" s="164"/>
-      <c r="F17" s="165"/>
+      <c r="E17" s="166"/>
+      <c r="F17" s="167"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="46">
@@ -25520,16 +25997,16 @@
       <c r="D18" s="88">
         <v>16.8</v>
       </c>
-      <c r="E18" s="164"/>
-      <c r="F18" s="165"/>
+      <c r="E18" s="166"/>
+      <c r="F18" s="167"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="59"/>
       <c r="B19" s="62"/>
       <c r="C19" s="62"/>
       <c r="D19" s="88"/>
-      <c r="E19" s="164"/>
-      <c r="F19" s="165"/>
+      <c r="E19" s="166"/>
+      <c r="F19" s="167"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="46">
@@ -25544,8 +26021,8 @@
       <c r="D20" s="49">
         <v>28.6</v>
       </c>
-      <c r="E20" s="164"/>
-      <c r="F20" s="165"/>
+      <c r="E20" s="166"/>
+      <c r="F20" s="167"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="46">
@@ -25560,8 +26037,8 @@
       <c r="D21" s="49">
         <v>19.100000000000001</v>
       </c>
-      <c r="E21" s="164"/>
-      <c r="F21" s="165"/>
+      <c r="E21" s="166"/>
+      <c r="F21" s="167"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="46">
@@ -25576,8 +26053,8 @@
       <c r="D22" s="88">
         <v>5.2</v>
       </c>
-      <c r="E22" s="164"/>
-      <c r="F22" s="165"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="167"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="46">
@@ -25592,8 +26069,8 @@
       <c r="D23" s="49">
         <v>5</v>
       </c>
-      <c r="E23" s="164"/>
-      <c r="F23" s="165"/>
+      <c r="E23" s="166"/>
+      <c r="F23" s="167"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="46">
@@ -25608,8 +26085,8 @@
       <c r="D24" s="88">
         <v>13.9</v>
       </c>
-      <c r="E24" s="164"/>
-      <c r="F24" s="165"/>
+      <c r="E24" s="166"/>
+      <c r="F24" s="167"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="46">
@@ -25624,8 +26101,8 @@
       <c r="D25" s="49">
         <v>5.5</v>
       </c>
-      <c r="E25" s="164"/>
-      <c r="F25" s="165"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="167"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="46">
@@ -25640,8 +26117,8 @@
       <c r="D26" s="88">
         <v>6.7</v>
       </c>
-      <c r="E26" s="164"/>
-      <c r="F26" s="165"/>
+      <c r="E26" s="166"/>
+      <c r="F26" s="167"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="46">
@@ -25656,16 +26133,16 @@
       <c r="D27" s="49">
         <v>16.399999999999999</v>
       </c>
-      <c r="E27" s="164"/>
-      <c r="F27" s="165"/>
+      <c r="E27" s="166"/>
+      <c r="F27" s="167"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="46"/>
       <c r="B28" s="41"/>
       <c r="C28" s="41"/>
       <c r="D28" s="49"/>
-      <c r="E28" s="164"/>
-      <c r="F28" s="165"/>
+      <c r="E28" s="166"/>
+      <c r="F28" s="167"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="46">
@@ -25680,8 +26157,8 @@
       <c r="D29" s="49">
         <v>5</v>
       </c>
-      <c r="E29" s="164"/>
-      <c r="F29" s="165"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="167"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="46">
@@ -25696,8 +26173,8 @@
       <c r="D30" s="88">
         <v>14</v>
       </c>
-      <c r="E30" s="164"/>
-      <c r="F30" s="165"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="167"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="46">
@@ -25712,8 +26189,8 @@
       <c r="D31" s="49">
         <v>4.4000000000000004</v>
       </c>
-      <c r="E31" s="164"/>
-      <c r="F31" s="165"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="167"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="46">
@@ -25728,8 +26205,8 @@
       <c r="D32" s="88">
         <v>6.6</v>
       </c>
-      <c r="E32" s="164"/>
-      <c r="F32" s="165"/>
+      <c r="E32" s="166"/>
+      <c r="F32" s="167"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="46">
@@ -25744,8 +26221,8 @@
       <c r="D33" s="49">
         <v>16.5</v>
       </c>
-      <c r="E33" s="164"/>
-      <c r="F33" s="165"/>
+      <c r="E33" s="166"/>
+      <c r="F33" s="167"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="46"/>
@@ -25757,8 +26234,8 @@
         <f>SUM(D5:D33)</f>
         <v>318.29999999999995</v>
       </c>
-      <c r="E34" s="164"/>
-      <c r="F34" s="165"/>
+      <c r="E34" s="166"/>
+      <c r="F34" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25791,11 +26268,11 @@
       <c r="B1" s="143" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="166" t="s">
+      <c r="C1" s="168" t="s">
         <v>240</v>
       </c>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
       <c r="F1" s="138" t="s">
         <v>303</v>
       </c>
@@ -25810,11 +26287,11 @@
       <c r="B2" s="138">
         <v>531</v>
       </c>
-      <c r="C2" s="167" t="s">
+      <c r="C2" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="167"/>
-      <c r="E2" s="167"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
       <c r="F2" s="58" t="s">
         <v>455</v>
       </c>
@@ -25824,11 +26301,11 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="156"/>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="157"/>
+      <c r="A3" s="158"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="159"/>
       <c r="F3" s="138" t="s">
         <v>216</v>
       </c>
@@ -25853,8 +26330,8 @@
       <c r="E4" s="95" t="s">
         <v>326</v>
       </c>
-      <c r="F4" s="162"/>
-      <c r="G4" s="163"/>
+      <c r="F4" s="164"/>
+      <c r="G4" s="165"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="106"/>
@@ -25870,8 +26347,8 @@
       <c r="E5" s="107">
         <v>38.4</v>
       </c>
-      <c r="F5" s="164"/>
-      <c r="G5" s="165"/>
+      <c r="F5" s="166"/>
+      <c r="G5" s="167"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="106"/>
@@ -25887,8 +26364,8 @@
       <c r="E6" s="107">
         <v>865.8</v>
       </c>
-      <c r="F6" s="164"/>
-      <c r="G6" s="165"/>
+      <c r="F6" s="166"/>
+      <c r="G6" s="167"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="106"/>
@@ -25904,8 +26381,8 @@
       <c r="E7" s="107">
         <v>7.7</v>
       </c>
-      <c r="F7" s="164"/>
-      <c r="G7" s="165"/>
+      <c r="F7" s="166"/>
+      <c r="G7" s="167"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="106"/>
@@ -25913,8 +26390,8 @@
       <c r="C8" s="105"/>
       <c r="D8" s="130"/>
       <c r="E8" s="107"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="165"/>
+      <c r="F8" s="166"/>
+      <c r="G8" s="167"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="106"/>
@@ -25930,8 +26407,8 @@
       <c r="E9" s="107">
         <v>2382.3000000000002</v>
       </c>
-      <c r="F9" s="164"/>
-      <c r="G9" s="165"/>
+      <c r="F9" s="166"/>
+      <c r="G9" s="167"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="106"/>
@@ -25947,8 +26424,8 @@
       <c r="E10" s="107">
         <v>22.3</v>
       </c>
-      <c r="F10" s="164"/>
-      <c r="G10" s="165"/>
+      <c r="F10" s="166"/>
+      <c r="G10" s="167"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="106"/>
@@ -25964,8 +26441,8 @@
       <c r="E11" s="107">
         <v>23.1</v>
       </c>
-      <c r="F11" s="164"/>
-      <c r="G11" s="165"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="167"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="106"/>
@@ -25981,8 +26458,8 @@
       <c r="E12" s="107">
         <v>94</v>
       </c>
-      <c r="F12" s="164"/>
-      <c r="G12" s="165"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="167"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="106"/>
@@ -25998,8 +26475,8 @@
       <c r="E13" s="107">
         <v>12.1</v>
       </c>
-      <c r="F13" s="164"/>
-      <c r="G13" s="165"/>
+      <c r="F13" s="166"/>
+      <c r="G13" s="167"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="106"/>
@@ -26007,8 +26484,8 @@
       <c r="C14" s="105"/>
       <c r="D14" s="130"/>
       <c r="E14" s="107"/>
-      <c r="F14" s="164"/>
-      <c r="G14" s="165"/>
+      <c r="F14" s="166"/>
+      <c r="G14" s="167"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="106"/>
@@ -26024,8 +26501,8 @@
       <c r="E15" s="107">
         <v>10.199999999999999</v>
       </c>
-      <c r="F15" s="164"/>
-      <c r="G15" s="165"/>
+      <c r="F15" s="166"/>
+      <c r="G15" s="167"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="106"/>
@@ -26041,8 +26518,8 @@
       <c r="E16" s="107">
         <v>10.1</v>
       </c>
-      <c r="F16" s="164"/>
-      <c r="G16" s="165"/>
+      <c r="F16" s="166"/>
+      <c r="G16" s="167"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="139"/>
@@ -26050,8 +26527,8 @@
       <c r="C17" s="140"/>
       <c r="D17" s="141"/>
       <c r="E17" s="142"/>
-      <c r="F17" s="164"/>
-      <c r="G17" s="165"/>
+      <c r="F17" s="166"/>
+      <c r="G17" s="167"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="106"/>
@@ -26067,8 +26544,8 @@
       <c r="E18" s="107">
         <v>287.89999999999998</v>
       </c>
-      <c r="F18" s="164"/>
-      <c r="G18" s="165"/>
+      <c r="F18" s="166"/>
+      <c r="G18" s="167"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="106"/>
@@ -26084,8 +26561,8 @@
       <c r="E19" s="126">
         <v>13.8</v>
       </c>
-      <c r="F19" s="164"/>
-      <c r="G19" s="165"/>
+      <c r="F19" s="166"/>
+      <c r="G19" s="167"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="46"/>
@@ -26098,8 +26575,8 @@
         <f>SUM(E5:E19)</f>
         <v>3767.7000000000003</v>
       </c>
-      <c r="F20" s="164"/>
-      <c r="G20" s="165"/>
+      <c r="F20" s="166"/>
+      <c r="G20" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -26136,11 +26613,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="89"/>
-      <c r="C1" s="166" t="s">
+      <c r="C1" s="168" t="s">
         <v>240</v>
       </c>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
       <c r="F1" s="104" t="s">
         <v>303</v>
       </c>
@@ -26155,11 +26632,11 @@
       <c r="B2" s="104" t="s">
         <v>439</v>
       </c>
-      <c r="C2" s="167" t="s">
+      <c r="C2" s="169" t="s">
         <v>441</v>
       </c>
-      <c r="D2" s="167"/>
-      <c r="E2" s="167"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
       <c r="F2" s="58" t="s">
         <v>320</v>
       </c>
@@ -26169,11 +26646,11 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="156"/>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="157"/>
+      <c r="A3" s="158"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="159"/>
       <c r="F3" s="104" t="s">
         <v>216</v>
       </c>
@@ -26198,8 +26675,8 @@
       <c r="E4" s="95" t="s">
         <v>326</v>
       </c>
-      <c r="F4" s="162"/>
-      <c r="G4" s="163"/>
+      <c r="F4" s="164"/>
+      <c r="G4" s="165"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="106">
@@ -26217,8 +26694,8 @@
       <c r="E5" s="121">
         <v>7.1</v>
       </c>
-      <c r="F5" s="164"/>
-      <c r="G5" s="165"/>
+      <c r="F5" s="166"/>
+      <c r="G5" s="167"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="106">
@@ -26236,8 +26713,8 @@
       <c r="E6" s="121">
         <v>16.100000000000001</v>
       </c>
-      <c r="F6" s="164"/>
-      <c r="G6" s="165"/>
+      <c r="F6" s="166"/>
+      <c r="G6" s="167"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="106">
@@ -26255,8 +26732,8 @@
       <c r="E7" s="119">
         <v>7.9</v>
       </c>
-      <c r="F7" s="164"/>
-      <c r="G7" s="165"/>
+      <c r="F7" s="166"/>
+      <c r="G7" s="167"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="106">
@@ -26274,8 +26751,8 @@
       <c r="E8" s="121">
         <v>7.7</v>
       </c>
-      <c r="F8" s="164"/>
-      <c r="G8" s="165"/>
+      <c r="F8" s="166"/>
+      <c r="G8" s="167"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="106">
@@ -26293,8 +26770,8 @@
       <c r="E9" s="119">
         <v>12.5</v>
       </c>
-      <c r="F9" s="164"/>
-      <c r="G9" s="165"/>
+      <c r="F9" s="166"/>
+      <c r="G9" s="167"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="106">
@@ -26312,8 +26789,8 @@
       <c r="E10" s="121">
         <v>12</v>
       </c>
-      <c r="F10" s="164"/>
-      <c r="G10" s="165"/>
+      <c r="F10" s="166"/>
+      <c r="G10" s="167"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="106">
@@ -26331,8 +26808,8 @@
       <c r="E11" s="107">
         <v>7.6</v>
       </c>
-      <c r="F11" s="164"/>
-      <c r="G11" s="165"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="167"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="106">
@@ -26350,8 +26827,8 @@
       <c r="E12" s="121">
         <v>5.3</v>
       </c>
-      <c r="F12" s="164"/>
-      <c r="G12" s="165"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="167"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="106">
@@ -26369,8 +26846,8 @@
       <c r="E13" s="121">
         <v>21.8</v>
       </c>
-      <c r="F13" s="164"/>
-      <c r="G13" s="165"/>
+      <c r="F13" s="166"/>
+      <c r="G13" s="167"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="106">
@@ -26388,8 +26865,8 @@
       <c r="E14" s="107">
         <v>8.5</v>
       </c>
-      <c r="F14" s="164"/>
-      <c r="G14" s="165"/>
+      <c r="F14" s="166"/>
+      <c r="G14" s="167"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="106">
@@ -26407,8 +26884,8 @@
       <c r="E15" s="121">
         <v>15.7</v>
       </c>
-      <c r="F15" s="164"/>
-      <c r="G15" s="165"/>
+      <c r="F15" s="166"/>
+      <c r="G15" s="167"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="106">
@@ -26426,8 +26903,8 @@
       <c r="E16" s="107">
         <v>9.6999999999999993</v>
       </c>
-      <c r="F16" s="164"/>
-      <c r="G16" s="165"/>
+      <c r="F16" s="166"/>
+      <c r="G16" s="167"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="106">
@@ -26445,8 +26922,8 @@
       <c r="E17" s="119">
         <v>9.4</v>
       </c>
-      <c r="F17" s="164"/>
-      <c r="G17" s="165"/>
+      <c r="F17" s="166"/>
+      <c r="G17" s="167"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="106">
@@ -26464,8 +26941,8 @@
       <c r="E18" s="124">
         <v>3.7</v>
       </c>
-      <c r="F18" s="164"/>
-      <c r="G18" s="165"/>
+      <c r="F18" s="166"/>
+      <c r="G18" s="167"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="46"/>
@@ -26478,8 +26955,8 @@
         <f>SUM(E5:E18)</f>
         <v>145</v>
       </c>
-      <c r="F19" s="164"/>
-      <c r="G19" s="165"/>
+      <c r="F19" s="166"/>
+      <c r="G19" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="4">
